--- a/research/traditional_assets/database/data/kazakhstan/kazakhstan_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/kazakhstan/kazakhstan_telecom_services.xlsx
@@ -647,10 +647,10 @@
         <v>0.08510777269758328</v>
       </c>
       <c r="X2">
-        <v>0.09793741277793405</v>
+        <v>0.09792330640809235</v>
       </c>
       <c r="Y2">
-        <v>-0.01282964008035077</v>
+        <v>-0.01281553371050907</v>
       </c>
       <c r="Z2">
         <v>0.8083852129359265</v>
@@ -659,10 +659,10 @@
         <v>0.1372465689685168</v>
       </c>
       <c r="AB2">
-        <v>0.08377212442307029</v>
+        <v>0.08376353299358304</v>
       </c>
       <c r="AC2">
-        <v>0.05347444454544649</v>
+        <v>0.05348303597493374</v>
       </c>
       <c r="AD2">
         <v>586.9</v>
@@ -781,10 +781,10 @@
         <v>0.08510777269758328</v>
       </c>
       <c r="X3">
-        <v>0.09793741277793405</v>
+        <v>0.09792330640809235</v>
       </c>
       <c r="Y3">
-        <v>-0.01282964008035077</v>
+        <v>-0.01281553371050907</v>
       </c>
       <c r="Z3">
         <v>0.8083852129359265</v>
@@ -793,10 +793,10 @@
         <v>0.1372465689685168</v>
       </c>
       <c r="AB3">
-        <v>0.08377212442307029</v>
+        <v>0.08376353299358304</v>
       </c>
       <c r="AC3">
-        <v>0.05347444454544649</v>
+        <v>0.05348303597493374</v>
       </c>
       <c r="AD3">
         <v>586.9</v>
@@ -1151,13 +1151,13 @@
         <v>914.3</v>
       </c>
       <c r="L2">
-        <v>1648.85291934188</v>
+        <v>1648.92341695661</v>
       </c>
       <c r="M2">
         <v>1443.1</v>
       </c>
       <c r="N2">
-        <v>1590.75291934188</v>
+        <v>1590.82341695661</v>
       </c>
       <c r="O2">
         <v>586.9</v>
@@ -1166,16 +1166,16 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.0837721244230703</v>
+        <v>0.083763532993583</v>
       </c>
       <c r="R2">
-        <v>0.080247570134024</v>
+        <v>0.08023824995224731</v>
       </c>
       <c r="S2">
         <v>0.0617047822134061</v>
       </c>
       <c r="T2">
-        <v>0.0540247822134061</v>
+        <v>0.0529047822134061</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.09793741277793409</v>
+        <v>0.09792330640809239</v>
       </c>
       <c r="X2">
-        <v>0.080247570134024</v>
+        <v>0.08023824995224731</v>
       </c>
       <c r="Y2">
         <v>0.806330972935308</v>
@@ -1230,7 +1230,7 @@
         <v>914.3</v>
       </c>
       <c r="AK2">
-        <v>0.0646600645739018</v>
+        <v>0.06464257005823121</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.080247570134024</v>
+        <v>0.08023824995224729</v>
       </c>
       <c r="C2">
-        <v>1648.852919341877</v>
+        <v>1648.923416956605</v>
       </c>
       <c r="D2">
-        <v>1590.752919341877</v>
+        <v>1590.823416956605</v>
       </c>
       <c r="E2">
         <v>-586.9</v>
@@ -1469,19 +1469,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.080247570134024</v>
+        <v>0.08023824995224729</v>
       </c>
       <c r="T2">
         <v>0.5327487740853231</v>
       </c>
       <c r="U2">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V2">
         <v>0.2</v>
       </c>
       <c r="W2">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1500,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08026092281589002</v>
+        <v>0.08024042127447686</v>
       </c>
       <c r="C3">
-        <v>1633.224545318091</v>
+        <v>1633.811122299318</v>
       </c>
       <c r="D3">
-        <v>1590.136545318091</v>
+        <v>1590.723122299318</v>
       </c>
       <c r="E3">
         <v>-571.888</v>
@@ -1533,37 +1533,37 @@
         <v>448.025</v>
       </c>
       <c r="M3">
-        <v>1.013775038234565</v>
+        <v>0.9927582382345648</v>
       </c>
       <c r="N3">
-        <v>447.0112249617654</v>
+        <v>447.0322417617654</v>
       </c>
       <c r="O3">
-        <v>89.40224499235309</v>
+        <v>89.4064483523531</v>
       </c>
       <c r="P3">
-        <v>357.6089799694124</v>
+        <v>357.6257934094123</v>
       </c>
       <c r="Q3">
-        <v>582.7089799694124</v>
+        <v>582.7257934094123</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08052593433712724</v>
+        <v>0.0805165388407503</v>
       </c>
       <c r="T3">
         <v>0.5370538146839924</v>
       </c>
       <c r="U3">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V3">
         <v>0.2</v>
       </c>
       <c r="W3">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>441.9372968387658</v>
+        <v>451.2931575332266</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1582,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08027427549775605</v>
+        <v>0.08024259259670641</v>
       </c>
       <c r="C4">
-        <v>1617.59664876605</v>
+        <v>1618.698840287538</v>
       </c>
       <c r="D4">
-        <v>1589.52064876605</v>
+        <v>1590.622840287538</v>
       </c>
       <c r="E4">
         <v>-556.876</v>
@@ -1615,37 +1615,37 @@
         <v>448.025</v>
       </c>
       <c r="M4">
-        <v>2.027550076469129</v>
+        <v>1.98551647646913</v>
       </c>
       <c r="N4">
-        <v>445.9974499235308</v>
+        <v>446.0394835235309</v>
       </c>
       <c r="O4">
-        <v>89.19948998470618</v>
+        <v>89.20789670470617</v>
       </c>
       <c r="P4">
-        <v>356.7979599388246</v>
+        <v>356.8315868188247</v>
       </c>
       <c r="Q4">
-        <v>581.8979599388247</v>
+        <v>581.9315868188247</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08080997944233462</v>
+        <v>0.08080050709432479</v>
       </c>
       <c r="T4">
         <v>0.541446713254063</v>
       </c>
       <c r="U4">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V4">
         <v>0.2</v>
       </c>
       <c r="W4">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>220.9686484193829</v>
+        <v>225.6465787666133</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08028762817962205</v>
+        <v>0.08024476391893598</v>
       </c>
       <c r="C5">
-        <v>1601.969229131163</v>
+        <v>1603.586570918872</v>
       </c>
       <c r="D5">
-        <v>1588.905229131163</v>
+        <v>1590.522570918873</v>
       </c>
       <c r="E5">
         <v>-541.864</v>
@@ -1697,37 +1697,37 @@
         <v>448.025</v>
       </c>
       <c r="M5">
-        <v>3.041325114703694</v>
+        <v>2.978274714703694</v>
       </c>
       <c r="N5">
-        <v>444.9836748852963</v>
+        <v>445.0467252852963</v>
       </c>
       <c r="O5">
-        <v>88.99673497705926</v>
+        <v>89.00934505705926</v>
       </c>
       <c r="P5">
-        <v>355.986939908237</v>
+        <v>356.0373802282371</v>
       </c>
       <c r="Q5">
-        <v>581.0869399082371</v>
+        <v>581.1373802282371</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08109988114764935</v>
+        <v>0.08109033036343691</v>
       </c>
       <c r="T5">
         <v>0.5459301870523826</v>
       </c>
       <c r="U5">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V5">
         <v>0.2</v>
       </c>
       <c r="W5">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>147.3124322795886</v>
+        <v>150.4310525110756</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1746,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08030098086148806</v>
+        <v>0.08024693524116554</v>
       </c>
       <c r="C6">
-        <v>1586.342285859695</v>
+        <v>1588.474314190932</v>
       </c>
       <c r="D6">
-        <v>1588.290285859695</v>
+        <v>1590.422314190932</v>
       </c>
       <c r="E6">
         <v>-526.852</v>
@@ -1779,37 +1779,37 @@
         <v>448.025</v>
       </c>
       <c r="M6">
-        <v>4.055100152938259</v>
+        <v>3.971032952938259</v>
       </c>
       <c r="N6">
-        <v>443.9698998470617</v>
+        <v>444.0539670470617</v>
       </c>
       <c r="O6">
-        <v>88.79397996941235</v>
+        <v>88.81079340941236</v>
       </c>
       <c r="P6">
-        <v>355.1759198776493</v>
+        <v>355.2431736376494</v>
       </c>
       <c r="Q6">
-        <v>580.2759198776494</v>
+        <v>580.3431736376494</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08139582247182481</v>
+        <v>0.08138619161732219</v>
       </c>
       <c r="T6">
         <v>0.5505070665548338</v>
       </c>
       <c r="U6">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>110.4843242096915</v>
+        <v>112.8232893833067</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1828,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08031433354335407</v>
+        <v>0.0802491065633951</v>
       </c>
       <c r="C7">
-        <v>1570.715818398768</v>
+        <v>1573.362070101326</v>
       </c>
       <c r="D7">
-        <v>1587.675818398768</v>
+        <v>1590.322070101327</v>
       </c>
       <c r="E7">
         <v>-511.84</v>
@@ -1861,37 +1861,37 @@
         <v>448.025</v>
       </c>
       <c r="M7">
-        <v>5.068875191172824</v>
+        <v>4.963791191172823</v>
       </c>
       <c r="N7">
-        <v>442.9561248088272</v>
+        <v>443.0612088088271</v>
       </c>
       <c r="O7">
-        <v>88.59122496176543</v>
+        <v>88.61224176176543</v>
       </c>
       <c r="P7">
-        <v>354.3648998470617</v>
+        <v>354.4489670470617</v>
       </c>
       <c r="Q7">
-        <v>579.4648998470618</v>
+        <v>579.5489670470618</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08169799413966713</v>
+        <v>0.081688281529184</v>
       </c>
       <c r="T7">
         <v>0.5551803014152313</v>
       </c>
       <c r="U7">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>88.38745936775317</v>
+        <v>90.25863150664534</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08032768622522009</v>
+        <v>0.08025127788562468</v>
       </c>
       <c r="C8">
-        <v>1555.089826196361</v>
+        <v>1558.249838647664</v>
       </c>
       <c r="D8">
-        <v>1587.061826196361</v>
+        <v>1590.221838647664</v>
       </c>
       <c r="E8">
         <v>-496.828</v>
@@ -1943,37 +1943,37 @@
         <v>448.025</v>
       </c>
       <c r="M8">
-        <v>6.082650229407388</v>
+        <v>5.956549429407388</v>
       </c>
       <c r="N8">
-        <v>441.9423497705926</v>
+        <v>442.0684505705926</v>
       </c>
       <c r="O8">
-        <v>88.38846995411853</v>
+        <v>88.41369011411852</v>
       </c>
       <c r="P8">
-        <v>353.5538798164741</v>
+        <v>353.654760456474</v>
       </c>
       <c r="Q8">
-        <v>578.653879816474</v>
+        <v>578.7547604564741</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.08200659499193162</v>
+        <v>0.08199679888597906</v>
       </c>
       <c r="T8">
         <v>0.5599529668045736</v>
       </c>
       <c r="U8">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>73.65621613979431</v>
+        <v>75.21552625553778</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.0803410389070861</v>
+        <v>0.08025344920785424</v>
       </c>
       <c r="C9">
-        <v>1539.464308701305</v>
+        <v>1543.137619827558</v>
       </c>
       <c r="D9">
-        <v>1586.448308701305</v>
+        <v>1590.121619827558</v>
       </c>
       <c r="E9">
         <v>-481.816</v>
@@ -2025,37 +2025,37 @@
         <v>448.025</v>
       </c>
       <c r="M9">
-        <v>7.096425267641954</v>
+        <v>6.949307667641954</v>
       </c>
       <c r="N9">
-        <v>440.928574732358</v>
+        <v>441.075692332358</v>
       </c>
       <c r="O9">
-        <v>88.18571494647161</v>
+        <v>88.21513846647161</v>
       </c>
       <c r="P9">
-        <v>352.7428597858864</v>
+        <v>352.8605538658864</v>
       </c>
       <c r="Q9">
-        <v>577.8428597858865</v>
+        <v>577.9605538658864</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.08232183242166417</v>
+        <v>0.08231195102464067</v>
       </c>
       <c r="T9">
         <v>0.5648282701592781</v>
       </c>
       <c r="U9">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>63.13389954839511</v>
+        <v>64.47045107617522</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2074,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08035439158895212</v>
+        <v>0.08025562053008382</v>
       </c>
       <c r="C10">
-        <v>1523.839265363285</v>
+        <v>1528.025413638618</v>
       </c>
       <c r="D10">
-        <v>1585.835265363285</v>
+        <v>1590.021413638618</v>
       </c>
       <c r="E10">
         <v>-466.804</v>
@@ -2107,37 +2107,37 @@
         <v>448.025</v>
       </c>
       <c r="M10">
-        <v>8.110200305876518</v>
+        <v>7.942065905876518</v>
       </c>
       <c r="N10">
-        <v>439.9147996941235</v>
+        <v>440.0829340941235</v>
       </c>
       <c r="O10">
-        <v>87.98295993882471</v>
+        <v>88.01658681882469</v>
       </c>
       <c r="P10">
-        <v>351.9318397552988</v>
+        <v>352.0663472752988</v>
       </c>
       <c r="Q10">
-        <v>577.0318397552987</v>
+        <v>577.1663472752988</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.0826439228389996</v>
+        <v>0.08263395429675145</v>
       </c>
       <c r="T10">
         <v>0.5698095583695195</v>
       </c>
       <c r="U10">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>55.24216210484573</v>
+        <v>56.41164469165333</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08036774427081814</v>
+        <v>0.08025779185231338</v>
       </c>
       <c r="C11">
-        <v>1508.214695632833</v>
+        <v>1512.913220078459</v>
       </c>
       <c r="D11">
-        <v>1585.222695632833</v>
+        <v>1589.921220078459</v>
       </c>
       <c r="E11">
         <v>-451.792</v>
@@ -2189,37 +2189,37 @@
         <v>448.025</v>
       </c>
       <c r="M11">
-        <v>9.123975344111081</v>
+        <v>8.934824144111081</v>
       </c>
       <c r="N11">
-        <v>438.9010246558889</v>
+        <v>439.0901758558889</v>
       </c>
       <c r="O11">
-        <v>87.78020493117778</v>
+        <v>87.81803517117778</v>
       </c>
       <c r="P11">
-        <v>351.1208197247111</v>
+        <v>351.2721406847111</v>
       </c>
       <c r="Q11">
-        <v>576.2208197247112</v>
+        <v>576.3721406847112</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08297309216660613</v>
+        <v>0.08296303456385366</v>
       </c>
       <c r="T11">
         <v>0.5749003254415244</v>
       </c>
       <c r="U11">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>49.1041440931962</v>
+        <v>50.14368417035853</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08038109695268415</v>
+        <v>0.08025996317454295</v>
       </c>
       <c r="C12">
-        <v>1492.590598961332</v>
+        <v>1497.801039144691</v>
       </c>
       <c r="D12">
-        <v>1584.610598961332</v>
+        <v>1589.821039144691</v>
       </c>
       <c r="E12">
         <v>-436.78</v>
@@ -2271,37 +2271,37 @@
         <v>448.025</v>
       </c>
       <c r="M12">
-        <v>10.13775038234565</v>
+        <v>9.927582382345646</v>
       </c>
       <c r="N12">
-        <v>437.8872496176543</v>
+        <v>438.0974176176543</v>
       </c>
       <c r="O12">
-        <v>87.57744992353088</v>
+        <v>87.61948352353087</v>
       </c>
       <c r="P12">
-        <v>350.3097996941235</v>
+        <v>350.4779340941235</v>
       </c>
       <c r="Q12">
-        <v>575.4097996941234</v>
+        <v>575.5779340941235</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.0833095763681595</v>
+        <v>0.08329942772578039</v>
       </c>
       <c r="T12">
         <v>0.5801042206706852</v>
       </c>
       <c r="U12">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>44.19372968387658</v>
+        <v>45.12931575332267</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08039444963455014</v>
+        <v>0.08026213449677251</v>
       </c>
       <c r="C13">
-        <v>1476.966974801014</v>
+        <v>1482.68887083493</v>
       </c>
       <c r="D13">
-        <v>1583.998974801014</v>
+        <v>1589.72087083493</v>
       </c>
       <c r="E13">
         <v>-421.768</v>
@@ -2353,37 +2353,37 @@
         <v>448.025</v>
       </c>
       <c r="M13">
-        <v>11.15152542058021</v>
+        <v>10.92034062058021</v>
       </c>
       <c r="N13">
-        <v>436.8734745794198</v>
+        <v>437.1046593794198</v>
       </c>
       <c r="O13">
-        <v>87.37469491588396</v>
+        <v>87.42093187588397</v>
       </c>
       <c r="P13">
-        <v>349.4987796635359</v>
+        <v>349.6837275035358</v>
       </c>
       <c r="Q13">
-        <v>574.5987796635359</v>
+        <v>574.7837275035358</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.08365362201244436</v>
+        <v>0.08364338028460432</v>
       </c>
       <c r="T13">
         <v>0.5854250573656695</v>
       </c>
       <c r="U13">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>40.17611789443325</v>
+        <v>41.02665068483879</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08040780231641617</v>
+        <v>0.08026430581900208</v>
       </c>
       <c r="C14">
-        <v>1461.34382260495</v>
+        <v>1467.576715146787</v>
       </c>
       <c r="D14">
-        <v>1583.38782260495</v>
+        <v>1589.620715146787</v>
       </c>
       <c r="E14">
         <v>-406.756</v>
@@ -2435,37 +2435,37 @@
         <v>448.025</v>
       </c>
       <c r="M14">
-        <v>12.16530045881478</v>
+        <v>11.91309885881478</v>
       </c>
       <c r="N14">
-        <v>435.8596995411852</v>
+        <v>436.1119011411852</v>
       </c>
       <c r="O14">
-        <v>87.17193990823705</v>
+        <v>87.22238022823706</v>
       </c>
       <c r="P14">
-        <v>348.6877596329481</v>
+        <v>348.8895209129482</v>
       </c>
       <c r="Q14">
-        <v>573.7877596329481</v>
+        <v>573.9895209129481</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08400548687591755</v>
+        <v>0.0839951499470379</v>
       </c>
       <c r="T14">
         <v>0.5908668221673583</v>
       </c>
       <c r="U14">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>36.82810806989715</v>
+        <v>37.60776312776889</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2484,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08042115499828217</v>
+        <v>0.08026647714123165</v>
       </c>
       <c r="C15">
-        <v>1445.721141827061</v>
+        <v>1452.464572077879</v>
       </c>
       <c r="D15">
-        <v>1582.777141827061</v>
+        <v>1589.520572077879</v>
       </c>
       <c r="E15">
         <v>-391.744</v>
@@ -2517,37 +2517,37 @@
         <v>448.025</v>
       </c>
       <c r="M15">
-        <v>13.17907549704934</v>
+        <v>12.90585709704934</v>
       </c>
       <c r="N15">
-        <v>434.8459245029507</v>
+        <v>435.1191429029506</v>
       </c>
       <c r="O15">
-        <v>86.96918490059014</v>
+        <v>87.02382858059013</v>
       </c>
       <c r="P15">
-        <v>347.8767396023605</v>
+        <v>348.0953143223605</v>
       </c>
       <c r="Q15">
-        <v>572.9767396023606</v>
+        <v>573.1953143223604</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.08436544058682688</v>
+        <v>0.084355006268378</v>
       </c>
       <c r="T15">
         <v>0.5964336850104651</v>
       </c>
       <c r="U15">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>33.99517667990506</v>
+        <v>34.71485827178667</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2566,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08043450768014819</v>
+        <v>0.08026864846346121</v>
       </c>
       <c r="C16">
-        <v>1430.098931922108</v>
+        <v>1437.35244162582</v>
       </c>
       <c r="D16">
-        <v>1582.166931922108</v>
+        <v>1589.42044162582</v>
       </c>
       <c r="E16">
         <v>-376.732</v>
@@ -2599,37 +2599,37 @@
         <v>448.025</v>
       </c>
       <c r="M16">
-        <v>14.19285053528391</v>
+        <v>13.89861533528391</v>
       </c>
       <c r="N16">
-        <v>433.8321494647161</v>
+        <v>434.1263846647161</v>
       </c>
       <c r="O16">
-        <v>86.76642989294322</v>
+        <v>86.82527693294321</v>
       </c>
       <c r="P16">
-        <v>347.0657195717728</v>
+        <v>347.3011077317728</v>
       </c>
       <c r="Q16">
-        <v>572.1657195717728</v>
+        <v>572.4011077317729</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.084733765314269</v>
+        <v>0.08472323134137716</v>
       </c>
       <c r="T16">
         <v>0.6021300097801559</v>
       </c>
       <c r="U16">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>31.56694977419755</v>
+        <v>32.23522553808761</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2648,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08044786036201421</v>
+        <v>0.08027081978569078</v>
       </c>
       <c r="C17">
-        <v>1414.477192345691</v>
+        <v>1422.240323788226</v>
       </c>
       <c r="D17">
-        <v>1581.557192345691</v>
+        <v>1589.320323788226</v>
       </c>
       <c r="E17">
         <v>-361.72</v>
@@ -2681,37 +2681,37 @@
         <v>448.025</v>
       </c>
       <c r="M17">
-        <v>15.20662557351847</v>
+        <v>14.89137357351847</v>
       </c>
       <c r="N17">
-        <v>432.8183744264815</v>
+        <v>433.1336264264815</v>
       </c>
       <c r="O17">
-        <v>86.56367488529631</v>
+        <v>86.6267252852963</v>
       </c>
       <c r="P17">
-        <v>346.2546995411852</v>
+        <v>346.5069011411852</v>
       </c>
       <c r="Q17">
-        <v>571.3546995411853</v>
+        <v>571.6069011411853</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.08511075650588623</v>
+        <v>0.08510012053374102</v>
       </c>
       <c r="T17">
         <v>0.6079603657208981</v>
       </c>
       <c r="U17">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>29.46248645591772</v>
+        <v>30.08621050221511</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08046121304388021</v>
+        <v>0.08027299110792034</v>
       </c>
       <c r="C18">
-        <v>1398.855922554251</v>
+        <v>1407.128218562714</v>
       </c>
       <c r="D18">
-        <v>1580.947922554251</v>
+        <v>1589.220218562715</v>
       </c>
       <c r="E18">
         <v>-346.708</v>
@@ -2763,37 +2763,37 @@
         <v>448.025</v>
       </c>
       <c r="M18">
-        <v>16.22040061175304</v>
+        <v>15.88413181175304</v>
       </c>
       <c r="N18">
-        <v>431.804599388247</v>
+        <v>432.1408681882469</v>
       </c>
       <c r="O18">
-        <v>86.36091987764939</v>
+        <v>86.42817363764939</v>
       </c>
       <c r="P18">
-        <v>345.4436795105976</v>
+        <v>345.7126945505976</v>
       </c>
       <c r="Q18">
-        <v>570.5436795105976</v>
+        <v>570.8126945505976</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.08549672367825624</v>
+        <v>0.08548598327830401</v>
       </c>
       <c r="T18">
         <v>0.6139295396602293</v>
       </c>
       <c r="U18">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>27.62108105242286</v>
+        <v>28.20582234582666</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08047456572574622</v>
+        <v>0.08027516243014991</v>
       </c>
       <c r="C19">
-        <v>1383.235122005066</v>
+        <v>1392.016125946901</v>
       </c>
       <c r="D19">
-        <v>1580.339122005066</v>
+        <v>1589.120125946901</v>
       </c>
       <c r="E19">
         <v>-331.696</v>
@@ -2845,37 +2845,37 @@
         <v>448.025</v>
       </c>
       <c r="M19">
-        <v>17.2341756499876</v>
+        <v>16.8768900499876</v>
       </c>
       <c r="N19">
-        <v>430.7908243500124</v>
+        <v>431.1481099500124</v>
       </c>
       <c r="O19">
-        <v>86.15816487000248</v>
+        <v>86.22962199000249</v>
       </c>
       <c r="P19">
-        <v>344.6326594800099</v>
+        <v>344.9184879600099</v>
       </c>
       <c r="Q19">
-        <v>569.7326594800099</v>
+        <v>570.0184879600099</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.08589199126441831</v>
+        <v>0.08588114392032636</v>
       </c>
       <c r="T19">
         <v>0.6200425491161712</v>
       </c>
       <c r="U19">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>25.99631157875093</v>
+        <v>26.54665632548392</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08048791840761224</v>
+        <v>0.08027733375237947</v>
       </c>
       <c r="C20">
-        <v>1367.614790156248</v>
+        <v>1376.904045938403</v>
       </c>
       <c r="D20">
-        <v>1579.730790156248</v>
+        <v>1589.020045938403</v>
       </c>
       <c r="E20">
         <v>-316.684</v>
@@ -2927,37 +2927,37 @@
         <v>448.025</v>
       </c>
       <c r="M20">
-        <v>18.24795068822216</v>
+        <v>17.86964828822216</v>
       </c>
       <c r="N20">
-        <v>429.7770493117778</v>
+        <v>430.1553517117778</v>
       </c>
       <c r="O20">
-        <v>85.95540986235557</v>
+        <v>86.03107034235558</v>
       </c>
       <c r="P20">
-        <v>343.8216394494223</v>
+        <v>344.1242813694222</v>
       </c>
       <c r="Q20">
-        <v>568.9216394494223</v>
+        <v>569.2242813694222</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.0862968995234136</v>
+        <v>0.08628594262678826</v>
       </c>
       <c r="T20">
         <v>0.6263046563637212</v>
       </c>
       <c r="U20">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>24.55207204659811</v>
+        <v>25.07184208517926</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08050127108947827</v>
+        <v>0.08027950507460906</v>
       </c>
       <c r="C21">
-        <v>1351.994926466743</v>
+        <v>1361.791978534839</v>
       </c>
       <c r="D21">
-        <v>1579.122926466744</v>
+        <v>1588.919978534838</v>
       </c>
       <c r="E21">
         <v>-301.672</v>
@@ -3009,37 +3009,37 @@
         <v>448.025</v>
       </c>
       <c r="M21">
-        <v>19.26172572645673</v>
+        <v>18.86240652645673</v>
       </c>
       <c r="N21">
-        <v>428.7632742735432</v>
+        <v>429.1625934735433</v>
       </c>
       <c r="O21">
-        <v>85.75265485470865</v>
+        <v>85.83251869470865</v>
       </c>
       <c r="P21">
-        <v>343.0106194188346</v>
+        <v>343.3300747788346</v>
       </c>
       <c r="Q21">
-        <v>568.1106194188346</v>
+        <v>568.4300747788346</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.0867118055171989</v>
+        <v>0.08670073636303938</v>
       </c>
       <c r="T21">
         <v>0.6327213835433096</v>
       </c>
       <c r="U21">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>23.2598577283561</v>
+        <v>23.7522714491172</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3058,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08051462377134427</v>
+        <v>0.08028167639683861</v>
       </c>
       <c r="C22">
-        <v>1336.375530396335</v>
+        <v>1346.679923733828</v>
       </c>
       <c r="D22">
-        <v>1578.515530396335</v>
+        <v>1588.819923733829</v>
       </c>
       <c r="E22">
         <v>-286.66</v>
@@ -3091,37 +3091,37 @@
         <v>448.025</v>
       </c>
       <c r="M22">
-        <v>20.27550076469129</v>
+        <v>19.85516476469129</v>
       </c>
       <c r="N22">
-        <v>427.7494992353087</v>
+        <v>428.1698352353087</v>
       </c>
       <c r="O22">
-        <v>85.54989984706174</v>
+        <v>85.63396704706174</v>
       </c>
       <c r="P22">
-        <v>342.199599388247</v>
+        <v>342.535868188247</v>
       </c>
       <c r="Q22">
-        <v>567.299599388247</v>
+        <v>567.6358681882471</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.08713708416082883</v>
+        <v>0.08712589994269675</v>
       </c>
       <c r="T22">
         <v>0.6392985289023877</v>
       </c>
       <c r="U22">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>22.09686484193829</v>
+        <v>22.56465787666134</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3140,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08052797645321029</v>
+        <v>0.08028384771906819</v>
       </c>
       <c r="C23">
-        <v>1320.756601405631</v>
+        <v>1331.56788153299</v>
       </c>
       <c r="D23">
-        <v>1577.908601405631</v>
+        <v>1588.71988153299</v>
       </c>
       <c r="E23">
         <v>-271.648</v>
@@ -3173,37 +3173,37 @@
         <v>448.025</v>
       </c>
       <c r="M23">
-        <v>21.28927580292586</v>
+        <v>20.84792300292586</v>
       </c>
       <c r="N23">
-        <v>426.7357241970741</v>
+        <v>427.1770769970741</v>
       </c>
       <c r="O23">
-        <v>85.34714483941482</v>
+        <v>85.43541539941482</v>
       </c>
       <c r="P23">
-        <v>341.3885793576593</v>
+        <v>341.7416615976593</v>
       </c>
       <c r="Q23">
-        <v>566.4885793576593</v>
+        <v>566.8416615976594</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.08757312935239875</v>
+        <v>0.08756182715728215</v>
       </c>
       <c r="T23">
         <v>0.6460421842705564</v>
       </c>
       <c r="U23">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>21.04463318279837</v>
+        <v>21.49015035872508</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08054132913507631</v>
+        <v>0.08028601904129774</v>
       </c>
       <c r="C24">
-        <v>1305.138138956071</v>
+        <v>1316.455851929945</v>
       </c>
       <c r="D24">
-        <v>1577.302138956071</v>
+        <v>1588.619851929945</v>
       </c>
       <c r="E24">
         <v>-256.636</v>
@@ -3255,37 +3255,37 @@
         <v>448.025</v>
       </c>
       <c r="M24">
-        <v>22.30305084116042</v>
+        <v>21.84068124116042</v>
       </c>
       <c r="N24">
-        <v>425.7219491588395</v>
+        <v>426.1843187588395</v>
       </c>
       <c r="O24">
-        <v>85.14438983176791</v>
+        <v>85.23686375176791</v>
       </c>
       <c r="P24">
-        <v>340.5775593270716</v>
+        <v>340.9474550070717</v>
       </c>
       <c r="Q24">
-        <v>565.6775593270717</v>
+        <v>566.0474550070717</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.08802035518990636</v>
+        <v>0.08800893199275436</v>
       </c>
       <c r="T24">
         <v>0.6529587538789344</v>
       </c>
       <c r="U24">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>20.08805894721663</v>
+        <v>20.5133253424194</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3304,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08055468181694231</v>
+        <v>0.08028819036352731</v>
       </c>
       <c r="C25">
-        <v>1289.520142509924</v>
+        <v>1301.343834922312</v>
       </c>
       <c r="D25">
-        <v>1576.696142509924</v>
+        <v>1588.519834922312</v>
       </c>
       <c r="E25">
         <v>-241.624</v>
@@ -3337,37 +3337,37 @@
         <v>448.025</v>
       </c>
       <c r="M25">
-        <v>23.31682587939499</v>
+        <v>22.83343947939499</v>
       </c>
       <c r="N25">
-        <v>424.708174120605</v>
+        <v>425.191560520605</v>
       </c>
       <c r="O25">
-        <v>84.94163482412101</v>
+        <v>85.038312104121</v>
       </c>
       <c r="P25">
-        <v>339.766539296484</v>
+        <v>340.153248416484</v>
       </c>
       <c r="Q25">
-        <v>564.866539296484</v>
+        <v>565.253248416484</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.08847919728293366</v>
+        <v>0.08846764994083625</v>
       </c>
       <c r="T25">
         <v>0.6600549746459717</v>
       </c>
       <c r="U25">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>19.21466507994634</v>
+        <v>19.62144163187942</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3386,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08056803449880831</v>
+        <v>0.08029036168575686</v>
       </c>
       <c r="C26">
-        <v>1273.902611530282</v>
+        <v>1286.231830507714</v>
       </c>
       <c r="D26">
-        <v>1576.090611530282</v>
+        <v>1588.419830507715</v>
       </c>
       <c r="E26">
         <v>-226.612</v>
@@ -3419,37 +3419,37 @@
         <v>448.025</v>
       </c>
       <c r="M26">
-        <v>24.33060091762955</v>
+        <v>23.82619771762955</v>
       </c>
       <c r="N26">
-        <v>423.6943990823704</v>
+        <v>424.1988022823704</v>
       </c>
       <c r="O26">
-        <v>84.73887981647408</v>
+        <v>84.8397604564741</v>
       </c>
       <c r="P26">
-        <v>338.9555192658963</v>
+        <v>339.3590418258963</v>
       </c>
       <c r="Q26">
-        <v>564.0555192658964</v>
+        <v>564.4590418258963</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.0889501141678827</v>
+        <v>0.08893843941386764</v>
       </c>
       <c r="T26">
         <v>0.667337938064773</v>
       </c>
       <c r="U26">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>18.41405403494857</v>
+        <v>18.80388156388445</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3468,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08058138718067433</v>
+        <v>0.08029253300798643</v>
       </c>
       <c r="C27">
-        <v>1258.285545481063</v>
+        <v>1271.119838683772</v>
       </c>
       <c r="D27">
-        <v>1575.485545481063</v>
+        <v>1588.319838683772</v>
       </c>
       <c r="E27">
         <v>-211.6</v>
@@ -3501,37 +3501,37 @@
         <v>448.025</v>
       </c>
       <c r="M27">
-        <v>25.34437595586412</v>
+        <v>24.81895595586412</v>
       </c>
       <c r="N27">
-        <v>422.6806240441359</v>
+        <v>423.2060440441359</v>
       </c>
       <c r="O27">
-        <v>84.53612480882718</v>
+        <v>84.64120880882717</v>
       </c>
       <c r="P27">
-        <v>338.1444992353087</v>
+        <v>338.5648352353087</v>
       </c>
       <c r="Q27">
-        <v>563.2444992353087</v>
+        <v>563.6648352353087</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.08943358883643041</v>
+        <v>0.08942178327284656</v>
       </c>
       <c r="T27">
         <v>0.6748151138414091</v>
       </c>
       <c r="U27">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>17.67749187355063</v>
+        <v>18.05172630132907</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3550,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08059473986254034</v>
+        <v>0.080294704330216</v>
       </c>
       <c r="C28">
-        <v>1242.668943827007</v>
+        <v>1256.007859448107</v>
       </c>
       <c r="D28">
-        <v>1574.880943827007</v>
+        <v>1588.219859448107</v>
       </c>
       <c r="E28">
         <v>-196.588</v>
@@ -3583,37 +3583,37 @@
         <v>448.025</v>
       </c>
       <c r="M28">
-        <v>26.35815099409868</v>
+        <v>25.81171419409868</v>
       </c>
       <c r="N28">
-        <v>421.6668490059013</v>
+        <v>422.2132858059013</v>
       </c>
       <c r="O28">
-        <v>84.33336980118025</v>
+        <v>84.44265716118026</v>
       </c>
       <c r="P28">
-        <v>337.333479204721</v>
+        <v>337.7706286447211</v>
       </c>
       <c r="Q28">
-        <v>562.433479204721</v>
+        <v>562.8706286447211</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.08993013038791184</v>
+        <v>0.08991819047936545</v>
       </c>
       <c r="T28">
         <v>0.6824943754498463</v>
       </c>
       <c r="U28">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V28">
         <v>0.2</v>
       </c>
       <c r="W28">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>16.99758833995253</v>
+        <v>17.35742913589333</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08060809254440636</v>
+        <v>0.08029687565244557</v>
       </c>
       <c r="C29">
-        <v>1227.052806033678</v>
+        <v>1240.895892798344</v>
       </c>
       <c r="D29">
-        <v>1574.276806033678</v>
+        <v>1588.119892798344</v>
       </c>
       <c r="E29">
         <v>-181.576</v>
@@ -3665,37 +3665,37 @@
         <v>448.025</v>
       </c>
       <c r="M29">
-        <v>27.37192603233325</v>
+        <v>26.80447243233325</v>
       </c>
       <c r="N29">
-        <v>420.6530739676667</v>
+        <v>421.2205275676667</v>
       </c>
       <c r="O29">
-        <v>84.13061479353335</v>
+        <v>84.24410551353336</v>
       </c>
       <c r="P29">
-        <v>336.5224591741334</v>
+        <v>336.9764220541334</v>
       </c>
       <c r="Q29">
-        <v>561.6224591741334</v>
+        <v>562.0764220541334</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.09044027581751606</v>
+        <v>0.09042819788332321</v>
       </c>
       <c r="T29">
         <v>0.6903840277872817</v>
       </c>
       <c r="U29">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V29">
         <v>0.2</v>
       </c>
       <c r="W29">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>16.3680480310654</v>
+        <v>16.71456139011951</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3714,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08062144522627238</v>
+        <v>0.08029904697467513</v>
       </c>
       <c r="C30">
-        <v>1211.437131567457</v>
+        <v>1225.783938732107</v>
       </c>
       <c r="D30">
-        <v>1573.673131567457</v>
+        <v>1588.019938732107</v>
       </c>
       <c r="E30">
         <v>-166.564</v>
@@ -3747,37 +3747,37 @@
         <v>448.025</v>
       </c>
       <c r="M30">
-        <v>28.38570107056782</v>
+        <v>27.79723067056782</v>
       </c>
       <c r="N30">
-        <v>419.6392989294322</v>
+        <v>420.2277693294321</v>
       </c>
       <c r="O30">
-        <v>83.92785978588644</v>
+        <v>84.04555386588643</v>
       </c>
       <c r="P30">
-        <v>335.7114391435458</v>
+        <v>336.1822154635457</v>
       </c>
       <c r="Q30">
-        <v>560.8114391435458</v>
+        <v>561.2822154635458</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.09096459195349815</v>
+        <v>0.0909523721596131</v>
       </c>
       <c r="T30">
         <v>0.6984928371340903</v>
       </c>
       <c r="U30">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>15.78347488709878</v>
+        <v>16.11761276904381</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3796,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08063479790813836</v>
+        <v>0.08030121829690469</v>
       </c>
       <c r="C31">
-        <v>1195.821919895545</v>
+        <v>1210.671997247018</v>
       </c>
       <c r="D31">
-        <v>1573.069919895545</v>
+        <v>1587.919997247019</v>
       </c>
       <c r="E31">
         <v>-151.5520000000001</v>
@@ -3829,37 +3829,37 @@
         <v>448.025</v>
       </c>
       <c r="M31">
-        <v>29.39947610880237</v>
+        <v>28.78998890880237</v>
       </c>
       <c r="N31">
-        <v>418.6255238911976</v>
+        <v>419.2350110911976</v>
       </c>
       <c r="O31">
-        <v>83.72510477823953</v>
+        <v>83.84700221823954</v>
       </c>
       <c r="P31">
-        <v>334.900419112958</v>
+        <v>335.3880088729581</v>
       </c>
       <c r="Q31">
-        <v>560.0004191129581</v>
+        <v>560.4880088729581</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.09150367755809946</v>
+        <v>0.09149131190847457</v>
       </c>
       <c r="T31">
         <v>0.7068300636455976</v>
       </c>
       <c r="U31">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V31">
         <v>0.2</v>
       </c>
       <c r="W31">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>15.23921713237124</v>
+        <v>15.56183301838713</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3878,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08064815059000439</v>
+        <v>0.08030338961913427</v>
       </c>
       <c r="C32">
-        <v>1180.207170485957</v>
+        <v>1195.560068340703</v>
       </c>
       <c r="D32">
-        <v>1572.467170485957</v>
+        <v>1587.820068340703</v>
       </c>
       <c r="E32">
         <v>-136.54</v>
@@ -3911,37 +3911,37 @@
         <v>448.025</v>
       </c>
       <c r="M32">
-        <v>30.41325114703694</v>
+        <v>29.78274714703694</v>
       </c>
       <c r="N32">
-        <v>417.611748852963</v>
+        <v>418.242252852963</v>
       </c>
       <c r="O32">
-        <v>83.52234977059261</v>
+        <v>83.64845057059262</v>
       </c>
       <c r="P32">
-        <v>334.0893990823704</v>
+        <v>334.5938022823704</v>
       </c>
       <c r="Q32">
-        <v>559.1893990823705</v>
+        <v>559.6938022823704</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.09205816560854654</v>
+        <v>0.09204564993587494</v>
       </c>
       <c r="T32">
         <v>0.7154054966288624</v>
       </c>
       <c r="U32">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>14.73124322795886</v>
+        <v>15.04310525110755</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.0806615032718704</v>
+        <v>0.08030556094136385</v>
       </c>
       <c r="C33">
-        <v>1164.592882807526</v>
+        <v>1180.448152010787</v>
       </c>
       <c r="D33">
-        <v>1571.864882807526</v>
+        <v>1587.720152010787</v>
       </c>
       <c r="E33">
         <v>-121.528</v>
@@ -3993,37 +3993,37 @@
         <v>448.025</v>
       </c>
       <c r="M33">
-        <v>31.4270261852715</v>
+        <v>30.77550538527151</v>
       </c>
       <c r="N33">
-        <v>416.5979738147284</v>
+        <v>417.2494946147285</v>
       </c>
       <c r="O33">
-        <v>83.3195947629457</v>
+        <v>83.44989892294569</v>
       </c>
       <c r="P33">
-        <v>333.2783790517827</v>
+        <v>333.7995956917828</v>
       </c>
       <c r="Q33">
-        <v>558.3783790517828</v>
+        <v>558.8995956917828</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.09262872577639786</v>
+        <v>0.09261605573218545</v>
       </c>
       <c r="T33">
         <v>0.7242294928870044</v>
       </c>
       <c r="U33">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V33">
         <v>0.2</v>
       </c>
       <c r="W33">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>14.25604183350857</v>
+        <v>14.55784379139441</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4042,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08067485595373641</v>
+        <v>0.0803077322635934</v>
       </c>
       <c r="C34">
-        <v>1148.979056329895</v>
+        <v>1165.336248254897</v>
       </c>
       <c r="D34">
-        <v>1571.263056329896</v>
+        <v>1587.620248254897</v>
       </c>
       <c r="E34">
         <v>-106.516</v>
@@ -4075,37 +4075,37 @@
         <v>448.025</v>
       </c>
       <c r="M34">
-        <v>32.44080122350607</v>
+        <v>31.76826362350607</v>
       </c>
       <c r="N34">
-        <v>415.5841987764939</v>
+        <v>416.2567363764939</v>
       </c>
       <c r="O34">
-        <v>83.11683975529878</v>
+        <v>83.25134727529878</v>
       </c>
       <c r="P34">
-        <v>332.4673590211951</v>
+        <v>333.0053891011951</v>
       </c>
       <c r="Q34">
-        <v>557.5673590211952</v>
+        <v>558.1053891011952</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.09321606712565658</v>
+        <v>0.09320323816956391</v>
       </c>
       <c r="T34">
         <v>0.7333130184468565</v>
       </c>
       <c r="U34">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>13.81054052621143</v>
+        <v>14.10291117291333</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4124,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08068820863560243</v>
+        <v>0.08030990358582298</v>
       </c>
       <c r="C35">
-        <v>1133.365690523524</v>
+        <v>1150.224357070658</v>
       </c>
       <c r="D35">
-        <v>1570.661690523524</v>
+        <v>1587.520357070658</v>
       </c>
       <c r="E35">
         <v>-91.50400000000002</v>
@@ -4157,37 +4157,37 @@
         <v>448.025</v>
       </c>
       <c r="M35">
-        <v>33.45457626174063</v>
+        <v>32.76102186174064</v>
       </c>
       <c r="N35">
-        <v>414.5704237382594</v>
+        <v>415.2639781382593</v>
       </c>
       <c r="O35">
-        <v>82.91408474765188</v>
+        <v>83.05279562765188</v>
       </c>
       <c r="P35">
-        <v>331.6563389906075</v>
+        <v>332.2111825106075</v>
       </c>
       <c r="Q35">
-        <v>556.7563389906074</v>
+        <v>557.3111825106075</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.09382094105250513</v>
+        <v>0.09380794844089399</v>
       </c>
       <c r="T35">
         <v>0.7426676940234206</v>
       </c>
       <c r="U35">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>13.39203929814442</v>
+        <v>13.6755502282796</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4206,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08070156131746843</v>
+        <v>0.08031207490805253</v>
       </c>
       <c r="C36">
-        <v>1117.75278485968</v>
+        <v>1135.112478455699</v>
       </c>
       <c r="D36">
-        <v>1570.06078485968</v>
+        <v>1587.420478455699</v>
       </c>
       <c r="E36">
         <v>-76.49200000000002</v>
@@ -4239,37 +4239,37 @@
         <v>448.025</v>
       </c>
       <c r="M36">
-        <v>34.4683512999752</v>
+        <v>33.7537800999752</v>
       </c>
       <c r="N36">
-        <v>413.5566487000248</v>
+        <v>414.2712199000248</v>
       </c>
       <c r="O36">
-        <v>82.71132974000496</v>
+        <v>82.85424398000497</v>
       </c>
       <c r="P36">
-        <v>330.8453189600198</v>
+        <v>331.4169759200198</v>
       </c>
       <c r="Q36">
-        <v>555.9453189600199</v>
+        <v>556.5169759200198</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.09444414449228845</v>
+        <v>0.09443098326590071</v>
       </c>
       <c r="T36">
         <v>0.7523058446174562</v>
       </c>
       <c r="U36">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V36">
         <v>0.2</v>
       </c>
       <c r="W36">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>12.99815578937547</v>
+        <v>13.27332816274196</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4288,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08102291399933445</v>
+        <v>0.0803142462302821</v>
       </c>
       <c r="C37">
-        <v>1088.416494600309</v>
+        <v>1120.000612407646</v>
       </c>
       <c r="D37">
-        <v>1555.736494600309</v>
+        <v>1587.320612407646</v>
       </c>
       <c r="E37">
         <v>-61.48000000000002</v>
@@ -4321,45 +4321,45 @@
         <v>448.025</v>
       </c>
       <c r="M37">
-        <v>36.06008833820977</v>
+        <v>34.74653833820977</v>
       </c>
       <c r="N37">
-        <v>411.9649116617902</v>
+        <v>413.2784616617902</v>
       </c>
       <c r="O37">
-        <v>82.39298233235805</v>
+        <v>82.65569233235806</v>
       </c>
       <c r="P37">
-        <v>329.5719293294322</v>
+        <v>330.6227693294322</v>
       </c>
       <c r="Q37">
-        <v>554.6719293294323</v>
+        <v>555.7227693294321</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.09508652342252666</v>
+        <v>0.09507318839321535</v>
       </c>
       <c r="T37">
         <v>0.7622405536913084</v>
       </c>
       <c r="U37">
-        <v>0.06863097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V37">
         <v>0.2</v>
       </c>
       <c r="W37">
-        <v>0.05490478221340607</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y37">
-        <v>12.42440106629652</v>
+        <v>12.89409021523505</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4370,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08104506668120048</v>
+        <v>0.08074841755251166</v>
       </c>
       <c r="C38">
-        <v>1072.426663122673</v>
+        <v>1085.269004558285</v>
       </c>
       <c r="D38">
-        <v>1554.758663122673</v>
+        <v>1567.601004558285</v>
       </c>
       <c r="E38">
         <v>-46.46800000000007</v>
@@ -4403,37 +4403,37 @@
         <v>448.025</v>
       </c>
       <c r="M38">
-        <v>37.09037657644433</v>
+        <v>36.54994457644433</v>
       </c>
       <c r="N38">
-        <v>410.9346234235556</v>
+        <v>411.4750554235557</v>
       </c>
       <c r="O38">
-        <v>82.18692468471113</v>
+        <v>82.29501108471113</v>
       </c>
       <c r="P38">
-        <v>328.7476987388445</v>
+        <v>329.1800443388445</v>
       </c>
       <c r="Q38">
-        <v>553.8476987388445</v>
+        <v>554.2800443388446</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.09574897669433483</v>
+        <v>0.09573546243075856</v>
       </c>
       <c r="T38">
         <v>0.7724857224237184</v>
       </c>
       <c r="U38">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V38">
         <v>0.2</v>
       </c>
       <c r="W38">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>12.07927881445495</v>
+        <v>12.25788452463872</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08106721936306648</v>
+        <v>0.08076258887474123</v>
       </c>
       <c r="C39">
-        <v>1056.438060071325</v>
+        <v>1069.621611709014</v>
       </c>
       <c r="D39">
-        <v>1553.782060071325</v>
+        <v>1566.965611709014</v>
       </c>
       <c r="E39">
         <v>-31.45600000000002</v>
@@ -4485,37 +4485,37 @@
         <v>448.025</v>
       </c>
       <c r="M39">
-        <v>38.1206648146789</v>
+        <v>37.5652208146789</v>
       </c>
       <c r="N39">
-        <v>409.9043351853211</v>
+        <v>410.4597791853211</v>
       </c>
       <c r="O39">
-        <v>81.98086703706423</v>
+        <v>82.09195583706422</v>
       </c>
       <c r="P39">
-        <v>327.9234681482569</v>
+        <v>328.3678233482568</v>
       </c>
       <c r="Q39">
-        <v>553.0234681482568</v>
+        <v>553.4678233482568</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.09643246022874005</v>
+        <v>0.0964187610409222</v>
       </c>
       <c r="T39">
         <v>0.7830561346079511</v>
       </c>
       <c r="U39">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V39">
         <v>0.2</v>
       </c>
       <c r="W39">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>11.75281181946968</v>
+        <v>11.92659034829713</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4534,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08108937204493248</v>
+        <v>0.08077676019697079</v>
       </c>
       <c r="C40">
-        <v>1040.45068313285</v>
+        <v>1053.974733736294</v>
       </c>
       <c r="D40">
-        <v>1552.80668313285</v>
+        <v>1566.330733736294</v>
       </c>
       <c r="E40">
         <v>-16.44400000000007</v>
@@ -4567,37 +4567,37 @@
         <v>448.025</v>
       </c>
       <c r="M40">
-        <v>39.15095305291346</v>
+        <v>38.58049705291346</v>
       </c>
       <c r="N40">
-        <v>408.8740469470865</v>
+        <v>409.4445029470865</v>
       </c>
       <c r="O40">
-        <v>81.77480938941731</v>
+        <v>81.8889005894173</v>
       </c>
       <c r="P40">
-        <v>327.0992375576692</v>
+        <v>327.5556023576692</v>
       </c>
       <c r="Q40">
-        <v>552.1992375576692</v>
+        <v>552.6556023576693</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.09713799161909384</v>
+        <v>0.09712410154173627</v>
       </c>
       <c r="T40">
         <v>0.7939675278303846</v>
       </c>
       <c r="U40">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V40">
         <v>0.2</v>
       </c>
       <c r="W40">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>11.44352729790469</v>
+        <v>11.61273270755247</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4616,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08111152472679851</v>
+        <v>0.08079093151920037</v>
       </c>
       <c r="C41">
-        <v>1024.464529999644</v>
+        <v>1038.328370014548</v>
       </c>
       <c r="D41">
-        <v>1551.832529999644</v>
+        <v>1565.696370014549</v>
       </c>
       <c r="E41">
         <v>-1.432000000000016</v>
@@ -4649,37 +4649,37 @@
         <v>448.025</v>
       </c>
       <c r="M41">
-        <v>40.18124129114803</v>
+        <v>39.59577329114803</v>
       </c>
       <c r="N41">
-        <v>407.843758708852</v>
+        <v>408.429226708852</v>
       </c>
       <c r="O41">
-        <v>81.5687517417704</v>
+        <v>81.6858453417704</v>
       </c>
       <c r="P41">
-        <v>326.2750069670816</v>
+        <v>326.7433813670816</v>
       </c>
       <c r="Q41">
-        <v>551.3750069670816</v>
+        <v>551.8433813670815</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.09786665518618057</v>
+        <v>0.09785256796060984</v>
       </c>
       <c r="T41">
         <v>0.8052366716502752</v>
       </c>
       <c r="U41">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V41">
         <v>0.2</v>
       </c>
       <c r="W41">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>11.15010352103534</v>
+        <v>11.31497033043574</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4698,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08113367740866453</v>
+        <v>0.08080510284142994</v>
       </c>
       <c r="C42">
-        <v>1008.47959836989</v>
+        <v>1022.682519919217</v>
       </c>
       <c r="D42">
-        <v>1550.85959836989</v>
+        <v>1565.062519919217</v>
       </c>
       <c r="E42">
         <v>13.57999999999993</v>
@@ -4731,37 +4731,37 @@
         <v>448.025</v>
       </c>
       <c r="M42">
-        <v>41.21152952938259</v>
+        <v>40.61104952938258</v>
       </c>
       <c r="N42">
-        <v>406.8134704706174</v>
+        <v>407.4139504706174</v>
       </c>
       <c r="O42">
-        <v>81.36269409412348</v>
+        <v>81.48279009412349</v>
       </c>
       <c r="P42">
-        <v>325.4507763764939</v>
+        <v>325.9311603764939</v>
       </c>
       <c r="Q42">
-        <v>550.550776376494</v>
+        <v>551.031160376494</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.09861960753883683</v>
+        <v>0.09860531659344585</v>
       </c>
       <c r="T42">
         <v>0.8168814535974954</v>
       </c>
       <c r="U42">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V42">
         <v>0.2</v>
       </c>
       <c r="W42">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>10.87135093300945</v>
+        <v>11.03209607217485</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4780,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08115583009053054</v>
+        <v>0.0808192741636595</v>
       </c>
       <c r="C43">
-        <v>992.495885947538</v>
+        <v>1007.037182826748</v>
       </c>
       <c r="D43">
-        <v>1549.887885947538</v>
+        <v>1564.429182826748</v>
       </c>
       <c r="E43">
         <v>28.59199999999998</v>
@@ -4813,37 +4813,37 @@
         <v>448.025</v>
       </c>
       <c r="M43">
-        <v>42.24181776761716</v>
+        <v>41.62632576761715</v>
       </c>
       <c r="N43">
-        <v>405.7831822323828</v>
+        <v>406.3986742323828</v>
       </c>
       <c r="O43">
-        <v>81.15663644647657</v>
+        <v>81.27973484647657</v>
       </c>
       <c r="P43">
-        <v>324.6265457859063</v>
+        <v>325.1189393859062</v>
       </c>
       <c r="Q43">
-        <v>549.7265457859063</v>
+        <v>550.2189393859062</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.0993980837000577</v>
+        <v>0.09938358212908985</v>
       </c>
       <c r="T43">
         <v>0.8289209739158078</v>
       </c>
       <c r="U43">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V43">
         <v>0.2</v>
       </c>
       <c r="W43">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>10.60619603220434</v>
+        <v>10.76302055821937</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4862,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.08117798277239655</v>
+        <v>0.08083344548588907</v>
       </c>
       <c r="C44">
-        <v>976.5133904422896</v>
+        <v>991.3923581145993</v>
       </c>
       <c r="D44">
-        <v>1548.91739044229</v>
+        <v>1563.796358114599</v>
       </c>
       <c r="E44">
         <v>43.60399999999993</v>
@@ -4895,37 +4895,37 @@
         <v>448.025</v>
       </c>
       <c r="M44">
-        <v>43.27210600585172</v>
+        <v>42.64160200585172</v>
       </c>
       <c r="N44">
-        <v>404.7528939941483</v>
+        <v>405.3833979941483</v>
       </c>
       <c r="O44">
-        <v>80.95057879882967</v>
+        <v>81.07667959882966</v>
       </c>
       <c r="P44">
-        <v>323.8023151953186</v>
+        <v>324.3067183953186</v>
       </c>
       <c r="Q44">
-        <v>548.9023151953186</v>
+        <v>549.4067183953186</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1002034038668379</v>
+        <v>0.1001886844073423</v>
       </c>
       <c r="T44">
         <v>0.8413756501071653</v>
       </c>
       <c r="U44">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V44">
         <v>0.2</v>
       </c>
       <c r="W44">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>10.3536675552471</v>
+        <v>10.50675816397605</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.08120013545426256</v>
+        <v>0.08084761680811864</v>
       </c>
       <c r="C45">
-        <v>960.5321095695782</v>
+        <v>975.7480451612365</v>
       </c>
       <c r="D45">
-        <v>1547.948109569578</v>
+        <v>1563.164045161237</v>
       </c>
       <c r="E45">
         <v>58.61599999999999</v>
@@ -4977,37 +4977,37 @@
         <v>448.025</v>
       </c>
       <c r="M45">
-        <v>44.30239424408629</v>
+        <v>43.65687824408629</v>
       </c>
       <c r="N45">
-        <v>403.7226057559137</v>
+        <v>404.3681217559137</v>
       </c>
       <c r="O45">
-        <v>80.74452115118275</v>
+        <v>80.87362435118274</v>
       </c>
       <c r="P45">
-        <v>322.978084604731</v>
+        <v>323.494497404731</v>
       </c>
       <c r="Q45">
-        <v>548.078084604731</v>
+        <v>548.594497404731</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1010369808815754</v>
+        <v>0.1010220358883404</v>
       </c>
       <c r="T45">
         <v>0.854267332480676</v>
       </c>
       <c r="U45">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V45">
         <v>0.2</v>
       </c>
       <c r="W45">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>10.112884588846</v>
+        <v>10.26241495086033</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.08122228813612857</v>
+        <v>0.08086178813034821</v>
       </c>
       <c r="C46">
-        <v>944.5520410505543</v>
+        <v>960.1042433461295</v>
       </c>
       <c r="D46">
-        <v>1546.980041050554</v>
+        <v>1562.532243346129</v>
       </c>
       <c r="E46">
         <v>73.62799999999993</v>
@@ -5059,37 +5059,37 @@
         <v>448.025</v>
       </c>
       <c r="M46">
-        <v>45.33268248232085</v>
+        <v>44.67215448232085</v>
       </c>
       <c r="N46">
-        <v>402.6923175176792</v>
+        <v>403.3528455176792</v>
       </c>
       <c r="O46">
-        <v>80.53846350353584</v>
+        <v>80.67056910353584</v>
       </c>
       <c r="P46">
-        <v>322.1538540141433</v>
+        <v>322.6822764141433</v>
       </c>
       <c r="Q46">
-        <v>547.2538540141434</v>
+        <v>547.7822764141433</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.101900328503982</v>
+        <v>0.1018851499222313</v>
       </c>
       <c r="T46">
         <v>0.8676194320818118</v>
       </c>
       <c r="U46">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V46">
         <v>0.2</v>
       </c>
       <c r="W46">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>9.883046302735865</v>
+        <v>10.02917824743168</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5108,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.08203644081799459</v>
+        <v>0.08087595945257776</v>
       </c>
       <c r="C47">
-        <v>894.7828209488193</v>
+        <v>944.4609520497511</v>
       </c>
       <c r="D47">
-        <v>1512.222820948819</v>
+        <v>1561.900952049751</v>
       </c>
       <c r="E47">
         <v>88.63999999999999</v>
@@ -5141,45 +5141,45 @@
         <v>448.025</v>
       </c>
       <c r="M47">
-        <v>47.84915872055541</v>
+        <v>45.68743072055541</v>
       </c>
       <c r="N47">
-        <v>400.1758412794446</v>
+        <v>402.3375692794446</v>
       </c>
       <c r="O47">
-        <v>80.03516825588892</v>
+        <v>80.46751385588891</v>
       </c>
       <c r="P47">
-        <v>320.1406730235557</v>
+        <v>321.8700554235556</v>
       </c>
       <c r="Q47">
-        <v>545.2406730235557</v>
+        <v>546.9700554235557</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1027950705853852</v>
+        <v>0.102779649920991</v>
       </c>
       <c r="T47">
         <v>0.8814570625775345</v>
       </c>
       <c r="U47">
-        <v>0.07083097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V47">
         <v>0.2</v>
       </c>
       <c r="W47">
-        <v>0.05666478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y47">
-        <v>9.363278518991683</v>
+        <v>9.806307619710978</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5190,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.0820761934998606</v>
+        <v>0.08151573077480734</v>
       </c>
       <c r="C48">
-        <v>878.113675947872</v>
+        <v>901.4708198484259</v>
       </c>
       <c r="D48">
-        <v>1510.565675947872</v>
+        <v>1533.922819848426</v>
       </c>
       <c r="E48">
         <v>103.6519999999999</v>
@@ -5223,37 +5223,37 @@
         <v>448.025</v>
       </c>
       <c r="M48">
-        <v>48.91247335878997</v>
+        <v>47.87664535878997</v>
       </c>
       <c r="N48">
-        <v>399.11252664121</v>
+        <v>400.14835464121</v>
       </c>
       <c r="O48">
-        <v>79.82250532824202</v>
+        <v>80.02967092824201</v>
       </c>
       <c r="P48">
-        <v>319.290021312968</v>
+        <v>320.118683712968</v>
       </c>
       <c r="Q48">
-        <v>544.390021312968</v>
+        <v>545.218683712968</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1037229512623959</v>
+        <v>0.1037072795493343</v>
       </c>
       <c r="T48">
         <v>0.8958071979064322</v>
       </c>
       <c r="U48">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V48">
         <v>0.2</v>
       </c>
       <c r="W48">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>9.159728985970125</v>
+        <v>9.357902932473197</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.08211594618172662</v>
+        <v>0.0815435020970369</v>
       </c>
       <c r="C49">
-        <v>861.448158882581</v>
+        <v>885.267020992521</v>
       </c>
       <c r="D49">
-        <v>1508.912158882581</v>
+        <v>1532.731020992521</v>
       </c>
       <c r="E49">
         <v>118.664</v>
@@ -5305,37 +5305,37 @@
         <v>448.025</v>
       </c>
       <c r="M49">
-        <v>49.97578799702454</v>
+        <v>48.91744199702454</v>
       </c>
       <c r="N49">
-        <v>398.0492120029754</v>
+        <v>399.1075580029755</v>
       </c>
       <c r="O49">
-        <v>79.60984240059508</v>
+        <v>79.8215116005951</v>
       </c>
       <c r="P49">
-        <v>318.4393696023803</v>
+        <v>319.2860464023804</v>
       </c>
       <c r="Q49">
-        <v>543.5393696023804</v>
+        <v>544.3860464023803</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1046858463045769</v>
+        <v>0.1046699140693133</v>
       </c>
       <c r="T49">
         <v>0.9106988477760428</v>
       </c>
       <c r="U49">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V49">
         <v>0.2</v>
       </c>
       <c r="W49">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>8.9648411352048</v>
+        <v>9.158798614761002</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5354,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.08215569886359263</v>
+        <v>0.08157127341926647</v>
       </c>
       <c r="C50">
-        <v>844.7862578521848</v>
+        <v>869.065072662297</v>
       </c>
       <c r="D50">
-        <v>1507.262257852185</v>
+        <v>1531.541072662297</v>
       </c>
       <c r="E50">
         <v>133.6759999999999</v>
@@ -5387,37 +5387,37 @@
         <v>448.025</v>
       </c>
       <c r="M50">
-        <v>51.0391026352591</v>
+        <v>49.9582386352591</v>
       </c>
       <c r="N50">
-        <v>396.9858973647409</v>
+        <v>398.0667613647409</v>
       </c>
       <c r="O50">
-        <v>79.39717947294818</v>
+        <v>79.61335227294819</v>
       </c>
       <c r="P50">
-        <v>317.5887178917927</v>
+        <v>318.4534090917927</v>
       </c>
       <c r="Q50">
-        <v>542.6887178917927</v>
+        <v>543.5534090917927</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1056857757714571</v>
+        <v>0.1056695729939068</v>
       </c>
       <c r="T50">
         <v>0.9261632534098694</v>
       </c>
       <c r="U50">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V50">
         <v>0.2</v>
       </c>
       <c r="W50">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>8.778073611554703</v>
+        <v>8.967990310286815</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5436,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.08219545154545864</v>
+        <v>0.08159904474149603</v>
       </c>
       <c r="C51">
-        <v>828.1279610079156</v>
+        <v>852.864970551086</v>
       </c>
       <c r="D51">
-        <v>1505.615961007916</v>
+        <v>1530.352970551086</v>
       </c>
       <c r="E51">
         <v>148.6879999999999</v>
@@ -5469,37 +5469,37 @@
         <v>448.025</v>
       </c>
       <c r="M51">
-        <v>52.10241727349366</v>
+        <v>50.99903527349366</v>
       </c>
       <c r="N51">
-        <v>395.9225827265063</v>
+        <v>397.0259647265063</v>
       </c>
       <c r="O51">
-        <v>79.18451654530128</v>
+        <v>79.40519294530128</v>
       </c>
       <c r="P51">
-        <v>316.7380661812051</v>
+        <v>317.6207717812051</v>
       </c>
       <c r="Q51">
-        <v>541.838066181205</v>
+        <v>542.720771781205</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1067249181586072</v>
+        <v>0.1067084342292687</v>
       </c>
       <c r="T51">
         <v>0.9422341063234537</v>
       </c>
       <c r="U51">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V51">
         <v>0.2</v>
       </c>
       <c r="W51">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>8.598929252135219</v>
+        <v>8.784970099872799</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5518,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.08223520422732464</v>
+        <v>0.08162681606372559</v>
       </c>
       <c r="C52">
-        <v>811.4732565527163</v>
+        <v>836.6667103655718</v>
       </c>
       <c r="D52">
-        <v>1503.973256552716</v>
+        <v>1529.166710365572</v>
       </c>
       <c r="E52">
         <v>163.6999999999999</v>
@@ -5551,37 +5551,37 @@
         <v>448.025</v>
       </c>
       <c r="M52">
-        <v>53.16573191172823</v>
+        <v>52.03983191172823</v>
       </c>
       <c r="N52">
-        <v>394.8592680882717</v>
+        <v>395.9851680882717</v>
       </c>
       <c r="O52">
-        <v>78.97185361765435</v>
+        <v>79.19703361765436</v>
       </c>
       <c r="P52">
-        <v>315.8874144706174</v>
+        <v>316.7881344706174</v>
       </c>
       <c r="Q52">
-        <v>540.9874144706174</v>
+        <v>541.8881344706174</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1078056262412432</v>
+        <v>0.1077888499140451</v>
       </c>
       <c r="T52">
         <v>0.9589477933535815</v>
       </c>
       <c r="U52">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V52">
         <v>0.2</v>
       </c>
       <c r="W52">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>8.426950667092514</v>
+        <v>8.609270697875342</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5600,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.08227495690919066</v>
+        <v>0.08165458738595516</v>
       </c>
       <c r="C53">
-        <v>794.822132740957</v>
+        <v>820.4702878257398</v>
       </c>
       <c r="D53">
-        <v>1502.334132740957</v>
+        <v>1527.98228782574</v>
       </c>
       <c r="E53">
         <v>178.712</v>
@@ -5633,37 +5633,37 @@
         <v>448.025</v>
       </c>
       <c r="M53">
-        <v>54.2290465499628</v>
+        <v>53.0806285499628</v>
       </c>
       <c r="N53">
-        <v>393.7959534500372</v>
+        <v>394.9443714500372</v>
       </c>
       <c r="O53">
-        <v>78.75919069000744</v>
+        <v>78.98887429000744</v>
       </c>
       <c r="P53">
-        <v>315.0367627600298</v>
+        <v>315.9554971600297</v>
       </c>
       <c r="Q53">
-        <v>540.1367627600298</v>
+        <v>541.0554971600297</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1089304448578644</v>
+        <v>0.1089133641982001</v>
       </c>
       <c r="T53">
         <v>0.9763436716910615</v>
       </c>
       <c r="U53">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V53">
         <v>0.2</v>
       </c>
       <c r="W53">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>8.261716340286778</v>
+        <v>8.440461468505237</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5682,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.08231470959105666</v>
+        <v>0.08168235870818472</v>
       </c>
       <c r="C54">
-        <v>778.1745778781598</v>
+        <v>804.2756986648277</v>
       </c>
       <c r="D54">
-        <v>1500.69857787816</v>
+        <v>1526.799698664828</v>
       </c>
       <c r="E54">
         <v>193.7239999999999</v>
@@ -5715,37 +5715,37 @@
         <v>448.025</v>
       </c>
       <c r="M54">
-        <v>55.29236118819736</v>
+        <v>54.12142518819736</v>
       </c>
       <c r="N54">
-        <v>392.7326388118026</v>
+        <v>393.9035748118026</v>
       </c>
       <c r="O54">
-        <v>78.54652776236054</v>
+        <v>78.78071496236053</v>
       </c>
       <c r="P54">
-        <v>314.1861110494421</v>
+        <v>315.1228598494421</v>
       </c>
       <c r="Q54">
-        <v>539.2861110494421</v>
+        <v>540.2228598494421</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1101021309168448</v>
+        <v>0.1100847332441949</v>
       </c>
       <c r="T54">
         <v>0.994464378292603</v>
       </c>
       <c r="U54">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V54">
         <v>0.2</v>
       </c>
       <c r="W54">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>8.10283717989665</v>
+        <v>8.278144901803213</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.08235446227292267</v>
+        <v>0.08171013003041429</v>
       </c>
       <c r="C55">
-        <v>761.5305803207136</v>
+        <v>788.0829386292687</v>
       </c>
       <c r="D55">
-        <v>1499.066580320714</v>
+        <v>1525.618938629269</v>
       </c>
       <c r="E55">
         <v>208.736</v>
@@ -5797,37 +5797,37 @@
         <v>448.025</v>
       </c>
       <c r="M55">
-        <v>56.35567582643193</v>
+        <v>55.16222182643193</v>
       </c>
       <c r="N55">
-        <v>391.669324173568</v>
+        <v>392.862778173568</v>
       </c>
       <c r="O55">
-        <v>78.33386483471361</v>
+        <v>78.57255563471361</v>
       </c>
       <c r="P55">
-        <v>313.3354593388544</v>
+        <v>314.2902225388544</v>
       </c>
       <c r="Q55">
-        <v>538.4354593388545</v>
+        <v>539.3902225388545</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1113236759570584</v>
+        <v>0.1113059477815087</v>
       </c>
       <c r="T55">
         <v>1.013356178792083</v>
       </c>
       <c r="U55">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V55">
         <v>0.2</v>
       </c>
       <c r="W55">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.94995345952124</v>
+        <v>8.12195348856164</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5846,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.0823942149547887</v>
+        <v>0.08173790135264385</v>
       </c>
       <c r="C56">
-        <v>744.8901284756034</v>
+        <v>771.8920034786474</v>
       </c>
       <c r="D56">
-        <v>1497.438128475603</v>
+        <v>1524.440003478647</v>
       </c>
       <c r="E56">
         <v>223.7479999999999</v>
@@ -5879,37 +5879,37 @@
         <v>448.025</v>
       </c>
       <c r="M56">
-        <v>57.41899046466649</v>
+        <v>56.20301846466649</v>
       </c>
       <c r="N56">
-        <v>390.6060095353335</v>
+        <v>391.8219815353335</v>
       </c>
       <c r="O56">
-        <v>78.12120190706671</v>
+        <v>78.3643963070667</v>
       </c>
       <c r="P56">
-        <v>312.4848076282668</v>
+        <v>313.4575852282668</v>
       </c>
       <c r="Q56">
-        <v>537.5848076282668</v>
+        <v>538.5575852282668</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1125983316511944</v>
+        <v>0.1125802586030534</v>
       </c>
       <c r="T56">
         <v>1.033069361921974</v>
       </c>
       <c r="U56">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V56">
         <v>0.2</v>
       </c>
       <c r="W56">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>7.802732099159735</v>
+        <v>7.971546942477167</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +5928,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.08243396763665471</v>
+        <v>0.08176567267487342</v>
       </c>
       <c r="C57">
-        <v>728.2532108001354</v>
+        <v>755.7028889856427</v>
       </c>
       <c r="D57">
-        <v>1495.813210800135</v>
+        <v>1523.262888985643</v>
       </c>
       <c r="E57">
         <v>238.76</v>
@@ -5961,37 +5961,37 @@
         <v>448.025</v>
       </c>
       <c r="M57">
-        <v>58.48230510290106</v>
+        <v>57.24381510290106</v>
       </c>
       <c r="N57">
-        <v>389.5426948970989</v>
+        <v>390.7811848970989</v>
       </c>
       <c r="O57">
-        <v>77.90853897941979</v>
+        <v>78.15623697941979</v>
       </c>
       <c r="P57">
-        <v>311.6341559176791</v>
+        <v>312.6249479176792</v>
       </c>
       <c r="Q57">
-        <v>536.7341559176791</v>
+        <v>537.7249479176792</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1139296387095142</v>
+        <v>0.1139112054611113</v>
       </c>
       <c r="T57">
         <v>1.053658686524306</v>
       </c>
       <c r="U57">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V57">
         <v>0.2</v>
       </c>
       <c r="W57">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>7.660864242811376</v>
+        <v>7.826609725341219</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6010,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08314572031852072</v>
+        <v>0.08179344399710299</v>
       </c>
       <c r="C58">
-        <v>684.7332839138087</v>
+        <v>739.5155909359821</v>
       </c>
       <c r="D58">
-        <v>1467.305283913809</v>
+        <v>1522.087590935982</v>
       </c>
       <c r="E58">
         <v>253.772</v>
@@ -6043,45 +6043,45 @@
         <v>448.025</v>
       </c>
       <c r="M58">
-        <v>60.80662774113563</v>
+        <v>58.28461174113563</v>
       </c>
       <c r="N58">
-        <v>387.2183722588643</v>
+        <v>389.7403882588644</v>
       </c>
       <c r="O58">
-        <v>77.44367445177288</v>
+        <v>77.94807765177288</v>
       </c>
       <c r="P58">
-        <v>309.7746978070915</v>
+        <v>311.7923106070915</v>
       </c>
       <c r="Q58">
-        <v>534.8746978070915</v>
+        <v>536.8923106070915</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1153214597250303</v>
+        <v>0.1153026499036263</v>
       </c>
       <c r="T58">
         <v>1.075183889517652</v>
       </c>
       <c r="U58">
-        <v>0.07233097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V58">
         <v>0.2</v>
       </c>
       <c r="W58">
-        <v>0.05786478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y58">
-        <v>7.368029056097638</v>
+        <v>7.686848837388697</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6092,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08319747300038674</v>
+        <v>0.08218601531933256</v>
       </c>
       <c r="C59">
-        <v>667.6907460868827</v>
+        <v>708.0816790316719</v>
       </c>
       <c r="D59">
-        <v>1465.274746086883</v>
+        <v>1505.665679031672</v>
       </c>
       <c r="E59">
         <v>268.784</v>
@@ -6125,37 +6125,37 @@
         <v>448.025</v>
       </c>
       <c r="M59">
-        <v>61.89246037937019</v>
+        <v>60.00995557937019</v>
       </c>
       <c r="N59">
-        <v>386.1325396206298</v>
+        <v>388.0150444206298</v>
       </c>
       <c r="O59">
-        <v>77.22650792412597</v>
+        <v>77.60300888412597</v>
       </c>
       <c r="P59">
-        <v>308.9060316965039</v>
+        <v>310.4120355365038</v>
       </c>
       <c r="Q59">
-        <v>534.0060316965039</v>
+        <v>535.5120355365038</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1167780166017332</v>
+        <v>0.1167588126923049</v>
       </c>
       <c r="T59">
         <v>1.097710264743247</v>
       </c>
       <c r="U59">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V59">
         <v>0.2</v>
       </c>
       <c r="W59">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>7.238765388446803</v>
+        <v>7.465844553199751</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6174,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.08324922568225275</v>
+        <v>0.08222018664156211</v>
       </c>
       <c r="C60">
-        <v>650.6538204335744</v>
+        <v>691.6569848136406</v>
       </c>
       <c r="D60">
-        <v>1463.249820433574</v>
+        <v>1504.252984813641</v>
       </c>
       <c r="E60">
         <v>283.7959999999998</v>
@@ -6207,37 +6207,37 @@
         <v>448.025</v>
       </c>
       <c r="M60">
-        <v>62.97829301760474</v>
+        <v>61.06276181760474</v>
       </c>
       <c r="N60">
-        <v>385.0467069823952</v>
+        <v>386.9622381823953</v>
       </c>
       <c r="O60">
-        <v>77.00934139647904</v>
+        <v>77.39244763647906</v>
       </c>
       <c r="P60">
-        <v>308.0373655859162</v>
+        <v>309.5697905459162</v>
       </c>
       <c r="Q60">
-        <v>533.1373655859162</v>
+        <v>534.6697905459162</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1183039333297077</v>
+        <v>0.1182843165661586</v>
       </c>
       <c r="T60">
         <v>1.121309324503394</v>
       </c>
       <c r="U60">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V60">
         <v>0.2</v>
       </c>
       <c r="W60">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>7.113959088645997</v>
+        <v>7.337123095385964</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6256,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.08330097836411876</v>
+        <v>0.0822543579637917</v>
       </c>
       <c r="C61">
-        <v>633.6224837188859</v>
+        <v>675.2349390377708</v>
       </c>
       <c r="D61">
-        <v>1461.230483718886</v>
+        <v>1502.842939037771</v>
       </c>
       <c r="E61">
         <v>298.8079999999999</v>
@@ -6289,37 +6289,37 @@
         <v>448.025</v>
       </c>
       <c r="M61">
-        <v>64.06412565583931</v>
+        <v>62.11556805583932</v>
       </c>
       <c r="N61">
-        <v>383.9608743441607</v>
+        <v>385.9094319441606</v>
       </c>
       <c r="O61">
-        <v>76.79217486883213</v>
+        <v>77.18188638883214</v>
       </c>
       <c r="P61">
-        <v>307.1686994753285</v>
+        <v>308.7275455553285</v>
       </c>
       <c r="Q61">
-        <v>532.2686994753285</v>
+        <v>533.8275455553285</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1199042850200224</v>
+        <v>0.1198842352631271</v>
       </c>
       <c r="T61">
         <v>1.146059557910378</v>
       </c>
       <c r="U61">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V61">
         <v>0.2</v>
       </c>
       <c r="W61">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.993383510872336</v>
+        <v>7.212765076820099</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6338,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.08335273104598477</v>
+        <v>0.08228852928602126</v>
       </c>
       <c r="C62">
-        <v>616.5967128359049</v>
+        <v>658.8155342633078</v>
       </c>
       <c r="D62">
-        <v>1459.216712835905</v>
+        <v>1501.435534263308</v>
       </c>
       <c r="E62">
         <v>313.8199999999999</v>
@@ -6371,37 +6371,37 @@
         <v>448.025</v>
       </c>
       <c r="M62">
-        <v>65.14995829407388</v>
+        <v>63.16837429407389</v>
       </c>
       <c r="N62">
-        <v>382.8750417059261</v>
+        <v>384.8566257059261</v>
       </c>
       <c r="O62">
-        <v>76.57500834118522</v>
+        <v>76.97132514118522</v>
       </c>
       <c r="P62">
-        <v>306.3000333647409</v>
+        <v>307.8853005647409</v>
       </c>
       <c r="Q62">
-        <v>531.4000333647409</v>
+        <v>532.9853005647409</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1215846542948528</v>
+        <v>0.121564149894944</v>
       </c>
       <c r="T62">
         <v>1.172047302987711</v>
       </c>
       <c r="U62">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V62">
         <v>0.2</v>
       </c>
       <c r="W62">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>6.876827119024463</v>
+        <v>7.092552325539764</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6420,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.08340448372785078</v>
+        <v>0.08232270060825082</v>
       </c>
       <c r="C63">
-        <v>599.5764848049208</v>
+        <v>642.3987630773389</v>
       </c>
       <c r="D63">
-        <v>1457.208484804921</v>
+        <v>1500.030763077339</v>
       </c>
       <c r="E63">
         <v>328.8319999999999</v>
@@ -6453,37 +6453,37 @@
         <v>448.025</v>
       </c>
       <c r="M63">
-        <v>66.23579093230845</v>
+        <v>64.22118053230845</v>
       </c>
       <c r="N63">
-        <v>381.7892090676916</v>
+        <v>383.8038194676915</v>
       </c>
       <c r="O63">
-        <v>76.35784181353831</v>
+        <v>76.76076389353831</v>
       </c>
       <c r="P63">
-        <v>305.4313672541533</v>
+        <v>307.0430555741532</v>
       </c>
       <c r="Q63">
-        <v>530.5313672541533</v>
+        <v>532.1430555741533</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1233511963530079</v>
+        <v>0.1233302139950593</v>
       </c>
       <c r="T63">
         <v>1.199367752940804</v>
       </c>
       <c r="U63">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V63">
         <v>0.2</v>
       </c>
       <c r="W63">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>6.764092248220783</v>
+        <v>6.976280975940751</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6502,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.08345623640971681</v>
+        <v>0.08235687193048039</v>
       </c>
       <c r="C64">
-        <v>582.5617767725503</v>
+        <v>625.9846180946709</v>
       </c>
       <c r="D64">
-        <v>1455.20577677255</v>
+        <v>1498.628618094671</v>
       </c>
       <c r="E64">
         <v>343.8439999999999</v>
@@ -6535,37 +6535,37 @@
         <v>448.025</v>
       </c>
       <c r="M64">
-        <v>67.32162357054301</v>
+        <v>65.27398677054302</v>
       </c>
       <c r="N64">
-        <v>380.703376429457</v>
+        <v>382.7510132294569</v>
       </c>
       <c r="O64">
-        <v>76.14067528589139</v>
+        <v>76.55020264589139</v>
       </c>
       <c r="P64">
-        <v>304.5627011435656</v>
+        <v>306.2008105835656</v>
       </c>
       <c r="Q64">
-        <v>529.6627011435655</v>
+        <v>531.3008105835656</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1252107143089606</v>
+        <v>0.1251892288372859</v>
       </c>
       <c r="T64">
         <v>1.228126121312482</v>
       </c>
       <c r="U64">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V64">
         <v>0.2</v>
       </c>
       <c r="W64">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>6.654993986152705</v>
+        <v>6.863760315038481</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6584,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.08350798909158282</v>
+        <v>0.08239104325270996</v>
       </c>
       <c r="C65">
-        <v>565.552566010874</v>
+        <v>609.5730919576949</v>
       </c>
       <c r="D65">
-        <v>1453.208566010874</v>
+        <v>1497.229091957695</v>
       </c>
       <c r="E65">
         <v>358.8559999999999</v>
@@ -6617,37 +6617,37 @@
         <v>448.025</v>
       </c>
       <c r="M65">
-        <v>68.40745620877757</v>
+        <v>66.32679300877757</v>
       </c>
       <c r="N65">
-        <v>379.6175437912224</v>
+        <v>381.6982069912224</v>
       </c>
       <c r="O65">
-        <v>75.92350875824448</v>
+        <v>76.33964139824448</v>
       </c>
       <c r="P65">
-        <v>303.6940350329779</v>
+        <v>305.3585655929779</v>
       </c>
       <c r="Q65">
-        <v>528.7940350329779</v>
+        <v>530.4585655929779</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1271707467490189</v>
+        <v>0.1271487309682814</v>
       </c>
       <c r="T65">
         <v>1.258438996082628</v>
       </c>
       <c r="U65">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V65">
         <v>0.2</v>
       </c>
       <c r="W65">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>6.549359160975678</v>
+        <v>6.754811738609299</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.08355974177344883</v>
+        <v>0.08242521457493951</v>
       </c>
       <c r="C66">
-        <v>548.548829916571</v>
+        <v>593.164177336265</v>
       </c>
       <c r="D66">
-        <v>1451.216829916571</v>
+        <v>1495.832177336265</v>
       </c>
       <c r="E66">
         <v>373.8679999999999</v>
@@ -6699,37 +6699,37 @@
         <v>448.025</v>
       </c>
       <c r="M66">
-        <v>69.49328884701214</v>
+        <v>67.37959924701215</v>
       </c>
       <c r="N66">
-        <v>378.5317111529878</v>
+        <v>380.6454007529878</v>
       </c>
       <c r="O66">
-        <v>75.70634223059757</v>
+        <v>76.12908015059757</v>
       </c>
       <c r="P66">
-        <v>302.8253689223903</v>
+        <v>304.5163206023902</v>
       </c>
       <c r="Q66">
-        <v>527.9253689223904</v>
+        <v>529.6163206023903</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1292396698801915</v>
+        <v>0.1292170943287768</v>
       </c>
       <c r="T66">
         <v>1.290435919451116</v>
       </c>
       <c r="U66">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V66">
         <v>0.2</v>
       </c>
       <c r="W66">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>6.447025424085433</v>
+        <v>6.649267805193528</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6748,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.08361149445531484</v>
+        <v>0.08245938589716909</v>
       </c>
       <c r="C67">
-        <v>531.550546010072</v>
+        <v>576.7578669275612</v>
       </c>
       <c r="D67">
-        <v>1449.230546010072</v>
+        <v>1494.437866927561</v>
       </c>
       <c r="E67">
         <v>388.8799999999999</v>
@@ -6781,37 +6781,37 @@
         <v>448.025</v>
       </c>
       <c r="M67">
-        <v>70.5791214852467</v>
+        <v>68.4324054852467</v>
       </c>
       <c r="N67">
-        <v>377.4458785147533</v>
+        <v>379.5925945147533</v>
       </c>
       <c r="O67">
-        <v>75.48917570295066</v>
+        <v>75.91851890295065</v>
       </c>
       <c r="P67">
-        <v>301.9567028118026</v>
+        <v>303.6740756118026</v>
       </c>
       <c r="Q67">
-        <v>527.0567028118027</v>
+        <v>528.7740756118026</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1314268171902883</v>
+        <v>0.1314036498813004</v>
       </c>
       <c r="T67">
         <v>1.32426123844066</v>
       </c>
       <c r="U67">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V67">
         <v>0.2</v>
       </c>
       <c r="W67">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>6.347840417561043</v>
+        <v>6.546971377421321</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6830,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.08366324713718085</v>
+        <v>0.08249355721939866</v>
       </c>
       <c r="C68">
-        <v>514.5576919347091</v>
+        <v>560.354153455969</v>
       </c>
       <c r="D68">
-        <v>1447.249691934709</v>
+        <v>1493.046153455969</v>
       </c>
       <c r="E68">
         <v>403.8919999999999</v>
@@ -6863,37 +6863,37 @@
         <v>448.025</v>
       </c>
       <c r="M68">
-        <v>71.66495412348127</v>
+        <v>69.48521172348127</v>
       </c>
       <c r="N68">
-        <v>376.3600458765187</v>
+        <v>378.5397882765187</v>
       </c>
       <c r="O68">
-        <v>75.27200917530375</v>
+        <v>75.70795765530374</v>
       </c>
       <c r="P68">
-        <v>301.0880367012149</v>
+        <v>302.831830621215</v>
       </c>
       <c r="Q68">
-        <v>526.188036701215</v>
+        <v>527.931830621215</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1337426202245084</v>
+        <v>0.1337188263486784</v>
       </c>
       <c r="T68">
         <v>1.360076282076648</v>
       </c>
       <c r="U68">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V68">
         <v>0.2</v>
       </c>
       <c r="W68">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>6.251661017294966</v>
+        <v>6.447774841399786</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +6912,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.08371499981904687</v>
+        <v>0.08252772854162822</v>
       </c>
       <c r="C69">
-        <v>497.5702454558783</v>
+        <v>543.9530296729525</v>
       </c>
       <c r="D69">
-        <v>1445.274245455878</v>
+        <v>1491.657029672953</v>
       </c>
       <c r="E69">
         <v>418.904</v>
@@ -6945,37 +6945,37 @@
         <v>448.025</v>
       </c>
       <c r="M69">
-        <v>72.75078676171584</v>
+        <v>70.53801796171584</v>
       </c>
       <c r="N69">
-        <v>375.2742132382841</v>
+        <v>377.4869820382842</v>
       </c>
       <c r="O69">
-        <v>75.05484264765683</v>
+        <v>75.49739640765684</v>
       </c>
       <c r="P69">
-        <v>300.2193705906273</v>
+        <v>301.9895856306273</v>
       </c>
       <c r="Q69">
-        <v>525.3193705906274</v>
+        <v>527.0895856306274</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1361987749577721</v>
+        <v>0.136174316541352</v>
       </c>
       <c r="T69">
         <v>1.398061934417848</v>
       </c>
       <c r="U69">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V69">
         <v>0.2</v>
       </c>
       <c r="W69">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>6.158352643902503</v>
+        <v>6.35153939600576</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +6994,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.08452835250091287</v>
+        <v>0.08256189986385779</v>
       </c>
       <c r="C70">
-        <v>452.2053487364611</v>
+        <v>527.554488356924</v>
       </c>
       <c r="D70">
-        <v>1414.921348736461</v>
+        <v>1490.270488356924</v>
       </c>
       <c r="E70">
         <v>433.9159999999999</v>
@@ -7027,45 +7027,45 @@
         <v>448.025</v>
       </c>
       <c r="M70">
-        <v>75.2657617999504</v>
+        <v>71.5908241999504</v>
       </c>
       <c r="N70">
-        <v>372.7592382000496</v>
+        <v>376.4341758000496</v>
       </c>
       <c r="O70">
-        <v>74.55184764000992</v>
+        <v>75.28683516000991</v>
       </c>
       <c r="P70">
-        <v>298.2073905600397</v>
+        <v>301.1473406400397</v>
       </c>
       <c r="Q70">
-        <v>523.3073905600397</v>
+        <v>526.2473406400397</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1388084393618648</v>
+        <v>0.1387832748710677</v>
       </c>
       <c r="T70">
         <v>1.438421690030372</v>
       </c>
       <c r="U70">
-        <v>0.07373097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V70">
         <v>0.2</v>
       </c>
       <c r="W70">
-        <v>0.05898478221340606</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y70">
-        <v>5.952573777048985</v>
+        <v>6.258134404888026</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7076,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08459130518277888</v>
+        <v>0.08259607118608735</v>
       </c>
       <c r="C71">
-        <v>434.8971358837937</v>
+        <v>511.1585223131221</v>
       </c>
       <c r="D71">
-        <v>1412.625135883794</v>
+        <v>1488.886522313122</v>
       </c>
       <c r="E71">
         <v>448.928</v>
@@ -7109,45 +7109,45 @@
         <v>448.025</v>
       </c>
       <c r="M71">
-        <v>76.37261123818496</v>
+        <v>72.64363043818497</v>
       </c>
       <c r="N71">
-        <v>371.652388761815</v>
+        <v>375.381369561815</v>
       </c>
       <c r="O71">
-        <v>74.33047775236301</v>
+        <v>75.07627391236301</v>
       </c>
       <c r="P71">
-        <v>297.321911009452</v>
+        <v>300.305095649452</v>
       </c>
       <c r="Q71">
-        <v>522.4219110094521</v>
+        <v>525.4050956494521</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1415864692113829</v>
+        <v>0.1415605530930231</v>
       </c>
       <c r="T71">
         <v>1.481385300843705</v>
       </c>
       <c r="U71">
-        <v>0.07373097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V71">
         <v>0.2</v>
       </c>
       <c r="W71">
-        <v>0.05898478221340606</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y71">
-        <v>5.866304591874362</v>
+        <v>6.167436804817186</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7158,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08465425786464489</v>
+        <v>0.08319024250831691</v>
       </c>
       <c r="C72">
-        <v>417.5963637990194</v>
+        <v>472.486507981421</v>
       </c>
       <c r="D72">
-        <v>1410.336363799019</v>
+        <v>1465.226507981421</v>
       </c>
       <c r="E72">
         <v>463.9399999999999</v>
@@ -7191,37 +7191,37 @@
         <v>448.025</v>
       </c>
       <c r="M72">
-        <v>77.47946067641952</v>
+        <v>74.74727667641953</v>
       </c>
       <c r="N72">
-        <v>370.5455393235804</v>
+        <v>373.2777233235805</v>
       </c>
       <c r="O72">
-        <v>74.10910786471609</v>
+        <v>74.65554466471609</v>
       </c>
       <c r="P72">
-        <v>296.4364314588644</v>
+        <v>298.6221786588644</v>
       </c>
       <c r="Q72">
-        <v>521.5364314588644</v>
+        <v>523.7221786588643</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1445497010508689</v>
+        <v>0.1445229831964422</v>
       </c>
       <c r="T72">
         <v>1.527213152377926</v>
       </c>
       <c r="U72">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V72">
         <v>0.2</v>
       </c>
       <c r="W72">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.782500240561872</v>
+        <v>5.993863855930127</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7240,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.08471721054651091</v>
+        <v>0.08323241383054648</v>
       </c>
       <c r="C73">
-        <v>400.3029963734637</v>
+        <v>455.8237851750557</v>
       </c>
       <c r="D73">
-        <v>1408.054996373464</v>
+        <v>1463.575785175056</v>
       </c>
       <c r="E73">
         <v>478.9519999999999</v>
@@ -7273,37 +7273,37 @@
         <v>448.025</v>
       </c>
       <c r="M73">
-        <v>78.58631011465408</v>
+        <v>75.8150949146541</v>
       </c>
       <c r="N73">
-        <v>369.4386898853459</v>
+        <v>372.2099050853459</v>
       </c>
       <c r="O73">
-        <v>73.88773797706918</v>
+        <v>74.44198101706918</v>
       </c>
       <c r="P73">
-        <v>295.5509519082767</v>
+        <v>297.7679240682767</v>
       </c>
       <c r="Q73">
-        <v>520.6509519082767</v>
+        <v>522.8679240682768</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1477172937068711</v>
+        <v>0.1476897188242351</v>
       </c>
       <c r="T73">
         <v>1.576201545397266</v>
       </c>
       <c r="U73">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V73">
         <v>0.2</v>
       </c>
       <c r="W73">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.701056575201846</v>
+        <v>5.90944323824097</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7322,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.08478016322837692</v>
+        <v>0.08327458515277605</v>
       </c>
       <c r="C74">
-        <v>383.016997731713</v>
+        <v>439.1647775886504</v>
       </c>
       <c r="D74">
-        <v>1405.780997731713</v>
+        <v>1461.92877758865</v>
       </c>
       <c r="E74">
         <v>493.9639999999998</v>
@@ -7355,37 +7355,37 @@
         <v>448.025</v>
       </c>
       <c r="M74">
-        <v>79.69315955288864</v>
+        <v>76.88291315288866</v>
       </c>
       <c r="N74">
-        <v>368.3318404471113</v>
+        <v>371.1420868471113</v>
       </c>
       <c r="O74">
-        <v>73.66636808942228</v>
+        <v>74.22841736942227</v>
       </c>
       <c r="P74">
-        <v>294.6654723576891</v>
+        <v>296.913669477689</v>
       </c>
       <c r="Q74">
-        <v>519.7654723576891</v>
+        <v>522.0136694776891</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1511111429811591</v>
+        <v>0.1510826498540131</v>
       </c>
       <c r="T74">
         <v>1.628689109346559</v>
       </c>
       <c r="U74">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V74">
         <v>0.2</v>
       </c>
       <c r="W74">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.621875233879599</v>
+        <v>5.827367637709846</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7404,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.08484311591024293</v>
+        <v>0.08331675647500561</v>
       </c>
       <c r="C75">
-        <v>365.7383322297346</v>
+        <v>422.5094726937448</v>
       </c>
       <c r="D75">
-        <v>1403.514332229734</v>
+        <v>1460.285472693745</v>
       </c>
       <c r="E75">
         <v>508.9759999999998</v>
@@ -7437,37 +7437,37 @@
         <v>448.025</v>
       </c>
       <c r="M75">
-        <v>80.80000899112321</v>
+        <v>77.95073139112321</v>
       </c>
       <c r="N75">
-        <v>367.2249910088768</v>
+        <v>370.0742686088768</v>
       </c>
       <c r="O75">
-        <v>73.44499820177536</v>
+        <v>74.01485372177535</v>
       </c>
       <c r="P75">
-        <v>293.7799928071014</v>
+        <v>296.0594148871014</v>
       </c>
       <c r="Q75">
-        <v>518.8799928071014</v>
+        <v>521.1594148871014</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1547563884979871</v>
+        <v>0.1547269091082192</v>
       </c>
       <c r="T75">
         <v>1.685064640995799</v>
       </c>
       <c r="U75">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V75">
         <v>0.2</v>
       </c>
       <c r="W75">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.544863244374398</v>
+        <v>5.747540683768615</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.08490606859210895</v>
+        <v>0.08335892779723518</v>
       </c>
       <c r="C76">
-        <v>348.4669644530136</v>
+        <v>405.8578580181454</v>
       </c>
       <c r="D76">
-        <v>1401.254964453014</v>
+        <v>1458.645858018145</v>
       </c>
       <c r="E76">
         <v>523.9879999999999</v>
@@ -7519,37 +7519,37 @@
         <v>448.025</v>
       </c>
       <c r="M76">
-        <v>81.90685842935778</v>
+        <v>79.01854962935779</v>
       </c>
       <c r="N76">
-        <v>366.1181415706422</v>
+        <v>369.0064503706422</v>
       </c>
       <c r="O76">
-        <v>73.22362831412845</v>
+        <v>73.80129007412845</v>
       </c>
       <c r="P76">
-        <v>292.8945132565137</v>
+        <v>295.2051602965138</v>
       </c>
       <c r="Q76">
-        <v>517.9945132565138</v>
+        <v>520.3051602965138</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1586820375161095</v>
+        <v>0.1586514959973642</v>
       </c>
       <c r="T76">
         <v>1.745776752002674</v>
       </c>
       <c r="U76">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V76">
         <v>0.2</v>
       </c>
       <c r="W76">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.46993265999096</v>
+        <v>5.669871215069039</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.08496902127397496</v>
+        <v>0.08340109911946475</v>
       </c>
       <c r="C77">
-        <v>331.2028592147092</v>
+        <v>389.209921145612</v>
       </c>
       <c r="D77">
-        <v>1399.002859214709</v>
+        <v>1457.009921145612</v>
       </c>
       <c r="E77">
         <v>538.9999999999999</v>
@@ -7601,37 +7601,37 @@
         <v>448.025</v>
       </c>
       <c r="M77">
-        <v>83.01370786759234</v>
+        <v>80.08636786759236</v>
       </c>
       <c r="N77">
-        <v>365.0112921324076</v>
+        <v>367.9386321324076</v>
       </c>
       <c r="O77">
-        <v>73.00225842648153</v>
+        <v>73.58772642648152</v>
       </c>
       <c r="P77">
-        <v>292.0090337059261</v>
+        <v>294.3509057059261</v>
       </c>
       <c r="Q77">
-        <v>517.1090337059261</v>
+        <v>519.4509057059261</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1629217384556817</v>
+        <v>0.1628900498376408</v>
       </c>
       <c r="T77">
         <v>1.811345831890099</v>
       </c>
       <c r="U77">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V77">
         <v>0.2</v>
       </c>
       <c r="W77">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.397000224524414</v>
+        <v>5.594272932201451</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.08503197395584097</v>
+        <v>0.08344327044169431</v>
       </c>
       <c r="C78">
-        <v>313.9459815538269</v>
+        <v>372.5656497155442</v>
       </c>
       <c r="D78">
-        <v>1396.757981553827</v>
+        <v>1455.377649715544</v>
       </c>
       <c r="E78">
         <v>554.0119999999998</v>
@@ -7683,37 +7683,37 @@
         <v>448.025</v>
       </c>
       <c r="M78">
-        <v>84.12055730582691</v>
+        <v>81.15418610582692</v>
       </c>
       <c r="N78">
-        <v>363.9044426941731</v>
+        <v>366.8708138941731</v>
       </c>
       <c r="O78">
-        <v>72.78088853883462</v>
+        <v>73.37416277883462</v>
       </c>
       <c r="P78">
-        <v>291.1235541553385</v>
+        <v>293.4966511153385</v>
       </c>
       <c r="Q78">
-        <v>516.2235541553384</v>
+        <v>518.5966511153385</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1675147478068849</v>
+        <v>0.1674818164979404</v>
       </c>
       <c r="T78">
         <v>1.882379001768142</v>
       </c>
       <c r="U78">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V78">
         <v>0.2</v>
       </c>
       <c r="W78">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.325987063675409</v>
+        <v>5.520664077830379</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7732,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.08509492663770699</v>
+        <v>0.08348544176392389</v>
       </c>
       <c r="C79">
-        <v>296.6962967334102</v>
+        <v>355.925031422667</v>
       </c>
       <c r="D79">
-        <v>1394.52029673341</v>
+        <v>1453.749031422667</v>
       </c>
       <c r="E79">
         <v>569.024</v>
@@ -7765,37 +7765,37 @@
         <v>448.025</v>
       </c>
       <c r="M79">
-        <v>85.22740674406148</v>
+        <v>82.22200434406149</v>
       </c>
       <c r="N79">
-        <v>362.7975932559385</v>
+        <v>365.8029956559385</v>
       </c>
       <c r="O79">
-        <v>72.5595186511877</v>
+        <v>73.16059913118771</v>
       </c>
       <c r="P79">
-        <v>290.2380746047508</v>
+        <v>292.6423965247508</v>
       </c>
       <c r="Q79">
-        <v>515.3380746047508</v>
+        <v>517.7423965247508</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.172507149275584</v>
+        <v>0.1724728672156574</v>
       </c>
       <c r="T79">
         <v>1.959588969026884</v>
       </c>
       <c r="U79">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V79">
         <v>0.2</v>
       </c>
       <c r="W79">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.256818400510793</v>
+        <v>5.44896714175466</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7814,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.085157879319573</v>
+        <v>0.08352761308615345</v>
       </c>
       <c r="C80">
-        <v>279.4537702387497</v>
+        <v>339.2880540167273</v>
       </c>
       <c r="D80">
-        <v>1392.28977023875</v>
+        <v>1452.124054016727</v>
       </c>
       <c r="E80">
         <v>584.0359999999999</v>
@@ -7847,37 +7847,37 @@
         <v>448.025</v>
       </c>
       <c r="M80">
-        <v>86.33425618229604</v>
+        <v>83.28982258229605</v>
       </c>
       <c r="N80">
-        <v>361.6907438177039</v>
+        <v>364.7351774177039</v>
       </c>
       <c r="O80">
-        <v>72.33814876354079</v>
+        <v>72.94703548354079</v>
       </c>
       <c r="P80">
-        <v>289.3525950541631</v>
+        <v>291.7881419341631</v>
       </c>
       <c r="Q80">
-        <v>514.4525950541631</v>
+        <v>516.8881419341632</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1779534054232558</v>
+        <v>0.1779176498168032</v>
       </c>
       <c r="T80">
         <v>2.04381802421824</v>
       </c>
       <c r="U80">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V80">
         <v>0.2</v>
       </c>
       <c r="W80">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.189423292811936</v>
+        <v>5.379108588655241</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +7896,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.08522083200143901</v>
+        <v>0.08356978440838302</v>
       </c>
       <c r="C81">
-        <v>262.2183677756068</v>
+        <v>322.6547053021804</v>
       </c>
       <c r="D81">
-        <v>1390.066367775607</v>
+        <v>1450.50270530218</v>
       </c>
       <c r="E81">
         <v>599.0479999999999</v>
@@ -7929,37 +7929,37 @@
         <v>448.025</v>
       </c>
       <c r="M81">
-        <v>87.44110562053061</v>
+        <v>84.35764082053062</v>
       </c>
       <c r="N81">
-        <v>360.5838943794694</v>
+        <v>363.6673591794694</v>
       </c>
       <c r="O81">
-        <v>72.11677887589387</v>
+        <v>72.73347183589388</v>
       </c>
       <c r="P81">
-        <v>288.4671155035755</v>
+        <v>290.9338873435755</v>
       </c>
       <c r="Q81">
-        <v>513.5671155035755</v>
+        <v>516.0338873435755</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1839183526326106</v>
+        <v>0.1838809831418677</v>
       </c>
       <c r="T81">
         <v>2.136068894189724</v>
       </c>
       <c r="U81">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V81">
         <v>0.2</v>
       </c>
       <c r="W81">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.123734390371279</v>
+        <v>5.311018606520365</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +7978,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.08528378468330503</v>
+        <v>0.08361195573061259</v>
       </c>
       <c r="C82">
-        <v>244.9900552684569</v>
+        <v>306.0249731378892</v>
       </c>
       <c r="D82">
-        <v>1387.850055268457</v>
+        <v>1448.884973137889</v>
       </c>
       <c r="E82">
         <v>614.0599999999998</v>
@@ -8011,37 +8011,37 @@
         <v>448.025</v>
       </c>
       <c r="M82">
-        <v>88.54795505876517</v>
+        <v>85.42545905876517</v>
       </c>
       <c r="N82">
-        <v>359.4770449412348</v>
+        <v>362.5995409412348</v>
       </c>
       <c r="O82">
-        <v>71.89540898824696</v>
+        <v>72.51990818824696</v>
       </c>
       <c r="P82">
-        <v>287.5816359529878</v>
+        <v>290.0796327529878</v>
       </c>
       <c r="Q82">
-        <v>512.6816359529878</v>
+        <v>515.1796327529878</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1904797945629009</v>
+        <v>0.1904406497994386</v>
       </c>
       <c r="T82">
         <v>2.237544851158357</v>
       </c>
       <c r="U82">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V82">
         <v>0.2</v>
       </c>
       <c r="W82">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.059687710491637</v>
+        <v>5.244630873938861</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8060,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08534673736517104</v>
+        <v>0.08365412705284214</v>
       </c>
       <c r="C83">
-        <v>227.7687988587488</v>
+        <v>289.3988454368209</v>
       </c>
       <c r="D83">
-        <v>1385.640798858749</v>
+        <v>1447.270845436821</v>
       </c>
       <c r="E83">
         <v>629.072</v>
@@ -8093,37 +8093,37 @@
         <v>448.025</v>
       </c>
       <c r="M83">
-        <v>89.65480449699974</v>
+        <v>86.49327729699975</v>
       </c>
       <c r="N83">
-        <v>358.3701955030002</v>
+        <v>361.5317227030002</v>
       </c>
       <c r="O83">
-        <v>71.67403910060004</v>
+        <v>72.30634454060005</v>
       </c>
       <c r="P83">
-        <v>286.6961564024002</v>
+        <v>289.2253781624002</v>
       </c>
       <c r="Q83">
-        <v>511.7961564024002</v>
+        <v>514.3253781624003</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1977319145911165</v>
+        <v>0.1976908076841223</v>
       </c>
       <c r="T83">
         <v>2.3497024878079</v>
       </c>
       <c r="U83">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V83">
         <v>0.2</v>
       </c>
       <c r="W83">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.997222430115198</v>
+        <v>5.179882344630974</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8142,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08540969004703705</v>
+        <v>0.0836962983750717</v>
       </c>
       <c r="C84">
-        <v>210.5545649031806</v>
+        <v>272.7763101657426</v>
       </c>
       <c r="D84">
-        <v>1383.438564903181</v>
+        <v>1445.660310165743</v>
       </c>
       <c r="E84">
         <v>644.0839999999999</v>
@@ -8175,37 +8175,37 @@
         <v>448.025</v>
       </c>
       <c r="M84">
-        <v>90.76165393523431</v>
+        <v>87.56109553523432</v>
       </c>
       <c r="N84">
-        <v>357.2633460647656</v>
+        <v>360.4639044647657</v>
       </c>
       <c r="O84">
-        <v>71.45266921295313</v>
+        <v>72.09278089295314</v>
       </c>
       <c r="P84">
-        <v>285.8106768518125</v>
+        <v>288.3711235718125</v>
       </c>
       <c r="Q84">
-        <v>510.9106768518125</v>
+        <v>513.4711235718125</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2057898257335782</v>
+        <v>0.2057465386671041</v>
       </c>
       <c r="T84">
         <v>2.474322084085168</v>
       </c>
       <c r="U84">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V84">
         <v>0.2</v>
       </c>
       <c r="W84">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.936280693162573</v>
+        <v>5.11671304774523</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8224,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08547264272890306</v>
+        <v>0.08373846969730128</v>
       </c>
       <c r="C85">
-        <v>193.3473199719908</v>
+        <v>256.157355344925</v>
       </c>
       <c r="D85">
-        <v>1381.243319971991</v>
+        <v>1444.053355344925</v>
       </c>
       <c r="E85">
         <v>659.0959999999999</v>
@@ -8257,37 +8257,37 @@
         <v>448.025</v>
       </c>
       <c r="M85">
-        <v>91.86850337346887</v>
+        <v>88.62891377346888</v>
       </c>
       <c r="N85">
-        <v>356.1564966265311</v>
+        <v>359.3960862265311</v>
       </c>
       <c r="O85">
-        <v>71.23129932530622</v>
+        <v>71.87921724530622</v>
       </c>
       <c r="P85">
-        <v>284.9251973012249</v>
+        <v>287.5168689812249</v>
       </c>
       <c r="Q85">
-        <v>510.0251973012249</v>
+        <v>512.6168689812249</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.214795726422212</v>
+        <v>0.2147500027069073</v>
       </c>
       <c r="T85">
         <v>2.613602809336233</v>
       </c>
       <c r="U85">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V85">
         <v>0.2</v>
       </c>
       <c r="W85">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.876807431799168</v>
+        <v>5.055065902591672</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8306,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.08553559541076908</v>
+        <v>0.08378064101953084</v>
       </c>
       <c r="C86">
-        <v>176.1470308472685</v>
+        <v>239.5419690478479</v>
       </c>
       <c r="D86">
-        <v>1379.055030847268</v>
+        <v>1442.449969047848</v>
       </c>
       <c r="E86">
         <v>674.1079999999998</v>
@@ -8339,37 +8339,37 @@
         <v>448.025</v>
       </c>
       <c r="M86">
-        <v>92.97535281170343</v>
+        <v>89.69673201170343</v>
       </c>
       <c r="N86">
-        <v>355.0496471882965</v>
+        <v>358.3282679882965</v>
       </c>
       <c r="O86">
-        <v>71.00992943765931</v>
+        <v>71.66565359765931</v>
       </c>
       <c r="P86">
-        <v>284.0397177506372</v>
+        <v>286.6626143906373</v>
       </c>
       <c r="Q86">
-        <v>509.1397177506373</v>
+        <v>511.7626143906373</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2249273646969249</v>
+        <v>0.2248788997516859</v>
       </c>
       <c r="T86">
         <v>2.77029362524368</v>
       </c>
       <c r="U86">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V86">
         <v>0.2</v>
       </c>
       <c r="W86">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.818750200468227</v>
+        <v>4.99488654660844</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8388,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.08559854809263509</v>
+        <v>0.08382281234176042</v>
       </c>
       <c r="C87">
-        <v>158.9536645212766</v>
+        <v>222.9301394008978</v>
       </c>
       <c r="D87">
-        <v>1376.873664521276</v>
+        <v>1440.850139400898</v>
       </c>
       <c r="E87">
         <v>689.1199999999998</v>
@@ -8421,37 +8421,37 @@
         <v>448.025</v>
       </c>
       <c r="M87">
-        <v>94.08220224993799</v>
+        <v>90.764550249938</v>
       </c>
       <c r="N87">
-        <v>353.942797750062</v>
+        <v>357.260449750062</v>
       </c>
       <c r="O87">
-        <v>70.78855955001239</v>
+        <v>71.45208995001239</v>
       </c>
       <c r="P87">
-        <v>283.1542382000496</v>
+        <v>285.8083598000496</v>
       </c>
       <c r="Q87">
-        <v>508.2542382000496</v>
+        <v>510.9083598000496</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2364098880749329</v>
+        <v>0.236358316402435</v>
       </c>
       <c r="T87">
         <v>2.947876549938787</v>
       </c>
       <c r="U87">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V87">
         <v>0.2</v>
       </c>
       <c r="W87">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.762059021639189</v>
+        <v>4.936123175471869</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8470,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.0856615007745011</v>
+        <v>0.08386498366398998</v>
       </c>
       <c r="C88">
-        <v>141.7671881947917</v>
+        <v>206.3218545830835</v>
       </c>
       <c r="D88">
-        <v>1374.699188194792</v>
+        <v>1439.253854583083</v>
       </c>
       <c r="E88">
         <v>704.1319999999999</v>
@@ -8503,37 +8503,37 @@
         <v>448.025</v>
       </c>
       <c r="M88">
-        <v>95.18905168817257</v>
+        <v>91.83236848817258</v>
       </c>
       <c r="N88">
-        <v>352.8359483118274</v>
+        <v>356.1926315118274</v>
       </c>
       <c r="O88">
-        <v>70.56718966236548</v>
+        <v>71.23852630236549</v>
       </c>
       <c r="P88">
-        <v>282.2687586494619</v>
+        <v>284.9541052094619</v>
       </c>
       <c r="Q88">
-        <v>507.3687586494619</v>
+        <v>510.054105209462</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2495327719355135</v>
+        <v>0.2494776497175768</v>
       </c>
       <c r="T88">
         <v>3.150828463876054</v>
       </c>
       <c r="U88">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V88">
         <v>0.2</v>
       </c>
       <c r="W88">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.706686242317802</v>
+        <v>4.87872639436173</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8552,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.0857244534563671</v>
+        <v>0.08390715498621953</v>
       </c>
       <c r="C89">
-        <v>124.5875692754632</v>
+        <v>189.7171028257374</v>
       </c>
       <c r="D89">
-        <v>1372.531569275463</v>
+        <v>1437.661102825737</v>
       </c>
       <c r="E89">
         <v>719.1439999999999</v>
@@ -8585,37 +8585,37 @@
         <v>448.025</v>
       </c>
       <c r="M89">
-        <v>96.29590112640712</v>
+        <v>92.90018672640714</v>
       </c>
       <c r="N89">
-        <v>351.7290988735929</v>
+        <v>355.1248132735928</v>
       </c>
       <c r="O89">
-        <v>70.34581977471858</v>
+        <v>71.02496265471858</v>
       </c>
       <c r="P89">
-        <v>281.3832790988743</v>
+        <v>284.0998506188743</v>
       </c>
       <c r="Q89">
-        <v>506.4832790988743</v>
+        <v>509.1998506188743</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2646745610054141</v>
+        <v>0.2646153420042789</v>
       </c>
       <c r="T89">
         <v>3.385003749188283</v>
       </c>
       <c r="U89">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V89">
         <v>0.2</v>
       </c>
       <c r="W89">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.652586400452082</v>
+        <v>4.822649079484009</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.08578740613823312</v>
+        <v>0.08394932630844912</v>
       </c>
       <c r="C90">
-        <v>107.4147753761802</v>
+        <v>173.1158724122301</v>
       </c>
       <c r="D90">
-        <v>1370.37077537618</v>
+        <v>1436.07187241223</v>
       </c>
       <c r="E90">
         <v>734.1559999999998</v>
@@ -8667,37 +8667,37 @@
         <v>448.025</v>
       </c>
       <c r="M90">
-        <v>97.40275056464168</v>
+        <v>93.96800496464169</v>
       </c>
       <c r="N90">
-        <v>350.6222494353583</v>
+        <v>354.0569950353583</v>
       </c>
       <c r="O90">
-        <v>70.12444988707166</v>
+        <v>70.81139900707166</v>
       </c>
       <c r="P90">
-        <v>280.4977995482867</v>
+        <v>283.2455960282866</v>
       </c>
       <c r="Q90">
-        <v>505.5977995482867</v>
+        <v>508.3455960282866</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2823399815869649</v>
+        <v>0.2822759830054314</v>
       </c>
       <c r="T90">
         <v>3.658208248719219</v>
       </c>
       <c r="U90">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V90">
         <v>0.2</v>
       </c>
       <c r="W90">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.599716100446944</v>
+        <v>4.767846249035328</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8716,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.08585035882009914</v>
+        <v>0.08399149763067867</v>
       </c>
       <c r="C91">
-        <v>90.24877431346135</v>
+        <v>156.5181516776852</v>
       </c>
       <c r="D91">
-        <v>1368.216774313461</v>
+        <v>1434.486151677685</v>
       </c>
       <c r="E91">
         <v>749.1679999999998</v>
@@ -8749,37 +8749,37 @@
         <v>448.025</v>
       </c>
       <c r="M91">
-        <v>98.50960000287624</v>
+        <v>95.03582320287626</v>
       </c>
       <c r="N91">
-        <v>349.5153999971237</v>
+        <v>352.9891767971237</v>
       </c>
       <c r="O91">
-        <v>69.90307999942475</v>
+        <v>70.59783535942475</v>
       </c>
       <c r="P91">
-        <v>279.612319997699</v>
+        <v>282.391341437699</v>
       </c>
       <c r="Q91">
-        <v>504.712319997699</v>
+        <v>507.491341437699</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3032172968197068</v>
+        <v>0.303147649643157</v>
       </c>
       <c r="T91">
         <v>3.981086293619414</v>
       </c>
       <c r="U91">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V91">
         <v>0.2</v>
       </c>
       <c r="W91">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>4.548033897071136</v>
+        <v>4.714274942866392</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.08778531150196514</v>
+        <v>0.08403366895290824</v>
       </c>
       <c r="C92">
-        <v>12.18056198291879</v>
+        <v>139.9239290086871</v>
       </c>
       <c r="D92">
-        <v>1305.160561982919</v>
+        <v>1432.903929008687</v>
       </c>
       <c r="E92">
         <v>764.1799999999999</v>
@@ -8831,45 +8831,45 @@
         <v>448.025</v>
       </c>
       <c r="M92">
-        <v>103.1292574411108</v>
+        <v>96.10364144111084</v>
       </c>
       <c r="N92">
-        <v>344.8957425588892</v>
+        <v>351.9213585588892</v>
       </c>
       <c r="O92">
-        <v>68.97914851177784</v>
+        <v>70.38427171177783</v>
       </c>
       <c r="P92">
-        <v>275.9165940471113</v>
+        <v>281.5370868471113</v>
       </c>
       <c r="Q92">
-        <v>501.0165940471114</v>
+        <v>506.6370868471113</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.328270075098997</v>
+        <v>0.3281936496084278</v>
       </c>
       <c r="T92">
         <v>4.36853994749965</v>
       </c>
       <c r="U92">
-        <v>0.07633097776675757</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V92">
         <v>0.2</v>
       </c>
       <c r="W92">
-        <v>0.06106478221340605</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y92">
-        <v>4.344305496971435</v>
+        <v>4.661894110167875</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8880,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.08786906418383116</v>
+        <v>0.0840758402751378</v>
       </c>
       <c r="C93">
-        <v>-5.429800957938596</v>
+        <v>123.3331928430052</v>
       </c>
       <c r="D93">
-        <v>1302.562199042061</v>
+        <v>1431.325192843005</v>
       </c>
       <c r="E93">
         <v>779.1919999999999</v>
@@ -8913,45 +8913,45 @@
         <v>448.025</v>
       </c>
       <c r="M93">
-        <v>104.2751380793454</v>
+        <v>97.17145967934539</v>
       </c>
       <c r="N93">
-        <v>343.7498619206546</v>
+        <v>350.8535403206546</v>
       </c>
       <c r="O93">
-        <v>68.74997238413093</v>
+        <v>70.17070806413092</v>
       </c>
       <c r="P93">
-        <v>274.9998895365237</v>
+        <v>280.6828322565237</v>
       </c>
       <c r="Q93">
-        <v>500.0998895365237</v>
+        <v>505.7828322565237</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.3588901374403517</v>
+        <v>0.3588054273437588</v>
       </c>
       <c r="T93">
         <v>4.842094413353271</v>
       </c>
       <c r="U93">
-        <v>0.07633097776675757</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V93">
         <v>0.2</v>
       </c>
       <c r="W93">
-        <v>0.06106478221340605</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y93">
-        <v>4.296565876125595</v>
+        <v>4.610664504561636</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +8962,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.08795281686569717</v>
+        <v>0.08411801159736737</v>
       </c>
       <c r="C94">
-        <v>-23.02983861659959</v>
+        <v>106.7459316693062</v>
       </c>
       <c r="D94">
-        <v>1299.9741613834</v>
+        <v>1429.749931669306</v>
       </c>
       <c r="E94">
         <v>794.2039999999998</v>
@@ -8995,45 +8995,45 @@
         <v>448.025</v>
       </c>
       <c r="M94">
-        <v>105.4210187175799</v>
+        <v>98.23927791757995</v>
       </c>
       <c r="N94">
-        <v>342.60398128242</v>
+        <v>349.78572208242</v>
       </c>
       <c r="O94">
-        <v>68.520796256484</v>
+        <v>69.95714441648401</v>
       </c>
       <c r="P94">
-        <v>274.083185025936</v>
+        <v>279.828577665936</v>
       </c>
       <c r="Q94">
-        <v>499.183185025936</v>
+        <v>504.928577665936</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3971652153670452</v>
+        <v>0.3970701495129225</v>
       </c>
       <c r="T94">
         <v>5.434037495670299</v>
       </c>
       <c r="U94">
-        <v>0.07633097776675757</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V94">
         <v>0.2</v>
       </c>
       <c r="W94">
-        <v>0.06106478221340605</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y94">
-        <v>4.249864073124231</v>
+        <v>4.560548586033792</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9044,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.08803656954756317</v>
+        <v>0.08416018291959694</v>
       </c>
       <c r="C95">
-        <v>-40.61961241638141</v>
+        <v>90.16213402687799</v>
       </c>
       <c r="D95">
-        <v>1297.396387583619</v>
+        <v>1428.178134026878</v>
       </c>
       <c r="E95">
         <v>809.216</v>
@@ -9077,45 +9077,45 @@
         <v>448.025</v>
       </c>
       <c r="M95">
-        <v>106.5668993558145</v>
+        <v>99.30709615581453</v>
       </c>
       <c r="N95">
-        <v>341.4581006441855</v>
+        <v>348.7179038441855</v>
       </c>
       <c r="O95">
-        <v>68.2916201288371</v>
+        <v>69.74358076883709</v>
       </c>
       <c r="P95">
-        <v>273.1664805153484</v>
+        <v>278.9743230753484</v>
       </c>
       <c r="Q95">
-        <v>498.2664805153484</v>
+        <v>504.0743230753484</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.4463760298442224</v>
+        <v>0.4462676494447044</v>
       </c>
       <c r="T95">
         <v>6.195107172935047</v>
       </c>
       <c r="U95">
-        <v>0.07633097776675757</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V95">
         <v>0.2</v>
       </c>
       <c r="W95">
-        <v>0.06106478221340605</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y95">
-        <v>4.204166609972356</v>
+        <v>4.511510429194718</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9126,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08812032222942918</v>
+        <v>0.08608235424182649</v>
       </c>
       <c r="C96">
-        <v>-58.19918329437064</v>
+        <v>7.001111857480055</v>
       </c>
       <c r="D96">
-        <v>1294.828816705629</v>
+        <v>1360.02911185748</v>
       </c>
       <c r="E96">
         <v>824.228</v>
@@ -9159,37 +9159,37 @@
         <v>448.025</v>
       </c>
       <c r="M96">
-        <v>107.7127799940491</v>
+        <v>103.9027343940491</v>
       </c>
       <c r="N96">
-        <v>340.3122200059509</v>
+        <v>344.1222656059509</v>
       </c>
       <c r="O96">
-        <v>68.06244400119019</v>
+        <v>68.82445312119019</v>
       </c>
       <c r="P96">
-        <v>272.2497760047607</v>
+        <v>275.2978124847608</v>
       </c>
       <c r="Q96">
-        <v>497.3497760047608</v>
+        <v>500.3978124847608</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.5119904491471253</v>
+        <v>0.5118643160204137</v>
       </c>
       <c r="T96">
         <v>7.209866742621378</v>
       </c>
       <c r="U96">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V96">
         <v>0.2</v>
       </c>
       <c r="W96">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.159441433270523</v>
+        <v>4.311965441649245</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9208,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.0882040749112952</v>
+        <v>0.08614452556405605</v>
       </c>
       <c r="C97">
-        <v>-75.76861170622374</v>
+        <v>-10.10670676903032</v>
       </c>
       <c r="D97">
-        <v>1292.271388293776</v>
+        <v>1357.93329323097</v>
       </c>
       <c r="E97">
         <v>839.2399999999999</v>
@@ -9241,37 +9241,37 @@
         <v>448.025</v>
       </c>
       <c r="M97">
-        <v>108.8586606322836</v>
+        <v>105.0080826322836</v>
       </c>
       <c r="N97">
-        <v>339.1663393677163</v>
+        <v>343.0169173677164</v>
       </c>
       <c r="O97">
-        <v>67.83326787354326</v>
+        <v>68.60338347354327</v>
       </c>
       <c r="P97">
-        <v>271.3330714941731</v>
+        <v>274.4135338941731</v>
       </c>
       <c r="Q97">
-        <v>496.4330714941731</v>
+        <v>499.5135338941731</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.6038506361711898</v>
+        <v>0.6036996492264068</v>
       </c>
       <c r="T97">
         <v>8.630530140182247</v>
       </c>
       <c r="U97">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V97">
         <v>0.2</v>
       </c>
       <c r="W97">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.115657839236096</v>
+        <v>4.266576331737148</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.08828782759316121</v>
+        <v>0.08620669688628563</v>
       </c>
       <c r="C98">
-        <v>-93.32795763091258</v>
+        <v>-27.20807597872636</v>
       </c>
       <c r="D98">
-        <v>1289.724042369087</v>
+        <v>1355.843924021274</v>
       </c>
       <c r="E98">
         <v>854.2519999999998</v>
@@ -9323,37 +9323,37 @@
         <v>448.025</v>
       </c>
       <c r="M98">
-        <v>110.0045412705182</v>
+        <v>106.1134308705182</v>
       </c>
       <c r="N98">
-        <v>338.0204587294818</v>
+        <v>341.9115691294818</v>
       </c>
       <c r="O98">
-        <v>67.60409174589635</v>
+        <v>68.38231382589636</v>
       </c>
       <c r="P98">
-        <v>270.4163669835854</v>
+        <v>273.5292553035854</v>
       </c>
       <c r="Q98">
-        <v>495.5163669835854</v>
+        <v>498.6292553035855</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.7416409167072845</v>
+        <v>0.7414526490353947</v>
       </c>
       <c r="T98">
         <v>10.76152523652352</v>
       </c>
       <c r="U98">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V98">
         <v>0.2</v>
       </c>
       <c r="W98">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.072786403410721</v>
+        <v>4.222132828281552</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9372,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.08837158027502723</v>
+        <v>0.08626886820851519</v>
       </c>
       <c r="C99">
-        <v>-110.8772805754134</v>
+        <v>-44.30302549584644</v>
       </c>
       <c r="D99">
-        <v>1287.186719424586</v>
+        <v>1353.760974504153</v>
       </c>
       <c r="E99">
         <v>869.2639999999998</v>
@@ -9405,37 +9405,37 @@
         <v>448.025</v>
       </c>
       <c r="M99">
-        <v>111.1504219087527</v>
+        <v>107.2187791087528</v>
       </c>
       <c r="N99">
-        <v>336.8745780912473</v>
+        <v>340.8062208912472</v>
       </c>
       <c r="O99">
-        <v>67.37491561824946</v>
+        <v>68.16124417824945</v>
       </c>
       <c r="P99">
-        <v>269.4996624729978</v>
+        <v>272.6449767129978</v>
       </c>
       <c r="Q99">
-        <v>494.5996624729978</v>
+        <v>497.7449767129978</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.9712913842674444</v>
+        <v>0.9710409820503764</v>
       </c>
       <c r="T99">
         <v>14.31318373042567</v>
       </c>
       <c r="U99">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V99">
         <v>0.2</v>
       </c>
       <c r="W99">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.030798914715765</v>
+        <v>4.178605685721949</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9454,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.09057213295689326</v>
+        <v>0.08633103953074477</v>
       </c>
       <c r="C100">
-        <v>-189.1545753117457</v>
+        <v>-61.39158486225188</v>
       </c>
       <c r="D100">
-        <v>1223.921424688254</v>
+        <v>1351.684415137748</v>
       </c>
       <c r="E100">
         <v>884.2759999999997</v>
@@ -9487,45 +9487,45 @@
         <v>448.025</v>
       </c>
       <c r="M100">
-        <v>116.2684777469873</v>
+        <v>108.3241273469873</v>
       </c>
       <c r="N100">
-        <v>331.7565222530127</v>
+        <v>339.7008726530127</v>
       </c>
       <c r="O100">
-        <v>66.35130445060254</v>
+        <v>67.94017453060253</v>
       </c>
       <c r="P100">
-        <v>265.4052178024102</v>
+        <v>271.7606981224101</v>
       </c>
       <c r="Q100">
-        <v>490.5052178024102</v>
+        <v>496.8606981224102</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.430592319387764</v>
+        <v>1.43021764808034</v>
       </c>
       <c r="T100">
         <v>21.41650071822997</v>
       </c>
       <c r="U100">
-        <v>0.07903097776675758</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V100">
         <v>0.2</v>
       </c>
       <c r="W100">
-        <v>0.06322478221340606</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y100">
-        <v>3.853366008411588</v>
+        <v>4.135966852194174</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.09067748563875927</v>
+        <v>0.08639321085297431</v>
       </c>
       <c r="C101">
-        <v>-207.039806791827</v>
+        <v>-78.47378343882087</v>
       </c>
       <c r="D101">
-        <v>1221.048193208173</v>
+        <v>1349.614216561179</v>
       </c>
       <c r="E101">
         <v>899.2879999999999</v>
@@ -9569,45 +9569,45 @@
         <v>448.025</v>
       </c>
       <c r="M101">
-        <v>117.4548907852219</v>
+        <v>109.4294755852219</v>
       </c>
       <c r="N101">
-        <v>330.5701092147781</v>
+        <v>338.5955244147781</v>
       </c>
       <c r="O101">
-        <v>66.11402184295562</v>
+        <v>67.71910488295562</v>
       </c>
       <c r="P101">
-        <v>264.4560873718225</v>
+        <v>270.8764195318225</v>
       </c>
       <c r="Q101">
-        <v>489.5560873718225</v>
+        <v>495.9764195318225</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.808495124748723</v>
+        <v>2.80774764617023</v>
       </c>
       <c r="T101">
         <v>42.72645168164287</v>
       </c>
       <c r="U101">
-        <v>0.07903097776675758</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V101">
         <v>0.2</v>
       </c>
       <c r="W101">
-        <v>0.06322478221340606</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y101">
-        <v>3.814443119437732</v>
+        <v>4.094189409242717</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/kazakhstan/kazakhstan_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/kazakhstan/kazakhstan_telecom_services.xlsx
@@ -1133,43 +1133,43 @@
         <v>3.3735199138859</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>451.293157533227</v>
       </c>
       <c r="G2">
         <v>1.08987929433612</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0278774373259053</v>
       </c>
       <c r="I2">
         <v>0.390953903543832</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>914.3</v>
       </c>
       <c r="L2">
-        <v>1648.92341695661</v>
+        <v>1633.81112229932</v>
       </c>
       <c r="M2">
         <v>1443.1</v>
       </c>
       <c r="N2">
-        <v>1590.82341695661</v>
+        <v>1590.72312229932</v>
       </c>
       <c r="O2">
         <v>586.9</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>15.012</v>
       </c>
       <c r="Q2">
         <v>0.083763532993583</v>
       </c>
       <c r="R2">
-        <v>0.08023824995224731</v>
+        <v>0.08024042127447691</v>
       </c>
       <c r="S2">
         <v>0.0617047822134061</v>
@@ -1191,13 +1191,13 @@
         <v>0.09792330640809239</v>
       </c>
       <c r="X2">
-        <v>0.08023824995224731</v>
+        <v>0.0805165388407503</v>
       </c>
       <c r="Y2">
         <v>0.806330972935308</v>
       </c>
       <c r="Z2">
-        <v>0.532748774085323</v>
+        <v>0.537053814683992</v>
       </c>
       <c r="AA2">
         <v>586.9</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08023824995224729</v>
+        <v>0.08024042127447686</v>
       </c>
       <c r="C2">
-        <v>1648.923416956605</v>
+        <v>1633.811122299318</v>
       </c>
       <c r="D2">
-        <v>1590.823416956605</v>
+        <v>1590.723122299318</v>
       </c>
       <c r="E2">
-        <v>-586.9</v>
+        <v>-571.888</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>15.012</v>
       </c>
       <c r="G2">
         <v>58.1</v>
@@ -1451,28 +1451,28 @@
         <v>448.025</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.9927582382345648</v>
       </c>
       <c r="N2">
-        <v>448.025</v>
+        <v>447.0322417617654</v>
       </c>
       <c r="O2">
-        <v>89.605</v>
+        <v>89.4064483523531</v>
       </c>
       <c r="P2">
-        <v>358.42</v>
+        <v>357.6257934094123</v>
       </c>
       <c r="Q2">
-        <v>583.52</v>
+        <v>582.7257934094123</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08023824995224729</v>
+        <v>0.0805165388407503</v>
       </c>
       <c r="T2">
-        <v>0.5327487740853231</v>
+        <v>0.5370538146839924</v>
       </c>
       <c r="U2">
         <v>0.06613097776675758</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>451.2931575332266</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08024042127447686</v>
+        <v>0.08024259259670641</v>
       </c>
       <c r="C3">
-        <v>1633.811122299318</v>
+        <v>1618.698840287538</v>
       </c>
       <c r="D3">
-        <v>1590.723122299318</v>
+        <v>1590.622840287538</v>
       </c>
       <c r="E3">
-        <v>-571.888</v>
+        <v>-556.876</v>
       </c>
       <c r="F3">
-        <v>15.012</v>
+        <v>30.024</v>
       </c>
       <c r="G3">
         <v>58.1</v>
@@ -1533,28 +1533,28 @@
         <v>448.025</v>
       </c>
       <c r="M3">
-        <v>0.9927582382345648</v>
+        <v>1.98551647646913</v>
       </c>
       <c r="N3">
-        <v>447.0322417617654</v>
+        <v>446.0394835235309</v>
       </c>
       <c r="O3">
-        <v>89.4064483523531</v>
+        <v>89.20789670470617</v>
       </c>
       <c r="P3">
-        <v>357.6257934094123</v>
+        <v>356.8315868188247</v>
       </c>
       <c r="Q3">
-        <v>582.7257934094123</v>
+        <v>581.9315868188247</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0805165388407503</v>
+        <v>0.08080050709432479</v>
       </c>
       <c r="T3">
-        <v>0.5370538146839924</v>
+        <v>0.541446713254063</v>
       </c>
       <c r="U3">
         <v>0.06613097776675758</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>451.2931575332266</v>
+        <v>225.6465787666133</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08024259259670641</v>
+        <v>0.08024476391893598</v>
       </c>
       <c r="C4">
-        <v>1618.698840287538</v>
+        <v>1603.586570918872</v>
       </c>
       <c r="D4">
-        <v>1590.622840287538</v>
+        <v>1590.522570918873</v>
       </c>
       <c r="E4">
-        <v>-556.876</v>
+        <v>-541.864</v>
       </c>
       <c r="F4">
-        <v>30.024</v>
+        <v>45.03599999999999</v>
       </c>
       <c r="G4">
         <v>58.1</v>
@@ -1615,28 +1615,28 @@
         <v>448.025</v>
       </c>
       <c r="M4">
-        <v>1.98551647646913</v>
+        <v>2.978274714703694</v>
       </c>
       <c r="N4">
-        <v>446.0394835235309</v>
+        <v>445.0467252852963</v>
       </c>
       <c r="O4">
-        <v>89.20789670470617</v>
+        <v>89.00934505705926</v>
       </c>
       <c r="P4">
-        <v>356.8315868188247</v>
+        <v>356.0373802282371</v>
       </c>
       <c r="Q4">
-        <v>581.9315868188247</v>
+        <v>581.1373802282371</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08080050709432479</v>
+        <v>0.08109033036343691</v>
       </c>
       <c r="T4">
-        <v>0.541446713254063</v>
+        <v>0.5459301870523826</v>
       </c>
       <c r="U4">
         <v>0.06613097776675758</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>225.6465787666133</v>
+        <v>150.4310525110756</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08024476391893598</v>
+        <v>0.08024693524116554</v>
       </c>
       <c r="C5">
-        <v>1603.586570918872</v>
+        <v>1588.474314190932</v>
       </c>
       <c r="D5">
-        <v>1590.522570918873</v>
+        <v>1590.422314190932</v>
       </c>
       <c r="E5">
-        <v>-541.864</v>
+        <v>-526.852</v>
       </c>
       <c r="F5">
-        <v>45.03599999999999</v>
+        <v>60.04799999999999</v>
       </c>
       <c r="G5">
         <v>58.1</v>
@@ -1697,28 +1697,28 @@
         <v>448.025</v>
       </c>
       <c r="M5">
-        <v>2.978274714703694</v>
+        <v>3.971032952938259</v>
       </c>
       <c r="N5">
-        <v>445.0467252852963</v>
+        <v>444.0539670470617</v>
       </c>
       <c r="O5">
-        <v>89.00934505705926</v>
+        <v>88.81079340941236</v>
       </c>
       <c r="P5">
-        <v>356.0373802282371</v>
+        <v>355.2431736376494</v>
       </c>
       <c r="Q5">
-        <v>581.1373802282371</v>
+        <v>580.3431736376494</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08109033036343691</v>
+        <v>0.08138619161732219</v>
       </c>
       <c r="T5">
-        <v>0.5459301870523826</v>
+        <v>0.5505070665548338</v>
       </c>
       <c r="U5">
         <v>0.06613097776675758</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>150.4310525110756</v>
+        <v>112.8232893833067</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08024693524116554</v>
+        <v>0.0802491065633951</v>
       </c>
       <c r="C6">
-        <v>1588.474314190932</v>
+        <v>1573.362070101326</v>
       </c>
       <c r="D6">
-        <v>1590.422314190932</v>
+        <v>1590.322070101327</v>
       </c>
       <c r="E6">
-        <v>-526.852</v>
+        <v>-511.84</v>
       </c>
       <c r="F6">
-        <v>60.04799999999999</v>
+        <v>75.05999999999999</v>
       </c>
       <c r="G6">
         <v>58.1</v>
@@ -1779,28 +1779,28 @@
         <v>448.025</v>
       </c>
       <c r="M6">
-        <v>3.971032952938259</v>
+        <v>4.963791191172823</v>
       </c>
       <c r="N6">
-        <v>444.0539670470617</v>
+        <v>443.0612088088271</v>
       </c>
       <c r="O6">
-        <v>88.81079340941236</v>
+        <v>88.61224176176543</v>
       </c>
       <c r="P6">
-        <v>355.2431736376494</v>
+        <v>354.4489670470617</v>
       </c>
       <c r="Q6">
-        <v>580.3431736376494</v>
+        <v>579.5489670470618</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08138619161732219</v>
+        <v>0.081688281529184</v>
       </c>
       <c r="T6">
-        <v>0.5505070665548338</v>
+        <v>0.5551803014152313</v>
       </c>
       <c r="U6">
         <v>0.06613097776675758</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>112.8232893833067</v>
+        <v>90.25863150664534</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0802491065633951</v>
+        <v>0.08025127788562468</v>
       </c>
       <c r="C7">
-        <v>1573.362070101326</v>
+        <v>1558.249838647664</v>
       </c>
       <c r="D7">
-        <v>1590.322070101327</v>
+        <v>1590.221838647664</v>
       </c>
       <c r="E7">
-        <v>-511.84</v>
+        <v>-496.828</v>
       </c>
       <c r="F7">
-        <v>75.05999999999999</v>
+        <v>90.072</v>
       </c>
       <c r="G7">
         <v>58.1</v>
@@ -1861,28 +1861,28 @@
         <v>448.025</v>
       </c>
       <c r="M7">
-        <v>4.963791191172823</v>
+        <v>5.956549429407389</v>
       </c>
       <c r="N7">
-        <v>443.0612088088271</v>
+        <v>442.0684505705926</v>
       </c>
       <c r="O7">
-        <v>88.61224176176543</v>
+        <v>88.41369011411852</v>
       </c>
       <c r="P7">
-        <v>354.4489670470617</v>
+        <v>353.654760456474</v>
       </c>
       <c r="Q7">
-        <v>579.5489670470618</v>
+        <v>578.7547604564741</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.081688281529184</v>
+        <v>0.08199679888597906</v>
       </c>
       <c r="T7">
-        <v>0.5551803014152313</v>
+        <v>0.5599529668045736</v>
       </c>
       <c r="U7">
         <v>0.06613097776675758</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>90.25863150664534</v>
+        <v>75.21552625553777</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08025127788562468</v>
+        <v>0.08025344920785425</v>
       </c>
       <c r="C8">
-        <v>1558.249838647664</v>
+        <v>1543.137619827557</v>
       </c>
       <c r="D8">
-        <v>1590.221838647664</v>
+        <v>1590.121619827557</v>
       </c>
       <c r="E8">
-        <v>-496.828</v>
+        <v>-481.816</v>
       </c>
       <c r="F8">
-        <v>90.07199999999999</v>
+        <v>105.084</v>
       </c>
       <c r="G8">
         <v>58.1</v>
@@ -1943,28 +1943,28 @@
         <v>448.025</v>
       </c>
       <c r="M8">
-        <v>5.956549429407388</v>
+        <v>6.949307667641952</v>
       </c>
       <c r="N8">
-        <v>442.0684505705926</v>
+        <v>441.075692332358</v>
       </c>
       <c r="O8">
-        <v>88.41369011411852</v>
+        <v>88.21513846647161</v>
       </c>
       <c r="P8">
-        <v>353.654760456474</v>
+        <v>352.8605538658864</v>
       </c>
       <c r="Q8">
-        <v>578.7547604564741</v>
+        <v>577.9605538658864</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08199679888597906</v>
+        <v>0.08231195102464067</v>
       </c>
       <c r="T8">
-        <v>0.5599529668045736</v>
+        <v>0.5648282701592781</v>
       </c>
       <c r="U8">
         <v>0.06613097776675758</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>75.21552625553778</v>
+        <v>64.47045107617525</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08025344920785424</v>
+        <v>0.08025562053008382</v>
       </c>
       <c r="C9">
-        <v>1543.137619827558</v>
+        <v>1528.025413638618</v>
       </c>
       <c r="D9">
-        <v>1590.121619827558</v>
+        <v>1590.021413638618</v>
       </c>
       <c r="E9">
-        <v>-481.816</v>
+        <v>-466.804</v>
       </c>
       <c r="F9">
-        <v>105.084</v>
+        <v>120.096</v>
       </c>
       <c r="G9">
         <v>58.1</v>
@@ -2025,28 +2025,28 @@
         <v>448.025</v>
       </c>
       <c r="M9">
-        <v>6.949307667641954</v>
+        <v>7.942065905876518</v>
       </c>
       <c r="N9">
-        <v>441.075692332358</v>
+        <v>440.0829340941235</v>
       </c>
       <c r="O9">
-        <v>88.21513846647161</v>
+        <v>88.01658681882469</v>
       </c>
       <c r="P9">
-        <v>352.8605538658864</v>
+        <v>352.0663472752988</v>
       </c>
       <c r="Q9">
-        <v>577.9605538658864</v>
+        <v>577.1663472752988</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08231195102464067</v>
+        <v>0.08263395429675145</v>
       </c>
       <c r="T9">
-        <v>0.5648282701592781</v>
+        <v>0.5698095583695195</v>
       </c>
       <c r="U9">
         <v>0.06613097776675758</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>64.47045107617522</v>
+        <v>56.41164469165333</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08025562053008382</v>
+        <v>0.08025779185231338</v>
       </c>
       <c r="C10">
-        <v>1528.025413638618</v>
+        <v>1512.913220078459</v>
       </c>
       <c r="D10">
-        <v>1590.021413638618</v>
+        <v>1589.921220078459</v>
       </c>
       <c r="E10">
-        <v>-466.804</v>
+        <v>-451.792</v>
       </c>
       <c r="F10">
-        <v>120.096</v>
+        <v>135.108</v>
       </c>
       <c r="G10">
         <v>58.1</v>
@@ -2107,28 +2107,28 @@
         <v>448.025</v>
       </c>
       <c r="M10">
-        <v>7.942065905876518</v>
+        <v>8.934824144111081</v>
       </c>
       <c r="N10">
-        <v>440.0829340941235</v>
+        <v>439.0901758558889</v>
       </c>
       <c r="O10">
-        <v>88.01658681882469</v>
+        <v>87.81803517117778</v>
       </c>
       <c r="P10">
-        <v>352.0663472752988</v>
+        <v>351.2721406847111</v>
       </c>
       <c r="Q10">
-        <v>577.1663472752988</v>
+        <v>576.3721406847112</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08263395429675145</v>
+        <v>0.08296303456385366</v>
       </c>
       <c r="T10">
-        <v>0.5698095583695195</v>
+        <v>0.5749003254415244</v>
       </c>
       <c r="U10">
         <v>0.06613097776675758</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>56.41164469165333</v>
+        <v>50.14368417035853</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08025779185231338</v>
+        <v>0.08025996317454294</v>
       </c>
       <c r="C11">
-        <v>1512.913220078459</v>
+        <v>1497.801039144692</v>
       </c>
       <c r="D11">
-        <v>1589.921220078459</v>
+        <v>1589.821039144692</v>
       </c>
       <c r="E11">
-        <v>-451.792</v>
+        <v>-436.78</v>
       </c>
       <c r="F11">
-        <v>135.108</v>
+        <v>150.12</v>
       </c>
       <c r="G11">
         <v>58.1</v>
@@ -2189,28 +2189,28 @@
         <v>448.025</v>
       </c>
       <c r="M11">
-        <v>8.934824144111081</v>
+        <v>9.927582382345646</v>
       </c>
       <c r="N11">
-        <v>439.0901758558889</v>
+        <v>438.0974176176543</v>
       </c>
       <c r="O11">
-        <v>87.81803517117778</v>
+        <v>87.61948352353087</v>
       </c>
       <c r="P11">
-        <v>351.2721406847111</v>
+        <v>350.4779340941235</v>
       </c>
       <c r="Q11">
-        <v>576.3721406847112</v>
+        <v>575.5779340941235</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08296303456385366</v>
+        <v>0.08329942772578038</v>
       </c>
       <c r="T11">
-        <v>0.5749003254415244</v>
+        <v>0.580104220670685</v>
       </c>
       <c r="U11">
         <v>0.06613097776675758</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>50.14368417035853</v>
+        <v>45.12931575332267</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08025996317454295</v>
+        <v>0.08026213449677251</v>
       </c>
       <c r="C12">
-        <v>1497.801039144691</v>
+        <v>1482.68887083493</v>
       </c>
       <c r="D12">
-        <v>1589.821039144691</v>
+        <v>1589.72087083493</v>
       </c>
       <c r="E12">
-        <v>-436.78</v>
+        <v>-421.768</v>
       </c>
       <c r="F12">
-        <v>150.12</v>
+        <v>165.132</v>
       </c>
       <c r="G12">
         <v>58.1</v>
@@ -2271,28 +2271,28 @@
         <v>448.025</v>
       </c>
       <c r="M12">
-        <v>9.927582382345646</v>
+        <v>10.92034062058021</v>
       </c>
       <c r="N12">
-        <v>438.0974176176543</v>
+        <v>437.1046593794198</v>
       </c>
       <c r="O12">
-        <v>87.61948352353087</v>
+        <v>87.42093187588397</v>
       </c>
       <c r="P12">
-        <v>350.4779340941235</v>
+        <v>349.6837275035358</v>
       </c>
       <c r="Q12">
-        <v>575.5779340941235</v>
+        <v>574.7837275035358</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08329942772578039</v>
+        <v>0.08364338028460432</v>
       </c>
       <c r="T12">
-        <v>0.5801042206706852</v>
+        <v>0.5854250573656695</v>
       </c>
       <c r="U12">
         <v>0.06613097776675758</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>45.12931575332267</v>
+        <v>41.02665068483879</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08026213449677251</v>
+        <v>0.08026430581900208</v>
       </c>
       <c r="C13">
-        <v>1482.68887083493</v>
+        <v>1467.576715146787</v>
       </c>
       <c r="D13">
-        <v>1589.72087083493</v>
+        <v>1589.620715146787</v>
       </c>
       <c r="E13">
-        <v>-421.768</v>
+        <v>-406.756</v>
       </c>
       <c r="F13">
-        <v>165.132</v>
+        <v>180.144</v>
       </c>
       <c r="G13">
         <v>58.1</v>
@@ -2353,28 +2353,28 @@
         <v>448.025</v>
       </c>
       <c r="M13">
-        <v>10.92034062058021</v>
+        <v>11.91309885881478</v>
       </c>
       <c r="N13">
-        <v>437.1046593794198</v>
+        <v>436.1119011411852</v>
       </c>
       <c r="O13">
-        <v>87.42093187588397</v>
+        <v>87.22238022823706</v>
       </c>
       <c r="P13">
-        <v>349.6837275035358</v>
+        <v>348.8895209129482</v>
       </c>
       <c r="Q13">
-        <v>574.7837275035358</v>
+        <v>573.9895209129481</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08364338028460432</v>
+        <v>0.0839951499470379</v>
       </c>
       <c r="T13">
-        <v>0.5854250573656695</v>
+        <v>0.5908668221673583</v>
       </c>
       <c r="U13">
         <v>0.06613097776675758</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>41.02665068483879</v>
+        <v>37.60776312776889</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08026430581900208</v>
+        <v>0.08026647714123165</v>
       </c>
       <c r="C14">
-        <v>1467.576715146787</v>
+        <v>1452.464572077879</v>
       </c>
       <c r="D14">
-        <v>1589.620715146787</v>
+        <v>1589.520572077879</v>
       </c>
       <c r="E14">
-        <v>-406.756</v>
+        <v>-391.744</v>
       </c>
       <c r="F14">
-        <v>180.144</v>
+        <v>195.156</v>
       </c>
       <c r="G14">
         <v>58.1</v>
@@ -2435,28 +2435,28 @@
         <v>448.025</v>
       </c>
       <c r="M14">
-        <v>11.91309885881478</v>
+        <v>12.90585709704934</v>
       </c>
       <c r="N14">
-        <v>436.1119011411852</v>
+        <v>435.1191429029506</v>
       </c>
       <c r="O14">
-        <v>87.22238022823706</v>
+        <v>87.02382858059013</v>
       </c>
       <c r="P14">
-        <v>348.8895209129482</v>
+        <v>348.0953143223605</v>
       </c>
       <c r="Q14">
-        <v>573.9895209129481</v>
+        <v>573.1953143223604</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0839951499470379</v>
+        <v>0.084355006268378</v>
       </c>
       <c r="T14">
-        <v>0.5908668221673583</v>
+        <v>0.5964336850104651</v>
       </c>
       <c r="U14">
         <v>0.06613097776675758</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>37.60776312776889</v>
+        <v>34.71485827178667</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08026647714123165</v>
+        <v>0.08026864846346121</v>
       </c>
       <c r="C15">
-        <v>1452.464572077879</v>
+        <v>1437.35244162582</v>
       </c>
       <c r="D15">
-        <v>1589.520572077879</v>
+        <v>1589.42044162582</v>
       </c>
       <c r="E15">
-        <v>-391.744</v>
+        <v>-376.732</v>
       </c>
       <c r="F15">
-        <v>195.156</v>
+        <v>210.168</v>
       </c>
       <c r="G15">
         <v>58.1</v>
@@ -2517,28 +2517,28 @@
         <v>448.025</v>
       </c>
       <c r="M15">
-        <v>12.90585709704934</v>
+        <v>13.89861533528391</v>
       </c>
       <c r="N15">
-        <v>435.1191429029506</v>
+        <v>434.1263846647161</v>
       </c>
       <c r="O15">
-        <v>87.02382858059013</v>
+        <v>86.82527693294321</v>
       </c>
       <c r="P15">
-        <v>348.0953143223605</v>
+        <v>347.3011077317728</v>
       </c>
       <c r="Q15">
-        <v>573.1953143223604</v>
+        <v>572.4011077317729</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.084355006268378</v>
+        <v>0.08472323134137716</v>
       </c>
       <c r="T15">
-        <v>0.5964336850104651</v>
+        <v>0.6021300097801559</v>
       </c>
       <c r="U15">
         <v>0.06613097776675758</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>34.71485827178667</v>
+        <v>32.23522553808761</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08026864846346121</v>
+        <v>0.08027081978569078</v>
       </c>
       <c r="C16">
-        <v>1437.35244162582</v>
+        <v>1422.240323788226</v>
       </c>
       <c r="D16">
-        <v>1589.42044162582</v>
+        <v>1589.320323788226</v>
       </c>
       <c r="E16">
-        <v>-376.732</v>
+        <v>-361.72</v>
       </c>
       <c r="F16">
-        <v>210.168</v>
+        <v>225.18</v>
       </c>
       <c r="G16">
         <v>58.1</v>
@@ -2599,28 +2599,28 @@
         <v>448.025</v>
       </c>
       <c r="M16">
-        <v>13.89861533528391</v>
+        <v>14.89137357351847</v>
       </c>
       <c r="N16">
-        <v>434.1263846647161</v>
+        <v>433.1336264264815</v>
       </c>
       <c r="O16">
-        <v>86.82527693294321</v>
+        <v>86.6267252852963</v>
       </c>
       <c r="P16">
-        <v>347.3011077317728</v>
+        <v>346.5069011411852</v>
       </c>
       <c r="Q16">
-        <v>572.4011077317729</v>
+        <v>571.6069011411853</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08472323134137716</v>
+        <v>0.08510012053374102</v>
       </c>
       <c r="T16">
-        <v>0.6021300097801559</v>
+        <v>0.6079603657208981</v>
       </c>
       <c r="U16">
         <v>0.06613097776675758</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>32.23522553808761</v>
+        <v>30.08621050221511</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08027081978569078</v>
+        <v>0.08027299110792034</v>
       </c>
       <c r="C17">
-        <v>1422.240323788226</v>
+        <v>1407.128218562714</v>
       </c>
       <c r="D17">
-        <v>1589.320323788226</v>
+        <v>1589.220218562715</v>
       </c>
       <c r="E17">
-        <v>-361.72</v>
+        <v>-346.708</v>
       </c>
       <c r="F17">
-        <v>225.18</v>
+        <v>240.192</v>
       </c>
       <c r="G17">
         <v>58.1</v>
@@ -2681,28 +2681,28 @@
         <v>448.025</v>
       </c>
       <c r="M17">
-        <v>14.89137357351847</v>
+        <v>15.88413181175304</v>
       </c>
       <c r="N17">
-        <v>433.1336264264815</v>
+        <v>432.1408681882469</v>
       </c>
       <c r="O17">
-        <v>86.6267252852963</v>
+        <v>86.42817363764939</v>
       </c>
       <c r="P17">
-        <v>346.5069011411852</v>
+        <v>345.7126945505976</v>
       </c>
       <c r="Q17">
-        <v>571.6069011411853</v>
+        <v>570.8126945505976</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08510012053374102</v>
+        <v>0.08548598327830401</v>
       </c>
       <c r="T17">
-        <v>0.6079603657208981</v>
+        <v>0.6139295396602293</v>
       </c>
       <c r="U17">
         <v>0.06613097776675758</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>30.08621050221511</v>
+        <v>28.20582234582666</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08027299110792034</v>
+        <v>0.08027516243014991</v>
       </c>
       <c r="C18">
-        <v>1407.128218562714</v>
+        <v>1392.016125946901</v>
       </c>
       <c r="D18">
-        <v>1589.220218562715</v>
+        <v>1589.120125946901</v>
       </c>
       <c r="E18">
-        <v>-346.708</v>
+        <v>-331.696</v>
       </c>
       <c r="F18">
-        <v>240.192</v>
+        <v>255.204</v>
       </c>
       <c r="G18">
         <v>58.1</v>
@@ -2763,28 +2763,28 @@
         <v>448.025</v>
       </c>
       <c r="M18">
-        <v>15.88413181175304</v>
+        <v>16.8768900499876</v>
       </c>
       <c r="N18">
-        <v>432.1408681882469</v>
+        <v>431.1481099500124</v>
       </c>
       <c r="O18">
-        <v>86.42817363764939</v>
+        <v>86.22962199000249</v>
       </c>
       <c r="P18">
-        <v>345.7126945505976</v>
+        <v>344.9184879600099</v>
       </c>
       <c r="Q18">
-        <v>570.8126945505976</v>
+        <v>570.0184879600099</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08548598327830401</v>
+        <v>0.08588114392032636</v>
       </c>
       <c r="T18">
-        <v>0.6139295396602293</v>
+        <v>0.6200425491161712</v>
       </c>
       <c r="U18">
         <v>0.06613097776675758</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>28.20582234582666</v>
+        <v>26.54665632548392</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08027516243014991</v>
+        <v>0.08027733375237948</v>
       </c>
       <c r="C19">
-        <v>1392.016125946901</v>
+        <v>1376.904045938402</v>
       </c>
       <c r="D19">
-        <v>1589.120125946901</v>
+        <v>1589.020045938402</v>
       </c>
       <c r="E19">
-        <v>-331.696</v>
+        <v>-316.684</v>
       </c>
       <c r="F19">
-        <v>255.204</v>
+        <v>270.216</v>
       </c>
       <c r="G19">
         <v>58.1</v>
@@ -2845,28 +2845,28 @@
         <v>448.025</v>
       </c>
       <c r="M19">
-        <v>16.8768900499876</v>
+        <v>17.86964828822217</v>
       </c>
       <c r="N19">
-        <v>431.1481099500124</v>
+        <v>430.1553517117778</v>
       </c>
       <c r="O19">
-        <v>86.22962199000249</v>
+        <v>86.03107034235558</v>
       </c>
       <c r="P19">
-        <v>344.9184879600099</v>
+        <v>344.1242813694222</v>
       </c>
       <c r="Q19">
-        <v>570.0184879600099</v>
+        <v>569.2242813694222</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08588114392032636</v>
+        <v>0.08628594262678828</v>
       </c>
       <c r="T19">
-        <v>0.6200425491161712</v>
+        <v>0.6263046563637213</v>
       </c>
       <c r="U19">
         <v>0.06613097776675758</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>26.54665632548392</v>
+        <v>25.07184208517926</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08027733375237947</v>
+        <v>0.08027950507460906</v>
       </c>
       <c r="C20">
-        <v>1376.904045938403</v>
+        <v>1361.791978534839</v>
       </c>
       <c r="D20">
-        <v>1589.020045938403</v>
+        <v>1588.919978534838</v>
       </c>
       <c r="E20">
-        <v>-316.684</v>
+        <v>-301.672</v>
       </c>
       <c r="F20">
-        <v>270.216</v>
+        <v>285.228</v>
       </c>
       <c r="G20">
         <v>58.1</v>
@@ -2927,28 +2927,28 @@
         <v>448.025</v>
       </c>
       <c r="M20">
-        <v>17.86964828822216</v>
+        <v>18.86240652645673</v>
       </c>
       <c r="N20">
-        <v>430.1553517117778</v>
+        <v>429.1625934735433</v>
       </c>
       <c r="O20">
-        <v>86.03107034235558</v>
+        <v>85.83251869470865</v>
       </c>
       <c r="P20">
-        <v>344.1242813694222</v>
+        <v>343.3300747788346</v>
       </c>
       <c r="Q20">
-        <v>569.2242813694222</v>
+        <v>568.4300747788346</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08628594262678826</v>
+        <v>0.08670073636303938</v>
       </c>
       <c r="T20">
-        <v>0.6263046563637212</v>
+        <v>0.6327213835433096</v>
       </c>
       <c r="U20">
         <v>0.06613097776675758</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>25.07184208517926</v>
+        <v>23.7522714491172</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08027950507460906</v>
+        <v>0.08028167639683861</v>
       </c>
       <c r="C21">
-        <v>1361.791978534839</v>
+        <v>1346.679923733828</v>
       </c>
       <c r="D21">
-        <v>1588.919978534838</v>
+        <v>1588.819923733829</v>
       </c>
       <c r="E21">
-        <v>-301.672</v>
+        <v>-286.66</v>
       </c>
       <c r="F21">
-        <v>285.228</v>
+        <v>300.24</v>
       </c>
       <c r="G21">
         <v>58.1</v>
@@ -3009,28 +3009,28 @@
         <v>448.025</v>
       </c>
       <c r="M21">
-        <v>18.86240652645673</v>
+        <v>19.85516476469129</v>
       </c>
       <c r="N21">
-        <v>429.1625934735433</v>
+        <v>428.1698352353087</v>
       </c>
       <c r="O21">
-        <v>85.83251869470865</v>
+        <v>85.63396704706174</v>
       </c>
       <c r="P21">
-        <v>343.3300747788346</v>
+        <v>342.535868188247</v>
       </c>
       <c r="Q21">
-        <v>568.4300747788346</v>
+        <v>567.6358681882471</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08670073636303938</v>
+        <v>0.08712589994269675</v>
       </c>
       <c r="T21">
-        <v>0.6327213835433096</v>
+        <v>0.6392985289023877</v>
       </c>
       <c r="U21">
         <v>0.06613097776675758</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>23.7522714491172</v>
+        <v>22.56465787666134</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08028167639683861</v>
+        <v>0.08028384771906819</v>
       </c>
       <c r="C22">
-        <v>1346.679923733828</v>
+        <v>1331.56788153299</v>
       </c>
       <c r="D22">
-        <v>1588.819923733829</v>
+        <v>1588.71988153299</v>
       </c>
       <c r="E22">
-        <v>-286.66</v>
+        <v>-271.648</v>
       </c>
       <c r="F22">
-        <v>300.24</v>
+        <v>315.252</v>
       </c>
       <c r="G22">
         <v>58.1</v>
@@ -3091,28 +3091,28 @@
         <v>448.025</v>
       </c>
       <c r="M22">
-        <v>19.85516476469129</v>
+        <v>20.84792300292586</v>
       </c>
       <c r="N22">
-        <v>428.1698352353087</v>
+        <v>427.1770769970741</v>
       </c>
       <c r="O22">
-        <v>85.63396704706174</v>
+        <v>85.43541539941482</v>
       </c>
       <c r="P22">
-        <v>342.535868188247</v>
+        <v>341.7416615976593</v>
       </c>
       <c r="Q22">
-        <v>567.6358681882471</v>
+        <v>566.8416615976594</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08712589994269675</v>
+        <v>0.08756182715728215</v>
       </c>
       <c r="T22">
-        <v>0.6392985289023877</v>
+        <v>0.6460421842705564</v>
       </c>
       <c r="U22">
         <v>0.06613097776675758</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>22.56465787666134</v>
+        <v>21.49015035872508</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08028384771906819</v>
+        <v>0.08028601904129774</v>
       </c>
       <c r="C23">
-        <v>1331.56788153299</v>
+        <v>1316.455851929945</v>
       </c>
       <c r="D23">
-        <v>1588.71988153299</v>
+        <v>1588.619851929945</v>
       </c>
       <c r="E23">
-        <v>-271.648</v>
+        <v>-256.636</v>
       </c>
       <c r="F23">
-        <v>315.252</v>
+        <v>330.264</v>
       </c>
       <c r="G23">
         <v>58.1</v>
@@ -3173,28 +3173,28 @@
         <v>448.025</v>
       </c>
       <c r="M23">
-        <v>20.84792300292586</v>
+        <v>21.84068124116042</v>
       </c>
       <c r="N23">
-        <v>427.1770769970741</v>
+        <v>426.1843187588395</v>
       </c>
       <c r="O23">
-        <v>85.43541539941482</v>
+        <v>85.23686375176791</v>
       </c>
       <c r="P23">
-        <v>341.7416615976593</v>
+        <v>340.9474550070717</v>
       </c>
       <c r="Q23">
-        <v>566.8416615976594</v>
+        <v>566.0474550070717</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08756182715728215</v>
+        <v>0.08800893199275436</v>
       </c>
       <c r="T23">
-        <v>0.6460421842705564</v>
+        <v>0.6529587538789344</v>
       </c>
       <c r="U23">
         <v>0.06613097776675758</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>21.49015035872508</v>
+        <v>20.5133253424194</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08028601904129774</v>
+        <v>0.08028819036352731</v>
       </c>
       <c r="C24">
-        <v>1316.455851929945</v>
+        <v>1301.343834922312</v>
       </c>
       <c r="D24">
-        <v>1588.619851929945</v>
+        <v>1588.519834922312</v>
       </c>
       <c r="E24">
-        <v>-256.636</v>
+        <v>-241.624</v>
       </c>
       <c r="F24">
-        <v>330.264</v>
+        <v>345.276</v>
       </c>
       <c r="G24">
         <v>58.1</v>
@@ -3255,28 +3255,28 @@
         <v>448.025</v>
       </c>
       <c r="M24">
-        <v>21.84068124116042</v>
+        <v>22.83343947939499</v>
       </c>
       <c r="N24">
-        <v>426.1843187588395</v>
+        <v>425.191560520605</v>
       </c>
       <c r="O24">
-        <v>85.23686375176791</v>
+        <v>85.038312104121</v>
       </c>
       <c r="P24">
-        <v>340.9474550070717</v>
+        <v>340.153248416484</v>
       </c>
       <c r="Q24">
-        <v>566.0474550070717</v>
+        <v>565.253248416484</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08800893199275436</v>
+        <v>0.08846764994083625</v>
       </c>
       <c r="T24">
-        <v>0.6529587538789344</v>
+        <v>0.6600549746459717</v>
       </c>
       <c r="U24">
         <v>0.06613097776675758</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>20.5133253424194</v>
+        <v>19.62144163187942</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08028819036352731</v>
+        <v>0.08029036168575687</v>
       </c>
       <c r="C25">
-        <v>1301.343834922312</v>
+        <v>1286.231830507714</v>
       </c>
       <c r="D25">
-        <v>1588.519834922312</v>
+        <v>1588.419830507714</v>
       </c>
       <c r="E25">
-        <v>-241.624</v>
+        <v>-226.612</v>
       </c>
       <c r="F25">
-        <v>345.276</v>
+        <v>360.288</v>
       </c>
       <c r="G25">
         <v>58.1</v>
@@ -3337,28 +3337,28 @@
         <v>448.025</v>
       </c>
       <c r="M25">
-        <v>22.83343947939499</v>
+        <v>23.82619771762955</v>
       </c>
       <c r="N25">
-        <v>425.191560520605</v>
+        <v>424.1988022823704</v>
       </c>
       <c r="O25">
-        <v>85.038312104121</v>
+        <v>84.8397604564741</v>
       </c>
       <c r="P25">
-        <v>340.153248416484</v>
+        <v>339.3590418258963</v>
       </c>
       <c r="Q25">
-        <v>565.253248416484</v>
+        <v>564.4590418258963</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08846764994083625</v>
+        <v>0.08893843941386766</v>
       </c>
       <c r="T25">
-        <v>0.6600549746459717</v>
+        <v>0.6673379380647732</v>
       </c>
       <c r="U25">
         <v>0.06613097776675758</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>19.62144163187942</v>
+        <v>18.80388156388444</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08029036168575686</v>
+        <v>0.08029253300798643</v>
       </c>
       <c r="C26">
-        <v>1286.231830507714</v>
+        <v>1271.119838683772</v>
       </c>
       <c r="D26">
-        <v>1588.419830507715</v>
+        <v>1588.319838683772</v>
       </c>
       <c r="E26">
-        <v>-226.612</v>
+        <v>-211.6</v>
       </c>
       <c r="F26">
-        <v>360.288</v>
+        <v>375.3</v>
       </c>
       <c r="G26">
         <v>58.1</v>
@@ -3419,28 +3419,28 @@
         <v>448.025</v>
       </c>
       <c r="M26">
-        <v>23.82619771762955</v>
+        <v>24.81895595586412</v>
       </c>
       <c r="N26">
-        <v>424.1988022823704</v>
+        <v>423.2060440441359</v>
       </c>
       <c r="O26">
-        <v>84.8397604564741</v>
+        <v>84.64120880882717</v>
       </c>
       <c r="P26">
-        <v>339.3590418258963</v>
+        <v>338.5648352353087</v>
       </c>
       <c r="Q26">
-        <v>564.4590418258963</v>
+        <v>563.6648352353087</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08893843941386764</v>
+        <v>0.08942178327284656</v>
       </c>
       <c r="T26">
-        <v>0.667337938064773</v>
+        <v>0.6748151138414091</v>
       </c>
       <c r="U26">
         <v>0.06613097776675758</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>18.80388156388445</v>
+        <v>18.05172630132907</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08029253300798643</v>
+        <v>0.080294704330216</v>
       </c>
       <c r="C27">
-        <v>1271.119838683772</v>
+        <v>1256.007859448107</v>
       </c>
       <c r="D27">
-        <v>1588.319838683772</v>
+        <v>1588.219859448107</v>
       </c>
       <c r="E27">
-        <v>-211.6</v>
+        <v>-196.588</v>
       </c>
       <c r="F27">
-        <v>375.3</v>
+        <v>390.312</v>
       </c>
       <c r="G27">
         <v>58.1</v>
@@ -3501,28 +3501,28 @@
         <v>448.025</v>
       </c>
       <c r="M27">
-        <v>24.81895595586412</v>
+        <v>25.81171419409868</v>
       </c>
       <c r="N27">
-        <v>423.2060440441359</v>
+        <v>422.2132858059013</v>
       </c>
       <c r="O27">
-        <v>84.64120880882717</v>
+        <v>84.44265716118026</v>
       </c>
       <c r="P27">
-        <v>338.5648352353087</v>
+        <v>337.7706286447211</v>
       </c>
       <c r="Q27">
-        <v>563.6648352353087</v>
+        <v>562.8706286447211</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08942178327284656</v>
+        <v>0.08991819047936545</v>
       </c>
       <c r="T27">
-        <v>0.6748151138414091</v>
+        <v>0.6824943754498463</v>
       </c>
       <c r="U27">
         <v>0.06613097776675758</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>18.05172630132907</v>
+        <v>17.35742913589333</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.080294704330216</v>
+        <v>0.08029687565244557</v>
       </c>
       <c r="C28">
-        <v>1256.007859448107</v>
+        <v>1240.895892798344</v>
       </c>
       <c r="D28">
-        <v>1588.219859448107</v>
+        <v>1588.119892798344</v>
       </c>
       <c r="E28">
-        <v>-196.588</v>
+        <v>-181.576</v>
       </c>
       <c r="F28">
-        <v>390.312</v>
+        <v>405.324</v>
       </c>
       <c r="G28">
         <v>58.1</v>
@@ -3583,28 +3583,28 @@
         <v>448.025</v>
       </c>
       <c r="M28">
-        <v>25.81171419409868</v>
+        <v>26.80447243233325</v>
       </c>
       <c r="N28">
-        <v>422.2132858059013</v>
+        <v>421.2205275676667</v>
       </c>
       <c r="O28">
-        <v>84.44265716118026</v>
+        <v>84.24410551353336</v>
       </c>
       <c r="P28">
-        <v>337.7706286447211</v>
+        <v>336.9764220541334</v>
       </c>
       <c r="Q28">
-        <v>562.8706286447211</v>
+        <v>562.0764220541334</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08991819047936545</v>
+        <v>0.09042819788332321</v>
       </c>
       <c r="T28">
-        <v>0.6824943754498463</v>
+        <v>0.6903840277872817</v>
       </c>
       <c r="U28">
         <v>0.06613097776675758</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>17.35742913589333</v>
+        <v>16.71456139011951</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08029687565244557</v>
+        <v>0.08029904697467513</v>
       </c>
       <c r="C29">
-        <v>1240.895892798344</v>
+        <v>1225.783938732107</v>
       </c>
       <c r="D29">
-        <v>1588.119892798344</v>
+        <v>1588.019938732107</v>
       </c>
       <c r="E29">
-        <v>-181.576</v>
+        <v>-166.564</v>
       </c>
       <c r="F29">
-        <v>405.324</v>
+        <v>420.336</v>
       </c>
       <c r="G29">
         <v>58.1</v>
@@ -3665,28 +3665,28 @@
         <v>448.025</v>
       </c>
       <c r="M29">
-        <v>26.80447243233325</v>
+        <v>27.79723067056782</v>
       </c>
       <c r="N29">
-        <v>421.2205275676667</v>
+        <v>420.2277693294321</v>
       </c>
       <c r="O29">
-        <v>84.24410551353336</v>
+        <v>84.04555386588643</v>
       </c>
       <c r="P29">
-        <v>336.9764220541334</v>
+        <v>336.1822154635457</v>
       </c>
       <c r="Q29">
-        <v>562.0764220541334</v>
+        <v>561.2822154635458</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09042819788332321</v>
+        <v>0.0909523721596131</v>
       </c>
       <c r="T29">
-        <v>0.6903840277872817</v>
+        <v>0.6984928371340903</v>
       </c>
       <c r="U29">
         <v>0.06613097776675758</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>16.71456139011951</v>
+        <v>16.11761276904381</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08029904697467513</v>
+        <v>0.0803012182969047</v>
       </c>
       <c r="C30">
-        <v>1225.783938732107</v>
+        <v>1210.671997247018</v>
       </c>
       <c r="D30">
-        <v>1588.019938732107</v>
+        <v>1587.919997247018</v>
       </c>
       <c r="E30">
-        <v>-166.564</v>
+        <v>-151.552</v>
       </c>
       <c r="F30">
-        <v>420.336</v>
+        <v>435.348</v>
       </c>
       <c r="G30">
         <v>58.1</v>
@@ -3747,28 +3747,28 @@
         <v>448.025</v>
       </c>
       <c r="M30">
-        <v>27.79723067056782</v>
+        <v>28.78998890880238</v>
       </c>
       <c r="N30">
-        <v>420.2277693294321</v>
+        <v>419.2350110911976</v>
       </c>
       <c r="O30">
-        <v>84.04555386588643</v>
+        <v>83.84700221823952</v>
       </c>
       <c r="P30">
-        <v>336.1822154635457</v>
+        <v>335.388008872958</v>
       </c>
       <c r="Q30">
-        <v>561.2822154635458</v>
+        <v>560.4880088729581</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.0909523721596131</v>
+        <v>0.09149131190847457</v>
       </c>
       <c r="T30">
-        <v>0.6984928371340903</v>
+        <v>0.7068300636455976</v>
       </c>
       <c r="U30">
         <v>0.06613097776675758</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>16.11761276904381</v>
+        <v>15.56183301838712</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08030121829690469</v>
+        <v>0.08030338961913427</v>
       </c>
       <c r="C31">
-        <v>1210.671997247018</v>
+        <v>1195.560068340703</v>
       </c>
       <c r="D31">
-        <v>1587.919997247019</v>
+        <v>1587.820068340703</v>
       </c>
       <c r="E31">
-        <v>-151.5520000000001</v>
+        <v>-136.54</v>
       </c>
       <c r="F31">
-        <v>435.3479999999999</v>
+        <v>450.36</v>
       </c>
       <c r="G31">
         <v>58.1</v>
@@ -3829,28 +3829,28 @@
         <v>448.025</v>
       </c>
       <c r="M31">
-        <v>28.78998890880237</v>
+        <v>29.78274714703694</v>
       </c>
       <c r="N31">
-        <v>419.2350110911976</v>
+        <v>418.242252852963</v>
       </c>
       <c r="O31">
-        <v>83.84700221823954</v>
+        <v>83.64845057059262</v>
       </c>
       <c r="P31">
-        <v>335.3880088729581</v>
+        <v>334.5938022823704</v>
       </c>
       <c r="Q31">
-        <v>560.4880088729581</v>
+        <v>559.6938022823704</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09149131190847457</v>
+        <v>0.09204564993587494</v>
       </c>
       <c r="T31">
-        <v>0.7068300636455976</v>
+        <v>0.7154054966288624</v>
       </c>
       <c r="U31">
         <v>0.06613097776675758</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>15.56183301838713</v>
+        <v>15.04310525110755</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08030338961913427</v>
+        <v>0.08030556094136385</v>
       </c>
       <c r="C32">
-        <v>1195.560068340703</v>
+        <v>1180.448152010787</v>
       </c>
       <c r="D32">
-        <v>1587.820068340703</v>
+        <v>1587.720152010787</v>
       </c>
       <c r="E32">
-        <v>-136.54</v>
+        <v>-121.528</v>
       </c>
       <c r="F32">
-        <v>450.36</v>
+        <v>465.372</v>
       </c>
       <c r="G32">
         <v>58.1</v>
@@ -3911,28 +3911,28 @@
         <v>448.025</v>
       </c>
       <c r="M32">
-        <v>29.78274714703694</v>
+        <v>30.77550538527151</v>
       </c>
       <c r="N32">
-        <v>418.242252852963</v>
+        <v>417.2494946147285</v>
       </c>
       <c r="O32">
-        <v>83.64845057059262</v>
+        <v>83.44989892294569</v>
       </c>
       <c r="P32">
-        <v>334.5938022823704</v>
+        <v>333.7995956917828</v>
       </c>
       <c r="Q32">
-        <v>559.6938022823704</v>
+        <v>558.8995956917828</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09204564993587494</v>
+        <v>0.09261605573218545</v>
       </c>
       <c r="T32">
-        <v>0.7154054966288624</v>
+        <v>0.7242294928870044</v>
       </c>
       <c r="U32">
         <v>0.06613097776675758</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>15.04310525110755</v>
+        <v>14.55784379139441</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08030556094136385</v>
+        <v>0.0803077322635934</v>
       </c>
       <c r="C33">
-        <v>1180.448152010787</v>
+        <v>1165.336248254897</v>
       </c>
       <c r="D33">
-        <v>1587.720152010787</v>
+        <v>1587.620248254897</v>
       </c>
       <c r="E33">
-        <v>-121.528</v>
+        <v>-106.516</v>
       </c>
       <c r="F33">
-        <v>465.372</v>
+        <v>480.384</v>
       </c>
       <c r="G33">
         <v>58.1</v>
@@ -3993,28 +3993,28 @@
         <v>448.025</v>
       </c>
       <c r="M33">
-        <v>30.77550538527151</v>
+        <v>31.76826362350607</v>
       </c>
       <c r="N33">
-        <v>417.2494946147285</v>
+        <v>416.2567363764939</v>
       </c>
       <c r="O33">
-        <v>83.44989892294569</v>
+        <v>83.25134727529878</v>
       </c>
       <c r="P33">
-        <v>333.7995956917828</v>
+        <v>333.0053891011951</v>
       </c>
       <c r="Q33">
-        <v>558.8995956917828</v>
+        <v>558.1053891011952</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09261605573218545</v>
+        <v>0.09320323816956391</v>
       </c>
       <c r="T33">
-        <v>0.7242294928870044</v>
+        <v>0.7333130184468565</v>
       </c>
       <c r="U33">
         <v>0.06613097776675758</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>14.55784379139441</v>
+        <v>14.10291117291333</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0803077322635934</v>
+        <v>0.08030990358582298</v>
       </c>
       <c r="C34">
-        <v>1165.336248254897</v>
+        <v>1150.224357070658</v>
       </c>
       <c r="D34">
-        <v>1587.620248254897</v>
+        <v>1587.520357070658</v>
       </c>
       <c r="E34">
-        <v>-106.516</v>
+        <v>-91.50400000000002</v>
       </c>
       <c r="F34">
-        <v>480.384</v>
+        <v>495.396</v>
       </c>
       <c r="G34">
         <v>58.1</v>
@@ -4075,28 +4075,28 @@
         <v>448.025</v>
       </c>
       <c r="M34">
-        <v>31.76826362350607</v>
+        <v>32.76102186174064</v>
       </c>
       <c r="N34">
-        <v>416.2567363764939</v>
+        <v>415.2639781382593</v>
       </c>
       <c r="O34">
-        <v>83.25134727529878</v>
+        <v>83.05279562765188</v>
       </c>
       <c r="P34">
-        <v>333.0053891011951</v>
+        <v>332.2111825106075</v>
       </c>
       <c r="Q34">
-        <v>558.1053891011952</v>
+        <v>557.3111825106075</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09320323816956391</v>
+        <v>0.09380794844089399</v>
       </c>
       <c r="T34">
-        <v>0.7333130184468565</v>
+        <v>0.7426676940234206</v>
       </c>
       <c r="U34">
         <v>0.06613097776675758</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>14.10291117291333</v>
+        <v>13.6755502282796</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08030990358582298</v>
+        <v>0.08031207490805253</v>
       </c>
       <c r="C35">
-        <v>1150.224357070658</v>
+        <v>1135.112478455699</v>
       </c>
       <c r="D35">
-        <v>1587.520357070658</v>
+        <v>1587.420478455699</v>
       </c>
       <c r="E35">
-        <v>-91.50400000000002</v>
+        <v>-76.49200000000002</v>
       </c>
       <c r="F35">
-        <v>495.396</v>
+        <v>510.408</v>
       </c>
       <c r="G35">
         <v>58.1</v>
@@ -4157,28 +4157,28 @@
         <v>448.025</v>
       </c>
       <c r="M35">
-        <v>32.76102186174064</v>
+        <v>33.7537800999752</v>
       </c>
       <c r="N35">
-        <v>415.2639781382593</v>
+        <v>414.2712199000248</v>
       </c>
       <c r="O35">
-        <v>83.05279562765188</v>
+        <v>82.85424398000497</v>
       </c>
       <c r="P35">
-        <v>332.2111825106075</v>
+        <v>331.4169759200198</v>
       </c>
       <c r="Q35">
-        <v>557.3111825106075</v>
+        <v>556.5169759200198</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09380794844089399</v>
+        <v>0.09443098326590071</v>
       </c>
       <c r="T35">
-        <v>0.7426676940234206</v>
+        <v>0.7523058446174562</v>
       </c>
       <c r="U35">
         <v>0.06613097776675758</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>13.6755502282796</v>
+        <v>13.27332816274196</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08031207490805253</v>
+        <v>0.0803142462302821</v>
       </c>
       <c r="C36">
-        <v>1135.112478455699</v>
+        <v>1120.000612407646</v>
       </c>
       <c r="D36">
-        <v>1587.420478455699</v>
+        <v>1587.320612407646</v>
       </c>
       <c r="E36">
-        <v>-76.49200000000002</v>
+        <v>-61.48000000000002</v>
       </c>
       <c r="F36">
-        <v>510.408</v>
+        <v>525.42</v>
       </c>
       <c r="G36">
         <v>58.1</v>
@@ -4239,28 +4239,28 @@
         <v>448.025</v>
       </c>
       <c r="M36">
-        <v>33.7537800999752</v>
+        <v>34.74653833820977</v>
       </c>
       <c r="N36">
-        <v>414.2712199000248</v>
+        <v>413.2784616617902</v>
       </c>
       <c r="O36">
-        <v>82.85424398000497</v>
+        <v>82.65569233235806</v>
       </c>
       <c r="P36">
-        <v>331.4169759200198</v>
+        <v>330.6227693294322</v>
       </c>
       <c r="Q36">
-        <v>556.5169759200198</v>
+        <v>555.7227693294321</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09443098326590071</v>
+        <v>0.09507318839321535</v>
       </c>
       <c r="T36">
-        <v>0.7523058446174562</v>
+        <v>0.7622405536913084</v>
       </c>
       <c r="U36">
         <v>0.06613097776675758</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>13.27332816274196</v>
+        <v>12.89409021523505</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0803142462302821</v>
+        <v>0.08074841755251165</v>
       </c>
       <c r="C37">
-        <v>1120.000612407646</v>
+        <v>1085.269004558285</v>
       </c>
       <c r="D37">
-        <v>1587.320612407646</v>
+        <v>1567.601004558285</v>
       </c>
       <c r="E37">
-        <v>-61.48000000000002</v>
+        <v>-46.46799999999996</v>
       </c>
       <c r="F37">
-        <v>525.42</v>
+        <v>540.432</v>
       </c>
       <c r="G37">
         <v>58.1</v>
@@ -4321,45 +4321,45 @@
         <v>448.025</v>
       </c>
       <c r="M37">
-        <v>34.74653833820977</v>
+        <v>36.54994457644433</v>
       </c>
       <c r="N37">
-        <v>413.2784616617902</v>
+        <v>411.4750554235557</v>
       </c>
       <c r="O37">
-        <v>82.65569233235806</v>
+        <v>82.29501108471113</v>
       </c>
       <c r="P37">
-        <v>330.6227693294322</v>
+        <v>329.1800443388445</v>
       </c>
       <c r="Q37">
-        <v>555.7227693294321</v>
+        <v>554.2800443388446</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09507318839321535</v>
+        <v>0.09573546243075856</v>
       </c>
       <c r="T37">
-        <v>0.7622405536913084</v>
+        <v>0.7724857224237185</v>
       </c>
       <c r="U37">
-        <v>0.06613097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V37">
         <v>0.2</v>
       </c>
       <c r="W37">
-        <v>0.05290478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y37">
-        <v>12.89409021523505</v>
+        <v>12.25788452463872</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08074841755251166</v>
+        <v>0.08076258887474123</v>
       </c>
       <c r="C38">
-        <v>1085.269004558285</v>
+        <v>1069.621611709014</v>
       </c>
       <c r="D38">
-        <v>1567.601004558285</v>
+        <v>1566.965611709014</v>
       </c>
       <c r="E38">
-        <v>-46.46800000000007</v>
+        <v>-31.45600000000002</v>
       </c>
       <c r="F38">
-        <v>540.4319999999999</v>
+        <v>555.444</v>
       </c>
       <c r="G38">
         <v>58.1</v>
@@ -4403,28 +4403,28 @@
         <v>448.025</v>
       </c>
       <c r="M38">
-        <v>36.54994457644433</v>
+        <v>37.5652208146789</v>
       </c>
       <c r="N38">
-        <v>411.4750554235557</v>
+        <v>410.4597791853211</v>
       </c>
       <c r="O38">
-        <v>82.29501108471113</v>
+        <v>82.09195583706422</v>
       </c>
       <c r="P38">
-        <v>329.1800443388445</v>
+        <v>328.3678233482568</v>
       </c>
       <c r="Q38">
-        <v>554.2800443388446</v>
+        <v>553.4678233482568</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09573546243075856</v>
+        <v>0.0964187610409222</v>
       </c>
       <c r="T38">
-        <v>0.7724857224237184</v>
+        <v>0.7830561346079511</v>
       </c>
       <c r="U38">
         <v>0.06763097776675758</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>12.25788452463872</v>
+        <v>11.92659034829713</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08076258887474123</v>
+        <v>0.08077676019697079</v>
       </c>
       <c r="C39">
-        <v>1069.621611709014</v>
+        <v>1053.974733736294</v>
       </c>
       <c r="D39">
-        <v>1566.965611709014</v>
+        <v>1566.330733736294</v>
       </c>
       <c r="E39">
-        <v>-31.45600000000002</v>
+        <v>-16.44400000000007</v>
       </c>
       <c r="F39">
-        <v>555.444</v>
+        <v>570.4559999999999</v>
       </c>
       <c r="G39">
         <v>58.1</v>
@@ -4485,28 +4485,28 @@
         <v>448.025</v>
       </c>
       <c r="M39">
-        <v>37.5652208146789</v>
+        <v>38.58049705291346</v>
       </c>
       <c r="N39">
-        <v>410.4597791853211</v>
+        <v>409.4445029470865</v>
       </c>
       <c r="O39">
-        <v>82.09195583706422</v>
+        <v>81.8889005894173</v>
       </c>
       <c r="P39">
-        <v>328.3678233482568</v>
+        <v>327.5556023576692</v>
       </c>
       <c r="Q39">
-        <v>553.4678233482568</v>
+        <v>552.6556023576693</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.0964187610409222</v>
+        <v>0.09712410154173627</v>
       </c>
       <c r="T39">
-        <v>0.7830561346079511</v>
+        <v>0.7939675278303846</v>
       </c>
       <c r="U39">
         <v>0.06763097776675758</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>11.92659034829713</v>
+        <v>11.61273270755247</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08077676019697079</v>
+        <v>0.08079093151920037</v>
       </c>
       <c r="C40">
-        <v>1053.974733736294</v>
+        <v>1038.328370014548</v>
       </c>
       <c r="D40">
-        <v>1566.330733736294</v>
+        <v>1565.696370014549</v>
       </c>
       <c r="E40">
-        <v>-16.44400000000007</v>
+        <v>-1.432000000000016</v>
       </c>
       <c r="F40">
-        <v>570.4559999999999</v>
+        <v>585.468</v>
       </c>
       <c r="G40">
         <v>58.1</v>
@@ -4567,28 +4567,28 @@
         <v>448.025</v>
       </c>
       <c r="M40">
-        <v>38.58049705291346</v>
+        <v>39.59577329114803</v>
       </c>
       <c r="N40">
-        <v>409.4445029470865</v>
+        <v>408.429226708852</v>
       </c>
       <c r="O40">
-        <v>81.8889005894173</v>
+        <v>81.6858453417704</v>
       </c>
       <c r="P40">
-        <v>327.5556023576692</v>
+        <v>326.7433813670816</v>
       </c>
       <c r="Q40">
-        <v>552.6556023576693</v>
+        <v>551.8433813670815</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09712410154173627</v>
+        <v>0.09785256796060984</v>
       </c>
       <c r="T40">
-        <v>0.7939675278303846</v>
+        <v>0.8052366716502752</v>
       </c>
       <c r="U40">
         <v>0.06763097776675758</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>11.61273270755247</v>
+        <v>11.31497033043574</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08079093151920037</v>
+        <v>0.08080510284142994</v>
       </c>
       <c r="C41">
-        <v>1038.328370014548</v>
+        <v>1022.682519919217</v>
       </c>
       <c r="D41">
-        <v>1565.696370014549</v>
+        <v>1565.062519919217</v>
       </c>
       <c r="E41">
-        <v>-1.432000000000016</v>
+        <v>13.57999999999993</v>
       </c>
       <c r="F41">
-        <v>585.468</v>
+        <v>600.4799999999999</v>
       </c>
       <c r="G41">
         <v>58.1</v>
@@ -4649,28 +4649,28 @@
         <v>448.025</v>
       </c>
       <c r="M41">
-        <v>39.59577329114803</v>
+        <v>40.61104952938258</v>
       </c>
       <c r="N41">
-        <v>408.429226708852</v>
+        <v>407.4139504706174</v>
       </c>
       <c r="O41">
-        <v>81.6858453417704</v>
+        <v>81.48279009412349</v>
       </c>
       <c r="P41">
-        <v>326.7433813670816</v>
+        <v>325.9311603764939</v>
       </c>
       <c r="Q41">
-        <v>551.8433813670815</v>
+        <v>551.031160376494</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09785256796060984</v>
+        <v>0.09860531659344585</v>
       </c>
       <c r="T41">
-        <v>0.8052366716502752</v>
+        <v>0.8168814535974954</v>
       </c>
       <c r="U41">
         <v>0.06763097776675758</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>11.31497033043574</v>
+        <v>11.03209607217485</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08080510284142994</v>
+        <v>0.0808192741636595</v>
       </c>
       <c r="C42">
-        <v>1022.682519919217</v>
+        <v>1007.037182826748</v>
       </c>
       <c r="D42">
-        <v>1565.062519919217</v>
+        <v>1564.429182826748</v>
       </c>
       <c r="E42">
-        <v>13.57999999999993</v>
+        <v>28.59199999999998</v>
       </c>
       <c r="F42">
-        <v>600.4799999999999</v>
+        <v>615.492</v>
       </c>
       <c r="G42">
         <v>58.1</v>
@@ -4731,28 +4731,28 @@
         <v>448.025</v>
       </c>
       <c r="M42">
-        <v>40.61104952938258</v>
+        <v>41.62632576761715</v>
       </c>
       <c r="N42">
-        <v>407.4139504706174</v>
+        <v>406.3986742323828</v>
       </c>
       <c r="O42">
-        <v>81.48279009412349</v>
+        <v>81.27973484647657</v>
       </c>
       <c r="P42">
-        <v>325.9311603764939</v>
+        <v>325.1189393859062</v>
       </c>
       <c r="Q42">
-        <v>551.031160376494</v>
+        <v>550.2189393859062</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09860531659344585</v>
+        <v>0.09938358212908985</v>
       </c>
       <c r="T42">
-        <v>0.8168814535974954</v>
+        <v>0.8289209739158078</v>
       </c>
       <c r="U42">
         <v>0.06763097776675758</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>11.03209607217485</v>
+        <v>10.76302055821937</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0808192741636595</v>
+        <v>0.08083344548588905</v>
       </c>
       <c r="C43">
-        <v>1007.037182826748</v>
+        <v>991.3923581145999</v>
       </c>
       <c r="D43">
-        <v>1564.429182826748</v>
+        <v>1563.7963581146</v>
       </c>
       <c r="E43">
-        <v>28.59199999999998</v>
+        <v>43.60400000000004</v>
       </c>
       <c r="F43">
-        <v>615.492</v>
+        <v>630.504</v>
       </c>
       <c r="G43">
         <v>58.1</v>
@@ -4813,28 +4813,28 @@
         <v>448.025</v>
       </c>
       <c r="M43">
-        <v>41.62632576761715</v>
+        <v>42.64160200585172</v>
       </c>
       <c r="N43">
-        <v>406.3986742323828</v>
+        <v>405.3833979941483</v>
       </c>
       <c r="O43">
-        <v>81.27973484647657</v>
+        <v>81.07667959882966</v>
       </c>
       <c r="P43">
-        <v>325.1189393859062</v>
+        <v>324.3067183953186</v>
       </c>
       <c r="Q43">
-        <v>550.2189393859062</v>
+        <v>549.4067183953186</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09938358212908985</v>
+        <v>0.1001886844073423</v>
       </c>
       <c r="T43">
-        <v>0.8289209739158078</v>
+        <v>0.8413756501071655</v>
       </c>
       <c r="U43">
         <v>0.06763097776675758</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>10.76302055821937</v>
+        <v>10.50675816397605</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08083344548588907</v>
+        <v>0.08084761680811864</v>
       </c>
       <c r="C44">
-        <v>991.3923581145993</v>
+        <v>975.7480451612365</v>
       </c>
       <c r="D44">
-        <v>1563.796358114599</v>
+        <v>1563.164045161237</v>
       </c>
       <c r="E44">
-        <v>43.60399999999993</v>
+        <v>58.61599999999999</v>
       </c>
       <c r="F44">
-        <v>630.5039999999999</v>
+        <v>645.516</v>
       </c>
       <c r="G44">
         <v>58.1</v>
@@ -4895,28 +4895,28 @@
         <v>448.025</v>
       </c>
       <c r="M44">
-        <v>42.64160200585172</v>
+        <v>43.65687824408629</v>
       </c>
       <c r="N44">
-        <v>405.3833979941483</v>
+        <v>404.3681217559137</v>
       </c>
       <c r="O44">
-        <v>81.07667959882966</v>
+        <v>80.87362435118274</v>
       </c>
       <c r="P44">
-        <v>324.3067183953186</v>
+        <v>323.494497404731</v>
       </c>
       <c r="Q44">
-        <v>549.4067183953186</v>
+        <v>548.594497404731</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1001886844073423</v>
+        <v>0.1010220358883404</v>
       </c>
       <c r="T44">
-        <v>0.8413756501071653</v>
+        <v>0.854267332480676</v>
       </c>
       <c r="U44">
         <v>0.06763097776675758</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>10.50675816397605</v>
+        <v>10.26241495086033</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08084761680811864</v>
+        <v>0.08086178813034821</v>
       </c>
       <c r="C45">
-        <v>975.7480451612365</v>
+        <v>960.1042433461295</v>
       </c>
       <c r="D45">
-        <v>1563.164045161237</v>
+        <v>1562.532243346129</v>
       </c>
       <c r="E45">
-        <v>58.61599999999999</v>
+        <v>73.62799999999993</v>
       </c>
       <c r="F45">
-        <v>645.516</v>
+        <v>660.5279999999999</v>
       </c>
       <c r="G45">
         <v>58.1</v>
@@ -4977,28 +4977,28 @@
         <v>448.025</v>
       </c>
       <c r="M45">
-        <v>43.65687824408629</v>
+        <v>44.67215448232085</v>
       </c>
       <c r="N45">
-        <v>404.3681217559137</v>
+        <v>403.3528455176792</v>
       </c>
       <c r="O45">
-        <v>80.87362435118274</v>
+        <v>80.67056910353584</v>
       </c>
       <c r="P45">
-        <v>323.494497404731</v>
+        <v>322.6822764141433</v>
       </c>
       <c r="Q45">
-        <v>548.594497404731</v>
+        <v>547.7822764141433</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1010220358883404</v>
+        <v>0.1018851499222313</v>
       </c>
       <c r="T45">
-        <v>0.854267332480676</v>
+        <v>0.8676194320818118</v>
       </c>
       <c r="U45">
         <v>0.06763097776675758</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>10.26241495086033</v>
+        <v>10.02917824743168</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08086178813034821</v>
+        <v>0.08087595945257776</v>
       </c>
       <c r="C46">
-        <v>960.1042433461295</v>
+        <v>944.4609520497511</v>
       </c>
       <c r="D46">
-        <v>1562.532243346129</v>
+        <v>1561.900952049751</v>
       </c>
       <c r="E46">
-        <v>73.62799999999993</v>
+        <v>88.63999999999999</v>
       </c>
       <c r="F46">
-        <v>660.5279999999999</v>
+        <v>675.54</v>
       </c>
       <c r="G46">
         <v>58.1</v>
@@ -5059,28 +5059,28 @@
         <v>448.025</v>
       </c>
       <c r="M46">
-        <v>44.67215448232085</v>
+        <v>45.68743072055541</v>
       </c>
       <c r="N46">
-        <v>403.3528455176792</v>
+        <v>402.3375692794446</v>
       </c>
       <c r="O46">
-        <v>80.67056910353584</v>
+        <v>80.46751385588891</v>
       </c>
       <c r="P46">
-        <v>322.6822764141433</v>
+        <v>321.8700554235556</v>
       </c>
       <c r="Q46">
-        <v>547.7822764141433</v>
+        <v>546.9700554235557</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1018851499222313</v>
+        <v>0.102779649920991</v>
       </c>
       <c r="T46">
-        <v>0.8676194320818118</v>
+        <v>0.8814570625775345</v>
       </c>
       <c r="U46">
         <v>0.06763097776675758</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>10.02917824743168</v>
+        <v>9.806307619710978</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08087595945257776</v>
+        <v>0.08151573077480734</v>
       </c>
       <c r="C47">
-        <v>944.4609520497511</v>
+        <v>901.4708198484259</v>
       </c>
       <c r="D47">
-        <v>1561.900952049751</v>
+        <v>1533.922819848426</v>
       </c>
       <c r="E47">
-        <v>88.63999999999999</v>
+        <v>103.6519999999999</v>
       </c>
       <c r="F47">
-        <v>675.54</v>
+        <v>690.5519999999999</v>
       </c>
       <c r="G47">
         <v>58.1</v>
@@ -5141,45 +5141,45 @@
         <v>448.025</v>
       </c>
       <c r="M47">
-        <v>45.68743072055541</v>
+        <v>47.87664535878997</v>
       </c>
       <c r="N47">
-        <v>402.3375692794446</v>
+        <v>400.14835464121</v>
       </c>
       <c r="O47">
-        <v>80.46751385588891</v>
+        <v>80.02967092824201</v>
       </c>
       <c r="P47">
-        <v>321.8700554235556</v>
+        <v>320.118683712968</v>
       </c>
       <c r="Q47">
-        <v>546.9700554235557</v>
+        <v>545.218683712968</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.102779649920991</v>
+        <v>0.1037072795493343</v>
       </c>
       <c r="T47">
-        <v>0.8814570625775345</v>
+        <v>0.8958071979064322</v>
       </c>
       <c r="U47">
-        <v>0.06763097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V47">
         <v>0.2</v>
       </c>
       <c r="W47">
-        <v>0.05410478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>9.806307619710978</v>
+        <v>9.357902932473197</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08151573077480734</v>
+        <v>0.0815435020970369</v>
       </c>
       <c r="C48">
-        <v>901.4708198484259</v>
+        <v>885.267020992521</v>
       </c>
       <c r="D48">
-        <v>1533.922819848426</v>
+        <v>1532.731020992521</v>
       </c>
       <c r="E48">
-        <v>103.6519999999999</v>
+        <v>118.664</v>
       </c>
       <c r="F48">
-        <v>690.5519999999999</v>
+        <v>705.564</v>
       </c>
       <c r="G48">
         <v>58.1</v>
@@ -5223,28 +5223,28 @@
         <v>448.025</v>
       </c>
       <c r="M48">
-        <v>47.87664535878997</v>
+        <v>48.91744199702454</v>
       </c>
       <c r="N48">
-        <v>400.14835464121</v>
+        <v>399.1075580029755</v>
       </c>
       <c r="O48">
-        <v>80.02967092824201</v>
+        <v>79.8215116005951</v>
       </c>
       <c r="P48">
-        <v>320.118683712968</v>
+        <v>319.2860464023804</v>
       </c>
       <c r="Q48">
-        <v>545.218683712968</v>
+        <v>544.3860464023803</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1037072795493343</v>
+        <v>0.1046699140693133</v>
       </c>
       <c r="T48">
-        <v>0.8958071979064322</v>
+        <v>0.9106988477760428</v>
       </c>
       <c r="U48">
         <v>0.06933097776675758</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>9.357902932473197</v>
+        <v>9.158798614761002</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0815435020970369</v>
+        <v>0.08157127341926647</v>
       </c>
       <c r="C49">
-        <v>885.267020992521</v>
+        <v>869.0650726622969</v>
       </c>
       <c r="D49">
-        <v>1532.731020992521</v>
+        <v>1531.541072662297</v>
       </c>
       <c r="E49">
-        <v>118.664</v>
+        <v>133.676</v>
       </c>
       <c r="F49">
-        <v>705.564</v>
+        <v>720.576</v>
       </c>
       <c r="G49">
         <v>58.1</v>
@@ -5305,28 +5305,28 @@
         <v>448.025</v>
       </c>
       <c r="M49">
-        <v>48.91744199702454</v>
+        <v>49.95823863525911</v>
       </c>
       <c r="N49">
-        <v>399.1075580029755</v>
+        <v>398.0667613647408</v>
       </c>
       <c r="O49">
-        <v>79.8215116005951</v>
+        <v>79.61335227294818</v>
       </c>
       <c r="P49">
-        <v>319.2860464023804</v>
+        <v>318.4534090917927</v>
       </c>
       <c r="Q49">
-        <v>544.3860464023803</v>
+        <v>543.5534090917927</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1046699140693133</v>
+        <v>0.1056695729939068</v>
       </c>
       <c r="T49">
-        <v>0.9106988477760428</v>
+        <v>0.9261632534098694</v>
       </c>
       <c r="U49">
         <v>0.06933097776675758</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>9.158798614761002</v>
+        <v>8.967990310286812</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08157127341926647</v>
+        <v>0.08159904474149603</v>
       </c>
       <c r="C50">
-        <v>869.065072662297</v>
+        <v>852.864970551086</v>
       </c>
       <c r="D50">
-        <v>1531.541072662297</v>
+        <v>1530.352970551086</v>
       </c>
       <c r="E50">
-        <v>133.6759999999999</v>
+        <v>148.6879999999999</v>
       </c>
       <c r="F50">
-        <v>720.5759999999999</v>
+        <v>735.5879999999999</v>
       </c>
       <c r="G50">
         <v>58.1</v>
@@ -5387,28 +5387,28 @@
         <v>448.025</v>
       </c>
       <c r="M50">
-        <v>49.9582386352591</v>
+        <v>50.99903527349366</v>
       </c>
       <c r="N50">
-        <v>398.0667613647409</v>
+        <v>397.0259647265063</v>
       </c>
       <c r="O50">
-        <v>79.61335227294819</v>
+        <v>79.40519294530128</v>
       </c>
       <c r="P50">
-        <v>318.4534090917927</v>
+        <v>317.6207717812051</v>
       </c>
       <c r="Q50">
-        <v>543.5534090917927</v>
+        <v>542.720771781205</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1056695729939068</v>
+        <v>0.1067084342292687</v>
       </c>
       <c r="T50">
-        <v>0.9261632534098694</v>
+        <v>0.9422341063234537</v>
       </c>
       <c r="U50">
         <v>0.06933097776675758</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>8.967990310286815</v>
+        <v>8.784970099872799</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08159904474149603</v>
+        <v>0.08162681606372559</v>
       </c>
       <c r="C51">
-        <v>852.864970551086</v>
+        <v>836.6667103655718</v>
       </c>
       <c r="D51">
-        <v>1530.352970551086</v>
+        <v>1529.166710365572</v>
       </c>
       <c r="E51">
-        <v>148.6879999999999</v>
+        <v>163.6999999999999</v>
       </c>
       <c r="F51">
-        <v>735.5879999999999</v>
+        <v>750.5999999999999</v>
       </c>
       <c r="G51">
         <v>58.1</v>
@@ -5469,28 +5469,28 @@
         <v>448.025</v>
       </c>
       <c r="M51">
-        <v>50.99903527349366</v>
+        <v>52.03983191172823</v>
       </c>
       <c r="N51">
-        <v>397.0259647265063</v>
+        <v>395.9851680882717</v>
       </c>
       <c r="O51">
-        <v>79.40519294530128</v>
+        <v>79.19703361765436</v>
       </c>
       <c r="P51">
-        <v>317.6207717812051</v>
+        <v>316.7881344706174</v>
       </c>
       <c r="Q51">
-        <v>542.720771781205</v>
+        <v>541.8881344706174</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1067084342292687</v>
+        <v>0.1077888499140451</v>
       </c>
       <c r="T51">
-        <v>0.9422341063234537</v>
+        <v>0.9589477933535815</v>
       </c>
       <c r="U51">
         <v>0.06933097776675758</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>8.784970099872799</v>
+        <v>8.609270697875342</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08162681606372559</v>
+        <v>0.08165458738595516</v>
       </c>
       <c r="C52">
-        <v>836.6667103655718</v>
+        <v>820.4702878257398</v>
       </c>
       <c r="D52">
-        <v>1529.166710365572</v>
+        <v>1527.98228782574</v>
       </c>
       <c r="E52">
-        <v>163.6999999999999</v>
+        <v>178.712</v>
       </c>
       <c r="F52">
-        <v>750.5999999999999</v>
+        <v>765.612</v>
       </c>
       <c r="G52">
         <v>58.1</v>
@@ -5551,28 +5551,28 @@
         <v>448.025</v>
       </c>
       <c r="M52">
-        <v>52.03983191172823</v>
+        <v>53.0806285499628</v>
       </c>
       <c r="N52">
-        <v>395.9851680882717</v>
+        <v>394.9443714500372</v>
       </c>
       <c r="O52">
-        <v>79.19703361765436</v>
+        <v>78.98887429000744</v>
       </c>
       <c r="P52">
-        <v>316.7881344706174</v>
+        <v>315.9554971600297</v>
       </c>
       <c r="Q52">
-        <v>541.8881344706174</v>
+        <v>541.0554971600297</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1077888499140451</v>
+        <v>0.1089133641982001</v>
       </c>
       <c r="T52">
-        <v>0.9589477933535815</v>
+        <v>0.9763436716910615</v>
       </c>
       <c r="U52">
         <v>0.06933097776675758</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>8.609270697875342</v>
+        <v>8.440461468505237</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08165458738595516</v>
+        <v>0.08168235870818472</v>
       </c>
       <c r="C53">
-        <v>820.4702878257398</v>
+        <v>804.2756986648277</v>
       </c>
       <c r="D53">
-        <v>1527.98228782574</v>
+        <v>1526.799698664828</v>
       </c>
       <c r="E53">
-        <v>178.712</v>
+        <v>193.7239999999999</v>
       </c>
       <c r="F53">
-        <v>765.612</v>
+        <v>780.6239999999999</v>
       </c>
       <c r="G53">
         <v>58.1</v>
@@ -5633,28 +5633,28 @@
         <v>448.025</v>
       </c>
       <c r="M53">
-        <v>53.0806285499628</v>
+        <v>54.12142518819736</v>
       </c>
       <c r="N53">
-        <v>394.9443714500372</v>
+        <v>393.9035748118026</v>
       </c>
       <c r="O53">
-        <v>78.98887429000744</v>
+        <v>78.78071496236053</v>
       </c>
       <c r="P53">
-        <v>315.9554971600297</v>
+        <v>315.1228598494421</v>
       </c>
       <c r="Q53">
-        <v>541.0554971600297</v>
+        <v>540.2228598494421</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1089133641982001</v>
+        <v>0.1100847332441949</v>
       </c>
       <c r="T53">
-        <v>0.9763436716910615</v>
+        <v>0.994464378292603</v>
       </c>
       <c r="U53">
         <v>0.06933097776675758</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>8.440461468505237</v>
+        <v>8.278144901803213</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08168235870818472</v>
+        <v>0.08171013003041429</v>
       </c>
       <c r="C54">
-        <v>804.2756986648277</v>
+        <v>788.0829386292687</v>
       </c>
       <c r="D54">
-        <v>1526.799698664828</v>
+        <v>1525.618938629269</v>
       </c>
       <c r="E54">
-        <v>193.7239999999999</v>
+        <v>208.736</v>
       </c>
       <c r="F54">
-        <v>780.6239999999999</v>
+        <v>795.636</v>
       </c>
       <c r="G54">
         <v>58.1</v>
@@ -5715,28 +5715,28 @@
         <v>448.025</v>
       </c>
       <c r="M54">
-        <v>54.12142518819736</v>
+        <v>55.16222182643193</v>
       </c>
       <c r="N54">
-        <v>393.9035748118026</v>
+        <v>392.862778173568</v>
       </c>
       <c r="O54">
-        <v>78.78071496236053</v>
+        <v>78.57255563471361</v>
       </c>
       <c r="P54">
-        <v>315.1228598494421</v>
+        <v>314.2902225388544</v>
       </c>
       <c r="Q54">
-        <v>540.2228598494421</v>
+        <v>539.3902225388545</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1100847332441949</v>
+        <v>0.1113059477815087</v>
       </c>
       <c r="T54">
-        <v>0.994464378292603</v>
+        <v>1.013356178792083</v>
       </c>
       <c r="U54">
         <v>0.06933097776675758</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>8.278144901803213</v>
+        <v>8.12195348856164</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08171013003041429</v>
+        <v>0.08173790135264385</v>
       </c>
       <c r="C55">
-        <v>788.0829386292687</v>
+        <v>771.8920034786474</v>
       </c>
       <c r="D55">
-        <v>1525.618938629269</v>
+        <v>1524.440003478647</v>
       </c>
       <c r="E55">
-        <v>208.736</v>
+        <v>223.7479999999999</v>
       </c>
       <c r="F55">
-        <v>795.636</v>
+        <v>810.6479999999999</v>
       </c>
       <c r="G55">
         <v>58.1</v>
@@ -5797,28 +5797,28 @@
         <v>448.025</v>
       </c>
       <c r="M55">
-        <v>55.16222182643193</v>
+        <v>56.20301846466649</v>
       </c>
       <c r="N55">
-        <v>392.862778173568</v>
+        <v>391.8219815353335</v>
       </c>
       <c r="O55">
-        <v>78.57255563471361</v>
+        <v>78.3643963070667</v>
       </c>
       <c r="P55">
-        <v>314.2902225388544</v>
+        <v>313.4575852282668</v>
       </c>
       <c r="Q55">
-        <v>539.3902225388545</v>
+        <v>538.5575852282668</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1113059477815087</v>
+        <v>0.1125802586030534</v>
       </c>
       <c r="T55">
-        <v>1.013356178792083</v>
+        <v>1.033069361921974</v>
       </c>
       <c r="U55">
         <v>0.06933097776675758</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>8.12195348856164</v>
+        <v>7.971546942477167</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08173790135264385</v>
+        <v>0.08176567267487342</v>
       </c>
       <c r="C56">
-        <v>771.8920034786474</v>
+        <v>755.7028889856427</v>
       </c>
       <c r="D56">
-        <v>1524.440003478647</v>
+        <v>1523.262888985643</v>
       </c>
       <c r="E56">
-        <v>223.7479999999999</v>
+        <v>238.76</v>
       </c>
       <c r="F56">
-        <v>810.6479999999999</v>
+        <v>825.66</v>
       </c>
       <c r="G56">
         <v>58.1</v>
@@ -5879,28 +5879,28 @@
         <v>448.025</v>
       </c>
       <c r="M56">
-        <v>56.20301846466649</v>
+        <v>57.24381510290106</v>
       </c>
       <c r="N56">
-        <v>391.8219815353335</v>
+        <v>390.7811848970989</v>
       </c>
       <c r="O56">
-        <v>78.3643963070667</v>
+        <v>78.15623697941979</v>
       </c>
       <c r="P56">
-        <v>313.4575852282668</v>
+        <v>312.6249479176792</v>
       </c>
       <c r="Q56">
-        <v>538.5575852282668</v>
+        <v>537.7249479176792</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1125802586030534</v>
+        <v>0.1139112054611113</v>
       </c>
       <c r="T56">
-        <v>1.033069361921974</v>
+        <v>1.053658686524306</v>
       </c>
       <c r="U56">
         <v>0.06933097776675758</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>7.971546942477167</v>
+        <v>7.826609725341219</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08176567267487342</v>
+        <v>0.08179344399710299</v>
       </c>
       <c r="C57">
-        <v>755.7028889856427</v>
+        <v>739.5155909359821</v>
       </c>
       <c r="D57">
-        <v>1523.262888985643</v>
+        <v>1522.087590935982</v>
       </c>
       <c r="E57">
-        <v>238.76</v>
+        <v>253.772</v>
       </c>
       <c r="F57">
-        <v>825.66</v>
+        <v>840.672</v>
       </c>
       <c r="G57">
         <v>58.1</v>
@@ -5961,28 +5961,28 @@
         <v>448.025</v>
       </c>
       <c r="M57">
-        <v>57.24381510290106</v>
+        <v>58.28461174113563</v>
       </c>
       <c r="N57">
-        <v>390.7811848970989</v>
+        <v>389.7403882588644</v>
       </c>
       <c r="O57">
-        <v>78.15623697941979</v>
+        <v>77.94807765177288</v>
       </c>
       <c r="P57">
-        <v>312.6249479176792</v>
+        <v>311.7923106070915</v>
       </c>
       <c r="Q57">
-        <v>537.7249479176792</v>
+        <v>536.8923106070915</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1139112054611113</v>
+        <v>0.1153026499036263</v>
       </c>
       <c r="T57">
-        <v>1.053658686524306</v>
+        <v>1.075183889517652</v>
       </c>
       <c r="U57">
         <v>0.06933097776675758</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>7.826609725341219</v>
+        <v>7.686848837388697</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08179344399710299</v>
+        <v>0.08218601531933256</v>
       </c>
       <c r="C58">
-        <v>739.5155909359821</v>
+        <v>708.0816790316719</v>
       </c>
       <c r="D58">
-        <v>1522.087590935982</v>
+        <v>1505.665679031672</v>
       </c>
       <c r="E58">
-        <v>253.772</v>
+        <v>268.784</v>
       </c>
       <c r="F58">
-        <v>840.672</v>
+        <v>855.684</v>
       </c>
       <c r="G58">
         <v>58.1</v>
@@ -6043,45 +6043,45 @@
         <v>448.025</v>
       </c>
       <c r="M58">
-        <v>58.28461174113563</v>
+        <v>60.00995557937019</v>
       </c>
       <c r="N58">
-        <v>389.7403882588644</v>
+        <v>388.0150444206298</v>
       </c>
       <c r="O58">
-        <v>77.94807765177288</v>
+        <v>77.60300888412597</v>
       </c>
       <c r="P58">
-        <v>311.7923106070915</v>
+        <v>310.4120355365038</v>
       </c>
       <c r="Q58">
-        <v>536.8923106070915</v>
+        <v>535.5120355365038</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1153026499036263</v>
+        <v>0.1167588126923049</v>
       </c>
       <c r="T58">
-        <v>1.075183889517652</v>
+        <v>1.097710264743247</v>
       </c>
       <c r="U58">
-        <v>0.06933097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V58">
         <v>0.2</v>
       </c>
       <c r="W58">
-        <v>0.05546478221340606</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y58">
-        <v>7.686848837388697</v>
+        <v>7.465844553199751</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08218601531933256</v>
+        <v>0.08222018664156212</v>
       </c>
       <c r="C59">
-        <v>708.0816790316719</v>
+        <v>691.6569848136397</v>
       </c>
       <c r="D59">
-        <v>1505.665679031672</v>
+        <v>1504.25298481364</v>
       </c>
       <c r="E59">
-        <v>268.784</v>
+        <v>283.796</v>
       </c>
       <c r="F59">
-        <v>855.684</v>
+        <v>870.696</v>
       </c>
       <c r="G59">
         <v>58.1</v>
@@ -6125,28 +6125,28 @@
         <v>448.025</v>
       </c>
       <c r="M59">
-        <v>60.00995557937019</v>
+        <v>61.06276181760477</v>
       </c>
       <c r="N59">
-        <v>388.0150444206298</v>
+        <v>386.9622381823952</v>
       </c>
       <c r="O59">
-        <v>77.60300888412597</v>
+        <v>77.39244763647905</v>
       </c>
       <c r="P59">
-        <v>310.4120355365038</v>
+        <v>309.5697905459161</v>
       </c>
       <c r="Q59">
-        <v>535.5120355365038</v>
+        <v>534.6697905459162</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1167588126923049</v>
+        <v>0.1182843165661586</v>
       </c>
       <c r="T59">
-        <v>1.097710264743247</v>
+        <v>1.121309324503394</v>
       </c>
       <c r="U59">
         <v>0.07013097776675759</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>7.465844553199751</v>
+        <v>7.337123095385961</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08222018664156211</v>
+        <v>0.0822543579637917</v>
       </c>
       <c r="C60">
-        <v>691.6569848136406</v>
+        <v>675.2349390377708</v>
       </c>
       <c r="D60">
-        <v>1504.252984813641</v>
+        <v>1502.842939037771</v>
       </c>
       <c r="E60">
-        <v>283.7959999999998</v>
+        <v>298.8079999999999</v>
       </c>
       <c r="F60">
-        <v>870.6959999999998</v>
+        <v>885.7079999999999</v>
       </c>
       <c r="G60">
         <v>58.1</v>
@@ -6207,28 +6207,28 @@
         <v>448.025</v>
       </c>
       <c r="M60">
-        <v>61.06276181760474</v>
+        <v>62.11556805583932</v>
       </c>
       <c r="N60">
-        <v>386.9622381823953</v>
+        <v>385.9094319441606</v>
       </c>
       <c r="O60">
-        <v>77.39244763647906</v>
+        <v>77.18188638883214</v>
       </c>
       <c r="P60">
-        <v>309.5697905459162</v>
+        <v>308.7275455553285</v>
       </c>
       <c r="Q60">
-        <v>534.6697905459162</v>
+        <v>533.8275455553285</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1182843165661586</v>
+        <v>0.1198842352631271</v>
       </c>
       <c r="T60">
-        <v>1.121309324503394</v>
+        <v>1.146059557910378</v>
       </c>
       <c r="U60">
         <v>0.07013097776675759</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>7.337123095385964</v>
+        <v>7.212765076820099</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0822543579637917</v>
+        <v>0.08228852928602126</v>
       </c>
       <c r="C61">
-        <v>675.2349390377708</v>
+        <v>658.8155342633078</v>
       </c>
       <c r="D61">
-        <v>1502.842939037771</v>
+        <v>1501.435534263308</v>
       </c>
       <c r="E61">
-        <v>298.8079999999999</v>
+        <v>313.8199999999999</v>
       </c>
       <c r="F61">
-        <v>885.7079999999999</v>
+        <v>900.7199999999999</v>
       </c>
       <c r="G61">
         <v>58.1</v>
@@ -6289,28 +6289,28 @@
         <v>448.025</v>
       </c>
       <c r="M61">
-        <v>62.11556805583932</v>
+        <v>63.16837429407389</v>
       </c>
       <c r="N61">
-        <v>385.9094319441606</v>
+        <v>384.8566257059261</v>
       </c>
       <c r="O61">
-        <v>77.18188638883214</v>
+        <v>76.97132514118522</v>
       </c>
       <c r="P61">
-        <v>308.7275455553285</v>
+        <v>307.8853005647409</v>
       </c>
       <c r="Q61">
-        <v>533.8275455553285</v>
+        <v>532.9853005647409</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1198842352631271</v>
+        <v>0.121564149894944</v>
       </c>
       <c r="T61">
-        <v>1.146059557910378</v>
+        <v>1.172047302987711</v>
       </c>
       <c r="U61">
         <v>0.07013097776675759</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>7.212765076820099</v>
+        <v>7.092552325539764</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08228852928602126</v>
+        <v>0.08232270060825082</v>
       </c>
       <c r="C62">
-        <v>658.8155342633078</v>
+        <v>642.3987630773389</v>
       </c>
       <c r="D62">
-        <v>1501.435534263308</v>
+        <v>1500.030763077339</v>
       </c>
       <c r="E62">
-        <v>313.8199999999999</v>
+        <v>328.8319999999999</v>
       </c>
       <c r="F62">
-        <v>900.7199999999999</v>
+        <v>915.7319999999999</v>
       </c>
       <c r="G62">
         <v>58.1</v>
@@ -6371,28 +6371,28 @@
         <v>448.025</v>
       </c>
       <c r="M62">
-        <v>63.16837429407389</v>
+        <v>64.22118053230845</v>
       </c>
       <c r="N62">
-        <v>384.8566257059261</v>
+        <v>383.8038194676915</v>
       </c>
       <c r="O62">
-        <v>76.97132514118522</v>
+        <v>76.76076389353831</v>
       </c>
       <c r="P62">
-        <v>307.8853005647409</v>
+        <v>307.0430555741532</v>
       </c>
       <c r="Q62">
-        <v>532.9853005647409</v>
+        <v>532.1430555741533</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.121564149894944</v>
+        <v>0.1233302139950593</v>
       </c>
       <c r="T62">
-        <v>1.172047302987711</v>
+        <v>1.199367752940804</v>
       </c>
       <c r="U62">
         <v>0.07013097776675759</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>7.092552325539764</v>
+        <v>6.976280975940751</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08232270060825082</v>
+        <v>0.08235687193048039</v>
       </c>
       <c r="C63">
-        <v>642.3987630773389</v>
+        <v>625.9846180946709</v>
       </c>
       <c r="D63">
-        <v>1500.030763077339</v>
+        <v>1498.628618094671</v>
       </c>
       <c r="E63">
-        <v>328.8319999999999</v>
+        <v>343.8439999999999</v>
       </c>
       <c r="F63">
-        <v>915.7319999999999</v>
+        <v>930.7439999999999</v>
       </c>
       <c r="G63">
         <v>58.1</v>
@@ -6453,28 +6453,28 @@
         <v>448.025</v>
       </c>
       <c r="M63">
-        <v>64.22118053230845</v>
+        <v>65.27398677054302</v>
       </c>
       <c r="N63">
-        <v>383.8038194676915</v>
+        <v>382.7510132294569</v>
       </c>
       <c r="O63">
-        <v>76.76076389353831</v>
+        <v>76.55020264589139</v>
       </c>
       <c r="P63">
-        <v>307.0430555741532</v>
+        <v>306.2008105835656</v>
       </c>
       <c r="Q63">
-        <v>532.1430555741533</v>
+        <v>531.3008105835656</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1233302139950593</v>
+        <v>0.1251892288372859</v>
       </c>
       <c r="T63">
-        <v>1.199367752940804</v>
+        <v>1.228126121312482</v>
       </c>
       <c r="U63">
         <v>0.07013097776675759</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>6.976280975940751</v>
+        <v>6.863760315038481</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08235687193048039</v>
+        <v>0.08239104325270996</v>
       </c>
       <c r="C64">
-        <v>625.9846180946709</v>
+        <v>609.5730919576949</v>
       </c>
       <c r="D64">
-        <v>1498.628618094671</v>
+        <v>1497.229091957695</v>
       </c>
       <c r="E64">
-        <v>343.8439999999999</v>
+        <v>358.8559999999999</v>
       </c>
       <c r="F64">
-        <v>930.7439999999999</v>
+        <v>945.7559999999999</v>
       </c>
       <c r="G64">
         <v>58.1</v>
@@ -6535,28 +6535,28 @@
         <v>448.025</v>
       </c>
       <c r="M64">
-        <v>65.27398677054302</v>
+        <v>66.32679300877757</v>
       </c>
       <c r="N64">
-        <v>382.7510132294569</v>
+        <v>381.6982069912224</v>
       </c>
       <c r="O64">
-        <v>76.55020264589139</v>
+        <v>76.33964139824448</v>
       </c>
       <c r="P64">
-        <v>306.2008105835656</v>
+        <v>305.3585655929779</v>
       </c>
       <c r="Q64">
-        <v>531.3008105835656</v>
+        <v>530.4585655929779</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1251892288372859</v>
+        <v>0.1271487309682814</v>
       </c>
       <c r="T64">
-        <v>1.228126121312482</v>
+        <v>1.258438996082628</v>
       </c>
       <c r="U64">
         <v>0.07013097776675759</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>6.863760315038481</v>
+        <v>6.754811738609299</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08239104325270996</v>
+        <v>0.08242521457493951</v>
       </c>
       <c r="C65">
-        <v>609.5730919576949</v>
+        <v>593.164177336265</v>
       </c>
       <c r="D65">
-        <v>1497.229091957695</v>
+        <v>1495.832177336265</v>
       </c>
       <c r="E65">
-        <v>358.8559999999999</v>
+        <v>373.8679999999999</v>
       </c>
       <c r="F65">
-        <v>945.7559999999999</v>
+        <v>960.7679999999999</v>
       </c>
       <c r="G65">
         <v>58.1</v>
@@ -6617,28 +6617,28 @@
         <v>448.025</v>
       </c>
       <c r="M65">
-        <v>66.32679300877757</v>
+        <v>67.37959924701215</v>
       </c>
       <c r="N65">
-        <v>381.6982069912224</v>
+        <v>380.6454007529878</v>
       </c>
       <c r="O65">
-        <v>76.33964139824448</v>
+        <v>76.12908015059757</v>
       </c>
       <c r="P65">
-        <v>305.3585655929779</v>
+        <v>304.5163206023902</v>
       </c>
       <c r="Q65">
-        <v>530.4585655929779</v>
+        <v>529.6163206023903</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1271487309682814</v>
+        <v>0.1292170943287768</v>
       </c>
       <c r="T65">
-        <v>1.258438996082628</v>
+        <v>1.290435919451116</v>
       </c>
       <c r="U65">
         <v>0.07013097776675759</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>6.754811738609299</v>
+        <v>6.649267805193528</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08242521457493951</v>
+        <v>0.08245938589716909</v>
       </c>
       <c r="C66">
-        <v>593.164177336265</v>
+        <v>576.7578669275612</v>
       </c>
       <c r="D66">
-        <v>1495.832177336265</v>
+        <v>1494.437866927561</v>
       </c>
       <c r="E66">
-        <v>373.8679999999999</v>
+        <v>388.8799999999999</v>
       </c>
       <c r="F66">
-        <v>960.7679999999999</v>
+        <v>975.7799999999999</v>
       </c>
       <c r="G66">
         <v>58.1</v>
@@ -6699,28 +6699,28 @@
         <v>448.025</v>
       </c>
       <c r="M66">
-        <v>67.37959924701215</v>
+        <v>68.4324054852467</v>
       </c>
       <c r="N66">
-        <v>380.6454007529878</v>
+        <v>379.5925945147533</v>
       </c>
       <c r="O66">
-        <v>76.12908015059757</v>
+        <v>75.91851890295065</v>
       </c>
       <c r="P66">
-        <v>304.5163206023902</v>
+        <v>303.6740756118026</v>
       </c>
       <c r="Q66">
-        <v>529.6163206023903</v>
+        <v>528.7740756118026</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1292170943287768</v>
+        <v>0.1314036498813004</v>
       </c>
       <c r="T66">
-        <v>1.290435919451116</v>
+        <v>1.32426123844066</v>
       </c>
       <c r="U66">
         <v>0.07013097776675759</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>6.649267805193528</v>
+        <v>6.546971377421321</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08245938589716909</v>
+        <v>0.08249355721939866</v>
       </c>
       <c r="C67">
-        <v>576.7578669275612</v>
+        <v>560.354153455969</v>
       </c>
       <c r="D67">
-        <v>1494.437866927561</v>
+        <v>1493.046153455969</v>
       </c>
       <c r="E67">
-        <v>388.8799999999999</v>
+        <v>403.8919999999999</v>
       </c>
       <c r="F67">
-        <v>975.7799999999999</v>
+        <v>990.7919999999999</v>
       </c>
       <c r="G67">
         <v>58.1</v>
@@ -6781,28 +6781,28 @@
         <v>448.025</v>
       </c>
       <c r="M67">
-        <v>68.4324054852467</v>
+        <v>69.48521172348127</v>
       </c>
       <c r="N67">
-        <v>379.5925945147533</v>
+        <v>378.5397882765187</v>
       </c>
       <c r="O67">
-        <v>75.91851890295065</v>
+        <v>75.70795765530374</v>
       </c>
       <c r="P67">
-        <v>303.6740756118026</v>
+        <v>302.831830621215</v>
       </c>
       <c r="Q67">
-        <v>528.7740756118026</v>
+        <v>527.931830621215</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1314036498813004</v>
+        <v>0.1337188263486784</v>
       </c>
       <c r="T67">
-        <v>1.32426123844066</v>
+        <v>1.360076282076648</v>
       </c>
       <c r="U67">
         <v>0.07013097776675759</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>6.546971377421321</v>
+        <v>6.447774841399786</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08249355721939866</v>
+        <v>0.08252772854162822</v>
       </c>
       <c r="C68">
-        <v>560.354153455969</v>
+        <v>543.9530296729525</v>
       </c>
       <c r="D68">
-        <v>1493.046153455969</v>
+        <v>1491.657029672953</v>
       </c>
       <c r="E68">
-        <v>403.8919999999999</v>
+        <v>418.904</v>
       </c>
       <c r="F68">
-        <v>990.7919999999999</v>
+        <v>1005.804</v>
       </c>
       <c r="G68">
         <v>58.1</v>
@@ -6863,28 +6863,28 @@
         <v>448.025</v>
       </c>
       <c r="M68">
-        <v>69.48521172348127</v>
+        <v>70.53801796171584</v>
       </c>
       <c r="N68">
-        <v>378.5397882765187</v>
+        <v>377.4869820382842</v>
       </c>
       <c r="O68">
-        <v>75.70795765530374</v>
+        <v>75.49739640765684</v>
       </c>
       <c r="P68">
-        <v>302.831830621215</v>
+        <v>301.9895856306273</v>
       </c>
       <c r="Q68">
-        <v>527.931830621215</v>
+        <v>527.0895856306274</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1337188263486784</v>
+        <v>0.136174316541352</v>
       </c>
       <c r="T68">
-        <v>1.360076282076648</v>
+        <v>1.398061934417848</v>
       </c>
       <c r="U68">
         <v>0.07013097776675759</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>6.447774841399786</v>
+        <v>6.35153939600576</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08252772854162822</v>
+        <v>0.08256189986385779</v>
       </c>
       <c r="C69">
-        <v>543.9530296729525</v>
+        <v>527.554488356924</v>
       </c>
       <c r="D69">
-        <v>1491.657029672953</v>
+        <v>1490.270488356924</v>
       </c>
       <c r="E69">
-        <v>418.904</v>
+        <v>433.9159999999999</v>
       </c>
       <c r="F69">
-        <v>1005.804</v>
+        <v>1020.816</v>
       </c>
       <c r="G69">
         <v>58.1</v>
@@ -6945,28 +6945,28 @@
         <v>448.025</v>
       </c>
       <c r="M69">
-        <v>70.53801796171584</v>
+        <v>71.5908241999504</v>
       </c>
       <c r="N69">
-        <v>377.4869820382842</v>
+        <v>376.4341758000496</v>
       </c>
       <c r="O69">
-        <v>75.49739640765684</v>
+        <v>75.28683516000991</v>
       </c>
       <c r="P69">
-        <v>301.9895856306273</v>
+        <v>301.1473406400397</v>
       </c>
       <c r="Q69">
-        <v>527.0895856306274</v>
+        <v>526.2473406400397</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.136174316541352</v>
+        <v>0.1387832748710677</v>
       </c>
       <c r="T69">
-        <v>1.398061934417848</v>
+        <v>1.438421690030372</v>
       </c>
       <c r="U69">
         <v>0.07013097776675759</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>6.35153939600576</v>
+        <v>6.258134404888026</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08256189986385779</v>
+        <v>0.08259607118608735</v>
       </c>
       <c r="C70">
-        <v>527.554488356924</v>
+        <v>511.1585223131221</v>
       </c>
       <c r="D70">
-        <v>1490.270488356924</v>
+        <v>1488.886522313122</v>
       </c>
       <c r="E70">
-        <v>433.9159999999999</v>
+        <v>448.928</v>
       </c>
       <c r="F70">
-        <v>1020.816</v>
+        <v>1035.828</v>
       </c>
       <c r="G70">
         <v>58.1</v>
@@ -7027,28 +7027,28 @@
         <v>448.025</v>
       </c>
       <c r="M70">
-        <v>71.5908241999504</v>
+        <v>72.64363043818497</v>
       </c>
       <c r="N70">
-        <v>376.4341758000496</v>
+        <v>375.381369561815</v>
       </c>
       <c r="O70">
-        <v>75.28683516000991</v>
+        <v>75.07627391236301</v>
       </c>
       <c r="P70">
-        <v>301.1473406400397</v>
+        <v>300.305095649452</v>
       </c>
       <c r="Q70">
-        <v>526.2473406400397</v>
+        <v>525.4050956494521</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1387832748710677</v>
+        <v>0.1415605530930231</v>
       </c>
       <c r="T70">
-        <v>1.438421690030372</v>
+        <v>1.481385300843705</v>
       </c>
       <c r="U70">
         <v>0.07013097776675759</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>6.258134404888026</v>
+        <v>6.167436804817186</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08259607118608735</v>
+        <v>0.08319024250831691</v>
       </c>
       <c r="C71">
-        <v>511.1585223131221</v>
+        <v>472.486507981421</v>
       </c>
       <c r="D71">
-        <v>1488.886522313122</v>
+        <v>1465.226507981421</v>
       </c>
       <c r="E71">
-        <v>448.928</v>
+        <v>463.9399999999999</v>
       </c>
       <c r="F71">
-        <v>1035.828</v>
+        <v>1050.84</v>
       </c>
       <c r="G71">
         <v>58.1</v>
@@ -7109,45 +7109,45 @@
         <v>448.025</v>
       </c>
       <c r="M71">
-        <v>72.64363043818497</v>
+        <v>74.74727667641953</v>
       </c>
       <c r="N71">
-        <v>375.381369561815</v>
+        <v>373.2777233235805</v>
       </c>
       <c r="O71">
-        <v>75.07627391236301</v>
+        <v>74.65554466471609</v>
       </c>
       <c r="P71">
-        <v>300.305095649452</v>
+        <v>298.6221786588644</v>
       </c>
       <c r="Q71">
-        <v>525.4050956494521</v>
+        <v>523.7221786588643</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1415605530930231</v>
+        <v>0.1445229831964422</v>
       </c>
       <c r="T71">
-        <v>1.481385300843705</v>
+        <v>1.527213152377926</v>
       </c>
       <c r="U71">
-        <v>0.07013097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V71">
         <v>0.2</v>
       </c>
       <c r="W71">
-        <v>0.05610478221340607</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y71">
-        <v>6.167436804817186</v>
+        <v>5.993863855930127</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08319024250831691</v>
+        <v>0.0832324138305465</v>
       </c>
       <c r="C72">
-        <v>472.486507981421</v>
+        <v>455.8237851750548</v>
       </c>
       <c r="D72">
-        <v>1465.226507981421</v>
+        <v>1463.575785175055</v>
       </c>
       <c r="E72">
-        <v>463.9399999999999</v>
+        <v>478.9520000000001</v>
       </c>
       <c r="F72">
-        <v>1050.84</v>
+        <v>1065.852</v>
       </c>
       <c r="G72">
         <v>58.1</v>
@@ -7191,28 +7191,28 @@
         <v>448.025</v>
       </c>
       <c r="M72">
-        <v>74.74727667641953</v>
+        <v>75.81509491465411</v>
       </c>
       <c r="N72">
-        <v>373.2777233235805</v>
+        <v>372.2099050853459</v>
       </c>
       <c r="O72">
-        <v>74.65554466471609</v>
+        <v>74.44198101706918</v>
       </c>
       <c r="P72">
-        <v>298.6221786588644</v>
+        <v>297.7679240682767</v>
       </c>
       <c r="Q72">
-        <v>523.7221786588643</v>
+        <v>522.8679240682768</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1445229831964422</v>
+        <v>0.1476897188242351</v>
       </c>
       <c r="T72">
-        <v>1.527213152377926</v>
+        <v>1.576201545397267</v>
       </c>
       <c r="U72">
         <v>0.07113097776675759</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.993863855930127</v>
+        <v>5.909443238240969</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08323241383054648</v>
+        <v>0.08327458515277605</v>
       </c>
       <c r="C73">
-        <v>455.8237851750557</v>
+        <v>439.1647775886504</v>
       </c>
       <c r="D73">
-        <v>1463.575785175056</v>
+        <v>1461.92877758865</v>
       </c>
       <c r="E73">
-        <v>478.9519999999999</v>
+        <v>493.9639999999998</v>
       </c>
       <c r="F73">
-        <v>1065.852</v>
+        <v>1080.864</v>
       </c>
       <c r="G73">
         <v>58.1</v>
@@ -7273,28 +7273,28 @@
         <v>448.025</v>
       </c>
       <c r="M73">
-        <v>75.8150949146541</v>
+        <v>76.88291315288866</v>
       </c>
       <c r="N73">
-        <v>372.2099050853459</v>
+        <v>371.1420868471113</v>
       </c>
       <c r="O73">
-        <v>74.44198101706918</v>
+        <v>74.22841736942227</v>
       </c>
       <c r="P73">
-        <v>297.7679240682767</v>
+        <v>296.913669477689</v>
       </c>
       <c r="Q73">
-        <v>522.8679240682768</v>
+        <v>522.0136694776891</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1476897188242351</v>
+        <v>0.1510826498540131</v>
       </c>
       <c r="T73">
-        <v>1.576201545397266</v>
+        <v>1.628689109346559</v>
       </c>
       <c r="U73">
         <v>0.07113097776675759</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.90944323824097</v>
+        <v>5.827367637709846</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08327458515277605</v>
+        <v>0.08331675647500561</v>
       </c>
       <c r="C74">
-        <v>439.1647775886504</v>
+        <v>422.5094726937448</v>
       </c>
       <c r="D74">
-        <v>1461.92877758865</v>
+        <v>1460.285472693745</v>
       </c>
       <c r="E74">
-        <v>493.9639999999998</v>
+        <v>508.9759999999998</v>
       </c>
       <c r="F74">
-        <v>1080.864</v>
+        <v>1095.876</v>
       </c>
       <c r="G74">
         <v>58.1</v>
@@ -7355,28 +7355,28 @@
         <v>448.025</v>
       </c>
       <c r="M74">
-        <v>76.88291315288866</v>
+        <v>77.95073139112321</v>
       </c>
       <c r="N74">
-        <v>371.1420868471113</v>
+        <v>370.0742686088768</v>
       </c>
       <c r="O74">
-        <v>74.22841736942227</v>
+        <v>74.01485372177535</v>
       </c>
       <c r="P74">
-        <v>296.913669477689</v>
+        <v>296.0594148871014</v>
       </c>
       <c r="Q74">
-        <v>522.0136694776891</v>
+        <v>521.1594148871014</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1510826498540131</v>
+        <v>0.1547269091082192</v>
       </c>
       <c r="T74">
-        <v>1.628689109346559</v>
+        <v>1.685064640995799</v>
       </c>
       <c r="U74">
         <v>0.07113097776675759</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.827367637709846</v>
+        <v>5.747540683768615</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08331675647500561</v>
+        <v>0.08335892779723518</v>
       </c>
       <c r="C75">
-        <v>422.5094726937448</v>
+        <v>405.8578580181454</v>
       </c>
       <c r="D75">
-        <v>1460.285472693745</v>
+        <v>1458.645858018145</v>
       </c>
       <c r="E75">
-        <v>508.9759999999998</v>
+        <v>523.9879999999999</v>
       </c>
       <c r="F75">
-        <v>1095.876</v>
+        <v>1110.888</v>
       </c>
       <c r="G75">
         <v>58.1</v>
@@ -7437,28 +7437,28 @@
         <v>448.025</v>
       </c>
       <c r="M75">
-        <v>77.95073139112321</v>
+        <v>79.01854962935779</v>
       </c>
       <c r="N75">
-        <v>370.0742686088768</v>
+        <v>369.0064503706422</v>
       </c>
       <c r="O75">
-        <v>74.01485372177535</v>
+        <v>73.80129007412845</v>
       </c>
       <c r="P75">
-        <v>296.0594148871014</v>
+        <v>295.2051602965138</v>
       </c>
       <c r="Q75">
-        <v>521.1594148871014</v>
+        <v>520.3051602965138</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1547269091082192</v>
+        <v>0.1586514959973642</v>
       </c>
       <c r="T75">
-        <v>1.685064640995799</v>
+        <v>1.745776752002674</v>
       </c>
       <c r="U75">
         <v>0.07113097776675759</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.747540683768615</v>
+        <v>5.669871215069039</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08335892779723518</v>
+        <v>0.08340109911946475</v>
       </c>
       <c r="C76">
-        <v>405.8578580181454</v>
+        <v>389.209921145612</v>
       </c>
       <c r="D76">
-        <v>1458.645858018145</v>
+        <v>1457.009921145612</v>
       </c>
       <c r="E76">
-        <v>523.9879999999999</v>
+        <v>538.9999999999999</v>
       </c>
       <c r="F76">
-        <v>1110.888</v>
+        <v>1125.9</v>
       </c>
       <c r="G76">
         <v>58.1</v>
@@ -7519,28 +7519,28 @@
         <v>448.025</v>
       </c>
       <c r="M76">
-        <v>79.01854962935779</v>
+        <v>80.08636786759236</v>
       </c>
       <c r="N76">
-        <v>369.0064503706422</v>
+        <v>367.9386321324076</v>
       </c>
       <c r="O76">
-        <v>73.80129007412845</v>
+        <v>73.58772642648152</v>
       </c>
       <c r="P76">
-        <v>295.2051602965138</v>
+        <v>294.3509057059261</v>
       </c>
       <c r="Q76">
-        <v>520.3051602965138</v>
+        <v>519.4509057059261</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1586514959973642</v>
+        <v>0.1628900498376408</v>
       </c>
       <c r="T76">
-        <v>1.745776752002674</v>
+        <v>1.811345831890099</v>
       </c>
       <c r="U76">
         <v>0.07113097776675759</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.669871215069039</v>
+        <v>5.594272932201451</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08340109911946475</v>
+        <v>0.08344327044169431</v>
       </c>
       <c r="C77">
-        <v>389.209921145612</v>
+        <v>372.5656497155442</v>
       </c>
       <c r="D77">
-        <v>1457.009921145612</v>
+        <v>1455.377649715544</v>
       </c>
       <c r="E77">
-        <v>538.9999999999999</v>
+        <v>554.0119999999998</v>
       </c>
       <c r="F77">
-        <v>1125.9</v>
+        <v>1140.912</v>
       </c>
       <c r="G77">
         <v>58.1</v>
@@ -7601,28 +7601,28 @@
         <v>448.025</v>
       </c>
       <c r="M77">
-        <v>80.08636786759236</v>
+        <v>81.15418610582692</v>
       </c>
       <c r="N77">
-        <v>367.9386321324076</v>
+        <v>366.8708138941731</v>
       </c>
       <c r="O77">
-        <v>73.58772642648152</v>
+        <v>73.37416277883462</v>
       </c>
       <c r="P77">
-        <v>294.3509057059261</v>
+        <v>293.4966511153385</v>
       </c>
       <c r="Q77">
-        <v>519.4509057059261</v>
+        <v>518.5966511153385</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1628900498376408</v>
+        <v>0.1674818164979404</v>
       </c>
       <c r="T77">
-        <v>1.811345831890099</v>
+        <v>1.882379001768142</v>
       </c>
       <c r="U77">
         <v>0.07113097776675759</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.594272932201451</v>
+        <v>5.520664077830379</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08344327044169431</v>
+        <v>0.08348544176392389</v>
       </c>
       <c r="C78">
-        <v>372.5656497155442</v>
+        <v>355.925031422667</v>
       </c>
       <c r="D78">
-        <v>1455.377649715544</v>
+        <v>1453.749031422667</v>
       </c>
       <c r="E78">
-        <v>554.0119999999998</v>
+        <v>569.024</v>
       </c>
       <c r="F78">
-        <v>1140.912</v>
+        <v>1155.924</v>
       </c>
       <c r="G78">
         <v>58.1</v>
@@ -7683,28 +7683,28 @@
         <v>448.025</v>
       </c>
       <c r="M78">
-        <v>81.15418610582692</v>
+        <v>82.22200434406149</v>
       </c>
       <c r="N78">
-        <v>366.8708138941731</v>
+        <v>365.8029956559385</v>
       </c>
       <c r="O78">
-        <v>73.37416277883462</v>
+        <v>73.16059913118771</v>
       </c>
       <c r="P78">
-        <v>293.4966511153385</v>
+        <v>292.6423965247508</v>
       </c>
       <c r="Q78">
-        <v>518.5966511153385</v>
+        <v>517.7423965247508</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1674818164979404</v>
+        <v>0.1724728672156574</v>
       </c>
       <c r="T78">
-        <v>1.882379001768142</v>
+        <v>1.959588969026884</v>
       </c>
       <c r="U78">
         <v>0.07113097776675759</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.520664077830379</v>
+        <v>5.44896714175466</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08348544176392389</v>
+        <v>0.08352761308615345</v>
       </c>
       <c r="C79">
-        <v>355.925031422667</v>
+        <v>339.2880540167273</v>
       </c>
       <c r="D79">
-        <v>1453.749031422667</v>
+        <v>1452.124054016727</v>
       </c>
       <c r="E79">
-        <v>569.024</v>
+        <v>584.0359999999999</v>
       </c>
       <c r="F79">
-        <v>1155.924</v>
+        <v>1170.936</v>
       </c>
       <c r="G79">
         <v>58.1</v>
@@ -7765,28 +7765,28 @@
         <v>448.025</v>
       </c>
       <c r="M79">
-        <v>82.22200434406149</v>
+        <v>83.28982258229605</v>
       </c>
       <c r="N79">
-        <v>365.8029956559385</v>
+        <v>364.7351774177039</v>
       </c>
       <c r="O79">
-        <v>73.16059913118771</v>
+        <v>72.94703548354079</v>
       </c>
       <c r="P79">
-        <v>292.6423965247508</v>
+        <v>291.7881419341631</v>
       </c>
       <c r="Q79">
-        <v>517.7423965247508</v>
+        <v>516.8881419341632</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1724728672156574</v>
+        <v>0.1779176498168032</v>
       </c>
       <c r="T79">
-        <v>1.959588969026884</v>
+        <v>2.04381802421824</v>
       </c>
       <c r="U79">
         <v>0.07113097776675759</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.44896714175466</v>
+        <v>5.379108588655241</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08352761308615345</v>
+        <v>0.08356978440838302</v>
       </c>
       <c r="C80">
-        <v>339.2880540167273</v>
+        <v>322.6547053021804</v>
       </c>
       <c r="D80">
-        <v>1452.124054016727</v>
+        <v>1450.50270530218</v>
       </c>
       <c r="E80">
-        <v>584.0359999999999</v>
+        <v>599.0479999999999</v>
       </c>
       <c r="F80">
-        <v>1170.936</v>
+        <v>1185.948</v>
       </c>
       <c r="G80">
         <v>58.1</v>
@@ -7847,28 +7847,28 @@
         <v>448.025</v>
       </c>
       <c r="M80">
-        <v>83.28982258229605</v>
+        <v>84.35764082053062</v>
       </c>
       <c r="N80">
-        <v>364.7351774177039</v>
+        <v>363.6673591794694</v>
       </c>
       <c r="O80">
-        <v>72.94703548354079</v>
+        <v>72.73347183589388</v>
       </c>
       <c r="P80">
-        <v>291.7881419341631</v>
+        <v>290.9338873435755</v>
       </c>
       <c r="Q80">
-        <v>516.8881419341632</v>
+        <v>516.0338873435755</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1779176498168032</v>
+        <v>0.1838809831418677</v>
       </c>
       <c r="T80">
-        <v>2.04381802421824</v>
+        <v>2.136068894189724</v>
       </c>
       <c r="U80">
         <v>0.07113097776675759</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.379108588655241</v>
+        <v>5.311018606520365</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08356978440838302</v>
+        <v>0.08361195573061259</v>
       </c>
       <c r="C81">
-        <v>322.6547053021804</v>
+        <v>306.0249731378892</v>
       </c>
       <c r="D81">
-        <v>1450.50270530218</v>
+        <v>1448.884973137889</v>
       </c>
       <c r="E81">
-        <v>599.0479999999999</v>
+        <v>614.0599999999998</v>
       </c>
       <c r="F81">
-        <v>1185.948</v>
+        <v>1200.96</v>
       </c>
       <c r="G81">
         <v>58.1</v>
@@ -7929,28 +7929,28 @@
         <v>448.025</v>
       </c>
       <c r="M81">
-        <v>84.35764082053062</v>
+        <v>85.42545905876517</v>
       </c>
       <c r="N81">
-        <v>363.6673591794694</v>
+        <v>362.5995409412348</v>
       </c>
       <c r="O81">
-        <v>72.73347183589388</v>
+        <v>72.51990818824696</v>
       </c>
       <c r="P81">
-        <v>290.9338873435755</v>
+        <v>290.0796327529878</v>
       </c>
       <c r="Q81">
-        <v>516.0338873435755</v>
+        <v>515.1796327529878</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1838809831418677</v>
+        <v>0.1904406497994386</v>
       </c>
       <c r="T81">
-        <v>2.136068894189724</v>
+        <v>2.237544851158357</v>
       </c>
       <c r="U81">
         <v>0.07113097776675759</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.311018606520365</v>
+        <v>5.244630873938861</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08361195573061259</v>
+        <v>0.08365412705284214</v>
       </c>
       <c r="C82">
-        <v>306.0249731378892</v>
+        <v>289.3988454368209</v>
       </c>
       <c r="D82">
-        <v>1448.884973137889</v>
+        <v>1447.270845436821</v>
       </c>
       <c r="E82">
-        <v>614.0599999999998</v>
+        <v>629.072</v>
       </c>
       <c r="F82">
-        <v>1200.96</v>
+        <v>1215.972</v>
       </c>
       <c r="G82">
         <v>58.1</v>
@@ -8011,28 +8011,28 @@
         <v>448.025</v>
       </c>
       <c r="M82">
-        <v>85.42545905876517</v>
+        <v>86.49327729699975</v>
       </c>
       <c r="N82">
-        <v>362.5995409412348</v>
+        <v>361.5317227030002</v>
       </c>
       <c r="O82">
-        <v>72.51990818824696</v>
+        <v>72.30634454060005</v>
       </c>
       <c r="P82">
-        <v>290.0796327529878</v>
+        <v>289.2253781624002</v>
       </c>
       <c r="Q82">
-        <v>515.1796327529878</v>
+        <v>514.3253781624003</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1904406497994386</v>
+        <v>0.1976908076841223</v>
       </c>
       <c r="T82">
-        <v>2.237544851158357</v>
+        <v>2.3497024878079</v>
       </c>
       <c r="U82">
         <v>0.07113097776675759</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.244630873938861</v>
+        <v>5.179882344630974</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08365412705284214</v>
+        <v>0.0836962983750717</v>
       </c>
       <c r="C83">
-        <v>289.3988454368209</v>
+        <v>272.7763101657426</v>
       </c>
       <c r="D83">
-        <v>1447.270845436821</v>
+        <v>1445.660310165743</v>
       </c>
       <c r="E83">
-        <v>629.072</v>
+        <v>644.0839999999999</v>
       </c>
       <c r="F83">
-        <v>1215.972</v>
+        <v>1230.984</v>
       </c>
       <c r="G83">
         <v>58.1</v>
@@ -8093,28 +8093,28 @@
         <v>448.025</v>
       </c>
       <c r="M83">
-        <v>86.49327729699975</v>
+        <v>87.56109553523432</v>
       </c>
       <c r="N83">
-        <v>361.5317227030002</v>
+        <v>360.4639044647657</v>
       </c>
       <c r="O83">
-        <v>72.30634454060005</v>
+        <v>72.09278089295314</v>
       </c>
       <c r="P83">
-        <v>289.2253781624002</v>
+        <v>288.3711235718125</v>
       </c>
       <c r="Q83">
-        <v>514.3253781624003</v>
+        <v>513.4711235718125</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1976908076841223</v>
+        <v>0.2057465386671041</v>
       </c>
       <c r="T83">
-        <v>2.3497024878079</v>
+        <v>2.474322084085168</v>
       </c>
       <c r="U83">
         <v>0.07113097776675759</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.179882344630974</v>
+        <v>5.11671304774523</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.0836962983750717</v>
+        <v>0.08373846969730128</v>
       </c>
       <c r="C84">
-        <v>272.7763101657426</v>
+        <v>256.157355344925</v>
       </c>
       <c r="D84">
-        <v>1445.660310165743</v>
+        <v>1444.053355344925</v>
       </c>
       <c r="E84">
-        <v>644.0839999999999</v>
+        <v>659.0959999999999</v>
       </c>
       <c r="F84">
-        <v>1230.984</v>
+        <v>1245.996</v>
       </c>
       <c r="G84">
         <v>58.1</v>
@@ -8175,28 +8175,28 @@
         <v>448.025</v>
       </c>
       <c r="M84">
-        <v>87.56109553523432</v>
+        <v>88.62891377346888</v>
       </c>
       <c r="N84">
-        <v>360.4639044647657</v>
+        <v>359.3960862265311</v>
       </c>
       <c r="O84">
-        <v>72.09278089295314</v>
+        <v>71.87921724530622</v>
       </c>
       <c r="P84">
-        <v>288.3711235718125</v>
+        <v>287.5168689812249</v>
       </c>
       <c r="Q84">
-        <v>513.4711235718125</v>
+        <v>512.6168689812249</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2057465386671041</v>
+        <v>0.2147500027069073</v>
       </c>
       <c r="T84">
-        <v>2.474322084085168</v>
+        <v>2.613602809336233</v>
       </c>
       <c r="U84">
         <v>0.07113097776675759</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.11671304774523</v>
+        <v>5.055065902591672</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08373846969730128</v>
+        <v>0.08378064101953084</v>
       </c>
       <c r="C85">
-        <v>256.157355344925</v>
+        <v>239.5419690478477</v>
       </c>
       <c r="D85">
-        <v>1444.053355344925</v>
+        <v>1442.449969047848</v>
       </c>
       <c r="E85">
-        <v>659.0959999999999</v>
+        <v>674.1080000000001</v>
       </c>
       <c r="F85">
-        <v>1245.996</v>
+        <v>1261.008</v>
       </c>
       <c r="G85">
         <v>58.1</v>
@@ -8257,28 +8257,28 @@
         <v>448.025</v>
       </c>
       <c r="M85">
-        <v>88.62891377346888</v>
+        <v>89.69673201170345</v>
       </c>
       <c r="N85">
-        <v>359.3960862265311</v>
+        <v>358.3282679882965</v>
       </c>
       <c r="O85">
-        <v>71.87921724530622</v>
+        <v>71.66565359765931</v>
       </c>
       <c r="P85">
-        <v>287.5168689812249</v>
+        <v>286.6626143906373</v>
       </c>
       <c r="Q85">
-        <v>512.6168689812249</v>
+        <v>511.7626143906373</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2147500027069073</v>
+        <v>0.224878899751686</v>
       </c>
       <c r="T85">
-        <v>2.613602809336233</v>
+        <v>2.770293625243681</v>
       </c>
       <c r="U85">
         <v>0.07113097776675759</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.055065902591672</v>
+        <v>4.994886546608438</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08378064101953084</v>
+        <v>0.08382281234176042</v>
       </c>
       <c r="C86">
-        <v>239.5419690478479</v>
+        <v>222.9301394008978</v>
       </c>
       <c r="D86">
-        <v>1442.449969047848</v>
+        <v>1440.850139400898</v>
       </c>
       <c r="E86">
-        <v>674.1079999999998</v>
+        <v>689.1199999999998</v>
       </c>
       <c r="F86">
-        <v>1261.008</v>
+        <v>1276.02</v>
       </c>
       <c r="G86">
         <v>58.1</v>
@@ -8339,28 +8339,28 @@
         <v>448.025</v>
       </c>
       <c r="M86">
-        <v>89.69673201170343</v>
+        <v>90.764550249938</v>
       </c>
       <c r="N86">
-        <v>358.3282679882965</v>
+        <v>357.260449750062</v>
       </c>
       <c r="O86">
-        <v>71.66565359765931</v>
+        <v>71.45208995001239</v>
       </c>
       <c r="P86">
-        <v>286.6626143906373</v>
+        <v>285.8083598000496</v>
       </c>
       <c r="Q86">
-        <v>511.7626143906373</v>
+        <v>510.9083598000496</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2248788997516859</v>
+        <v>0.236358316402435</v>
       </c>
       <c r="T86">
-        <v>2.77029362524368</v>
+        <v>2.947876549938787</v>
       </c>
       <c r="U86">
         <v>0.07113097776675759</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.99488654660844</v>
+        <v>4.936123175471869</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08382281234176042</v>
+        <v>0.08386498366398998</v>
       </c>
       <c r="C87">
-        <v>222.9301394008978</v>
+        <v>206.3218545830835</v>
       </c>
       <c r="D87">
-        <v>1440.850139400898</v>
+        <v>1439.253854583083</v>
       </c>
       <c r="E87">
-        <v>689.1199999999998</v>
+        <v>704.1319999999999</v>
       </c>
       <c r="F87">
-        <v>1276.02</v>
+        <v>1291.032</v>
       </c>
       <c r="G87">
         <v>58.1</v>
@@ -8421,28 +8421,28 @@
         <v>448.025</v>
       </c>
       <c r="M87">
-        <v>90.764550249938</v>
+        <v>91.83236848817258</v>
       </c>
       <c r="N87">
-        <v>357.260449750062</v>
+        <v>356.1926315118274</v>
       </c>
       <c r="O87">
-        <v>71.45208995001239</v>
+        <v>71.23852630236549</v>
       </c>
       <c r="P87">
-        <v>285.8083598000496</v>
+        <v>284.9541052094619</v>
       </c>
       <c r="Q87">
-        <v>510.9083598000496</v>
+        <v>510.054105209462</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.236358316402435</v>
+        <v>0.2494776497175768</v>
       </c>
       <c r="T87">
-        <v>2.947876549938787</v>
+        <v>3.150828463876054</v>
       </c>
       <c r="U87">
         <v>0.07113097776675759</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.936123175471869</v>
+        <v>4.87872639436173</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08386498366398998</v>
+        <v>0.08390715498621953</v>
       </c>
       <c r="C88">
-        <v>206.3218545830835</v>
+        <v>189.7171028257374</v>
       </c>
       <c r="D88">
-        <v>1439.253854583083</v>
+        <v>1437.661102825737</v>
       </c>
       <c r="E88">
-        <v>704.1319999999999</v>
+        <v>719.1439999999999</v>
       </c>
       <c r="F88">
-        <v>1291.032</v>
+        <v>1306.044</v>
       </c>
       <c r="G88">
         <v>58.1</v>
@@ -8503,28 +8503,28 @@
         <v>448.025</v>
       </c>
       <c r="M88">
-        <v>91.83236848817258</v>
+        <v>92.90018672640714</v>
       </c>
       <c r="N88">
-        <v>356.1926315118274</v>
+        <v>355.1248132735928</v>
       </c>
       <c r="O88">
-        <v>71.23852630236549</v>
+        <v>71.02496265471858</v>
       </c>
       <c r="P88">
-        <v>284.9541052094619</v>
+        <v>284.0998506188743</v>
       </c>
       <c r="Q88">
-        <v>510.054105209462</v>
+        <v>509.1998506188743</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2494776497175768</v>
+        <v>0.2646153420042789</v>
       </c>
       <c r="T88">
-        <v>3.150828463876054</v>
+        <v>3.385003749188283</v>
       </c>
       <c r="U88">
         <v>0.07113097776675759</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.87872639436173</v>
+        <v>4.822649079484009</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08390715498621953</v>
+        <v>0.08394932630844912</v>
       </c>
       <c r="C89">
-        <v>189.7171028257374</v>
+        <v>173.1158724122301</v>
       </c>
       <c r="D89">
-        <v>1437.661102825737</v>
+        <v>1436.07187241223</v>
       </c>
       <c r="E89">
-        <v>719.1439999999999</v>
+        <v>734.1559999999998</v>
       </c>
       <c r="F89">
-        <v>1306.044</v>
+        <v>1321.056</v>
       </c>
       <c r="G89">
         <v>58.1</v>
@@ -8585,28 +8585,28 @@
         <v>448.025</v>
       </c>
       <c r="M89">
-        <v>92.90018672640714</v>
+        <v>93.96800496464169</v>
       </c>
       <c r="N89">
-        <v>355.1248132735928</v>
+        <v>354.0569950353583</v>
       </c>
       <c r="O89">
-        <v>71.02496265471858</v>
+        <v>70.81139900707166</v>
       </c>
       <c r="P89">
-        <v>284.0998506188743</v>
+        <v>283.2455960282866</v>
       </c>
       <c r="Q89">
-        <v>509.1998506188743</v>
+        <v>508.3455960282866</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2646153420042789</v>
+        <v>0.2822759830054314</v>
       </c>
       <c r="T89">
-        <v>3.385003749188283</v>
+        <v>3.658208248719219</v>
       </c>
       <c r="U89">
         <v>0.07113097776675759</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.822649079484009</v>
+        <v>4.767846249035328</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08394932630844912</v>
+        <v>0.08399149763067867</v>
       </c>
       <c r="C90">
-        <v>173.1158724122301</v>
+        <v>156.5181516776852</v>
       </c>
       <c r="D90">
-        <v>1436.07187241223</v>
+        <v>1434.486151677685</v>
       </c>
       <c r="E90">
-        <v>734.1559999999998</v>
+        <v>749.1679999999998</v>
       </c>
       <c r="F90">
-        <v>1321.056</v>
+        <v>1336.068</v>
       </c>
       <c r="G90">
         <v>58.1</v>
@@ -8667,28 +8667,28 @@
         <v>448.025</v>
       </c>
       <c r="M90">
-        <v>93.96800496464169</v>
+        <v>95.03582320287626</v>
       </c>
       <c r="N90">
-        <v>354.0569950353583</v>
+        <v>352.9891767971237</v>
       </c>
       <c r="O90">
-        <v>70.81139900707166</v>
+        <v>70.59783535942475</v>
       </c>
       <c r="P90">
-        <v>283.2455960282866</v>
+        <v>282.391341437699</v>
       </c>
       <c r="Q90">
-        <v>508.3455960282866</v>
+        <v>507.491341437699</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2822759830054314</v>
+        <v>0.303147649643157</v>
       </c>
       <c r="T90">
-        <v>3.658208248719219</v>
+        <v>3.981086293619414</v>
       </c>
       <c r="U90">
         <v>0.07113097776675759</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.767846249035328</v>
+        <v>4.714274942866392</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08399149763067867</v>
+        <v>0.08403366895290824</v>
       </c>
       <c r="C91">
-        <v>156.5181516776852</v>
+        <v>139.9239290086871</v>
       </c>
       <c r="D91">
-        <v>1434.486151677685</v>
+        <v>1432.903929008687</v>
       </c>
       <c r="E91">
-        <v>749.1679999999998</v>
+        <v>764.1799999999999</v>
       </c>
       <c r="F91">
-        <v>1336.068</v>
+        <v>1351.08</v>
       </c>
       <c r="G91">
         <v>58.1</v>
@@ -8749,28 +8749,28 @@
         <v>448.025</v>
       </c>
       <c r="M91">
-        <v>95.03582320287626</v>
+        <v>96.10364144111084</v>
       </c>
       <c r="N91">
-        <v>352.9891767971237</v>
+        <v>351.9213585588892</v>
       </c>
       <c r="O91">
-        <v>70.59783535942475</v>
+        <v>70.38427171177783</v>
       </c>
       <c r="P91">
-        <v>282.391341437699</v>
+        <v>281.5370868471113</v>
       </c>
       <c r="Q91">
-        <v>507.491341437699</v>
+        <v>506.6370868471113</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.303147649643157</v>
+        <v>0.3281936496084278</v>
       </c>
       <c r="T91">
-        <v>3.981086293619414</v>
+        <v>4.36853994749965</v>
       </c>
       <c r="U91">
         <v>0.07113097776675759</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>4.714274942866392</v>
+        <v>4.661894110167875</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08403366895290824</v>
+        <v>0.0840758402751378</v>
       </c>
       <c r="C92">
-        <v>139.9239290086871</v>
+        <v>123.3331928430052</v>
       </c>
       <c r="D92">
-        <v>1432.903929008687</v>
+        <v>1431.325192843005</v>
       </c>
       <c r="E92">
-        <v>764.1799999999999</v>
+        <v>779.1919999999999</v>
       </c>
       <c r="F92">
-        <v>1351.08</v>
+        <v>1366.092</v>
       </c>
       <c r="G92">
         <v>58.1</v>
@@ -8831,28 +8831,28 @@
         <v>448.025</v>
       </c>
       <c r="M92">
-        <v>96.10364144111084</v>
+        <v>97.17145967934539</v>
       </c>
       <c r="N92">
-        <v>351.9213585588892</v>
+        <v>350.8535403206546</v>
       </c>
       <c r="O92">
-        <v>70.38427171177783</v>
+        <v>70.17070806413092</v>
       </c>
       <c r="P92">
-        <v>281.5370868471113</v>
+        <v>280.6828322565237</v>
       </c>
       <c r="Q92">
-        <v>506.6370868471113</v>
+        <v>505.7828322565237</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3281936496084278</v>
+        <v>0.3588054273437588</v>
       </c>
       <c r="T92">
-        <v>4.36853994749965</v>
+        <v>4.842094413353271</v>
       </c>
       <c r="U92">
         <v>0.07113097776675759</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.661894110167875</v>
+        <v>4.610664504561636</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.0840758402751378</v>
+        <v>0.08411801159736737</v>
       </c>
       <c r="C93">
-        <v>123.3331928430052</v>
+        <v>106.7459316693062</v>
       </c>
       <c r="D93">
-        <v>1431.325192843005</v>
+        <v>1429.749931669306</v>
       </c>
       <c r="E93">
-        <v>779.1919999999999</v>
+        <v>794.2039999999998</v>
       </c>
       <c r="F93">
-        <v>1366.092</v>
+        <v>1381.104</v>
       </c>
       <c r="G93">
         <v>58.1</v>
@@ -8913,28 +8913,28 @@
         <v>448.025</v>
       </c>
       <c r="M93">
-        <v>97.17145967934539</v>
+        <v>98.23927791757995</v>
       </c>
       <c r="N93">
-        <v>350.8535403206546</v>
+        <v>349.78572208242</v>
       </c>
       <c r="O93">
-        <v>70.17070806413092</v>
+        <v>69.95714441648401</v>
       </c>
       <c r="P93">
-        <v>280.6828322565237</v>
+        <v>279.828577665936</v>
       </c>
       <c r="Q93">
-        <v>505.7828322565237</v>
+        <v>504.928577665936</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3588054273437588</v>
+        <v>0.3970701495129225</v>
       </c>
       <c r="T93">
-        <v>4.842094413353271</v>
+        <v>5.434037495670299</v>
       </c>
       <c r="U93">
         <v>0.07113097776675759</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.610664504561636</v>
+        <v>4.560548586033792</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08411801159736737</v>
+        <v>0.08416018291959694</v>
       </c>
       <c r="C94">
-        <v>106.7459316693062</v>
+        <v>90.16213402687799</v>
       </c>
       <c r="D94">
-        <v>1429.749931669306</v>
+        <v>1428.178134026878</v>
       </c>
       <c r="E94">
-        <v>794.2039999999998</v>
+        <v>809.216</v>
       </c>
       <c r="F94">
-        <v>1381.104</v>
+        <v>1396.116</v>
       </c>
       <c r="G94">
         <v>58.1</v>
@@ -8995,28 +8995,28 @@
         <v>448.025</v>
       </c>
       <c r="M94">
-        <v>98.23927791757995</v>
+        <v>99.30709615581453</v>
       </c>
       <c r="N94">
-        <v>349.78572208242</v>
+        <v>348.7179038441855</v>
       </c>
       <c r="O94">
-        <v>69.95714441648401</v>
+        <v>69.74358076883709</v>
       </c>
       <c r="P94">
-        <v>279.828577665936</v>
+        <v>278.9743230753484</v>
       </c>
       <c r="Q94">
-        <v>504.928577665936</v>
+        <v>504.0743230753484</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3970701495129225</v>
+        <v>0.4462676494447044</v>
       </c>
       <c r="T94">
-        <v>5.434037495670299</v>
+        <v>6.195107172935047</v>
       </c>
       <c r="U94">
         <v>0.07113097776675759</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.560548586033792</v>
+        <v>4.511510429194718</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08416018291959694</v>
+        <v>0.08608235424182649</v>
       </c>
       <c r="C95">
-        <v>90.16213402687799</v>
+        <v>7.001111857480055</v>
       </c>
       <c r="D95">
-        <v>1428.178134026878</v>
+        <v>1360.02911185748</v>
       </c>
       <c r="E95">
-        <v>809.216</v>
+        <v>824.228</v>
       </c>
       <c r="F95">
-        <v>1396.116</v>
+        <v>1411.128</v>
       </c>
       <c r="G95">
         <v>58.1</v>
@@ -9077,45 +9077,45 @@
         <v>448.025</v>
       </c>
       <c r="M95">
-        <v>99.30709615581453</v>
+        <v>103.9027343940491</v>
       </c>
       <c r="N95">
-        <v>348.7179038441855</v>
+        <v>344.1222656059509</v>
       </c>
       <c r="O95">
-        <v>69.74358076883709</v>
+        <v>68.82445312119019</v>
       </c>
       <c r="P95">
-        <v>278.9743230753484</v>
+        <v>275.2978124847608</v>
       </c>
       <c r="Q95">
-        <v>504.0743230753484</v>
+        <v>500.3978124847608</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4462676494447044</v>
+        <v>0.5118643160204137</v>
       </c>
       <c r="T95">
-        <v>6.195107172935047</v>
+        <v>7.209866742621378</v>
       </c>
       <c r="U95">
-        <v>0.07113097776675759</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V95">
         <v>0.2</v>
       </c>
       <c r="W95">
-        <v>0.05690478221340607</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y95">
-        <v>4.511510429194718</v>
+        <v>4.311965441649245</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08608235424182649</v>
+        <v>0.08614452556405605</v>
       </c>
       <c r="C96">
-        <v>7.001111857480055</v>
+        <v>-10.10670676903032</v>
       </c>
       <c r="D96">
-        <v>1360.02911185748</v>
+        <v>1357.93329323097</v>
       </c>
       <c r="E96">
-        <v>824.228</v>
+        <v>839.2399999999999</v>
       </c>
       <c r="F96">
-        <v>1411.128</v>
+        <v>1426.14</v>
       </c>
       <c r="G96">
         <v>58.1</v>
@@ -9159,28 +9159,28 @@
         <v>448.025</v>
       </c>
       <c r="M96">
-        <v>103.9027343940491</v>
+        <v>105.0080826322836</v>
       </c>
       <c r="N96">
-        <v>344.1222656059509</v>
+        <v>343.0169173677164</v>
       </c>
       <c r="O96">
-        <v>68.82445312119019</v>
+        <v>68.60338347354327</v>
       </c>
       <c r="P96">
-        <v>275.2978124847608</v>
+        <v>274.4135338941731</v>
       </c>
       <c r="Q96">
-        <v>500.3978124847608</v>
+        <v>499.5135338941731</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5118643160204137</v>
+        <v>0.6036996492264068</v>
       </c>
       <c r="T96">
-        <v>7.209866742621378</v>
+        <v>8.630530140182247</v>
       </c>
       <c r="U96">
         <v>0.07363097776675757</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.311965441649245</v>
+        <v>4.266576331737148</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08614452556405605</v>
+        <v>0.08620669688628563</v>
       </c>
       <c r="C97">
-        <v>-10.10670676903032</v>
+        <v>-27.20807597872658</v>
       </c>
       <c r="D97">
-        <v>1357.93329323097</v>
+        <v>1355.843924021274</v>
       </c>
       <c r="E97">
-        <v>839.2399999999999</v>
+        <v>854.2520000000001</v>
       </c>
       <c r="F97">
-        <v>1426.14</v>
+        <v>1441.152</v>
       </c>
       <c r="G97">
         <v>58.1</v>
@@ -9241,28 +9241,28 @@
         <v>448.025</v>
       </c>
       <c r="M97">
-        <v>105.0080826322836</v>
+        <v>106.1134308705182</v>
       </c>
       <c r="N97">
-        <v>343.0169173677164</v>
+        <v>341.9115691294818</v>
       </c>
       <c r="O97">
-        <v>68.60338347354327</v>
+        <v>68.38231382589636</v>
       </c>
       <c r="P97">
-        <v>274.4135338941731</v>
+        <v>273.5292553035854</v>
       </c>
       <c r="Q97">
-        <v>499.5135338941731</v>
+        <v>498.6292553035855</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6036996492264068</v>
+        <v>0.7414526490353964</v>
       </c>
       <c r="T97">
-        <v>8.630530140182247</v>
+        <v>10.76152523652355</v>
       </c>
       <c r="U97">
         <v>0.07363097776675757</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.266576331737148</v>
+        <v>4.222132828281552</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08620669688628563</v>
+        <v>0.08626886820851519</v>
       </c>
       <c r="C98">
-        <v>-27.20807597872636</v>
+        <v>-44.30302549584644</v>
       </c>
       <c r="D98">
-        <v>1355.843924021274</v>
+        <v>1353.760974504153</v>
       </c>
       <c r="E98">
-        <v>854.2519999999998</v>
+        <v>869.2639999999998</v>
       </c>
       <c r="F98">
-        <v>1441.152</v>
+        <v>1456.164</v>
       </c>
       <c r="G98">
         <v>58.1</v>
@@ -9323,28 +9323,28 @@
         <v>448.025</v>
       </c>
       <c r="M98">
-        <v>106.1134308705182</v>
+        <v>107.2187791087528</v>
       </c>
       <c r="N98">
-        <v>341.9115691294818</v>
+        <v>340.8062208912472</v>
       </c>
       <c r="O98">
-        <v>68.38231382589636</v>
+        <v>68.16124417824945</v>
       </c>
       <c r="P98">
-        <v>273.5292553035854</v>
+        <v>272.6449767129978</v>
       </c>
       <c r="Q98">
-        <v>498.6292553035855</v>
+        <v>497.7449767129978</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7414526490353947</v>
+        <v>0.9710409820503764</v>
       </c>
       <c r="T98">
-        <v>10.76152523652352</v>
+        <v>14.31318373042567</v>
       </c>
       <c r="U98">
         <v>0.07363097776675757</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.222132828281552</v>
+        <v>4.178605685721949</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08626886820851519</v>
+        <v>0.08633103953074477</v>
       </c>
       <c r="C99">
-        <v>-44.30302549584644</v>
+        <v>-61.39158486225188</v>
       </c>
       <c r="D99">
-        <v>1353.760974504153</v>
+        <v>1351.684415137748</v>
       </c>
       <c r="E99">
-        <v>869.2639999999998</v>
+        <v>884.2759999999997</v>
       </c>
       <c r="F99">
-        <v>1456.164</v>
+        <v>1471.176</v>
       </c>
       <c r="G99">
         <v>58.1</v>
@@ -9405,28 +9405,28 @@
         <v>448.025</v>
       </c>
       <c r="M99">
-        <v>107.2187791087528</v>
+        <v>108.3241273469873</v>
       </c>
       <c r="N99">
-        <v>340.8062208912472</v>
+        <v>339.7008726530127</v>
       </c>
       <c r="O99">
-        <v>68.16124417824945</v>
+        <v>67.94017453060253</v>
       </c>
       <c r="P99">
-        <v>272.6449767129978</v>
+        <v>271.7606981224101</v>
       </c>
       <c r="Q99">
-        <v>497.7449767129978</v>
+        <v>496.8606981224102</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9710409820503764</v>
+        <v>1.43021764808034</v>
       </c>
       <c r="T99">
-        <v>14.31318373042567</v>
+        <v>21.41650071822997</v>
       </c>
       <c r="U99">
         <v>0.07363097776675757</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.178605685721949</v>
+        <v>4.135966852194174</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08633103953074477</v>
+        <v>0.08639321085297431</v>
       </c>
       <c r="C100">
-        <v>-61.39158486225188</v>
+        <v>-78.47378343882087</v>
       </c>
       <c r="D100">
-        <v>1351.684415137748</v>
+        <v>1349.614216561179</v>
       </c>
       <c r="E100">
-        <v>884.2759999999997</v>
+        <v>899.2879999999999</v>
       </c>
       <c r="F100">
-        <v>1471.176</v>
+        <v>1486.188</v>
       </c>
       <c r="G100">
         <v>58.1</v>
@@ -9487,28 +9487,28 @@
         <v>448.025</v>
       </c>
       <c r="M100">
-        <v>108.3241273469873</v>
+        <v>109.4294755852219</v>
       </c>
       <c r="N100">
-        <v>339.7008726530127</v>
+        <v>338.5955244147781</v>
       </c>
       <c r="O100">
-        <v>67.94017453060253</v>
+        <v>67.71910488295562</v>
       </c>
       <c r="P100">
-        <v>271.7606981224101</v>
+        <v>270.8764195318225</v>
       </c>
       <c r="Q100">
-        <v>496.8606981224102</v>
+        <v>495.9764195318225</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.43021764808034</v>
+        <v>2.80774764617023</v>
       </c>
       <c r="T100">
-        <v>21.41650071822997</v>
+        <v>42.72645168164287</v>
       </c>
       <c r="U100">
         <v>0.07363097776675757</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.135966852194174</v>
+        <v>4.094189409242717</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08639321085297431</v>
-      </c>
-      <c r="C101">
-        <v>-78.47378343882087</v>
-      </c>
-      <c r="D101">
-        <v>1349.614216561179</v>
-      </c>
-      <c r="E101">
-        <v>899.2879999999999</v>
-      </c>
-      <c r="F101">
-        <v>1486.188</v>
-      </c>
-      <c r="G101">
-        <v>58.1</v>
-      </c>
-      <c r="H101">
-        <v>914.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>673.125</v>
-      </c>
-      <c r="K101">
-        <v>225.1</v>
-      </c>
-      <c r="L101">
-        <v>448.025</v>
-      </c>
-      <c r="M101">
-        <v>109.4294755852219</v>
-      </c>
-      <c r="N101">
-        <v>338.5955244147781</v>
-      </c>
-      <c r="O101">
-        <v>67.71910488295562</v>
-      </c>
-      <c r="P101">
-        <v>270.8764195318225</v>
-      </c>
-      <c r="Q101">
-        <v>495.9764195318225</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.80774764617023</v>
-      </c>
-      <c r="T101">
-        <v>42.72645168164287</v>
-      </c>
-      <c r="U101">
-        <v>0.07363097776675757</v>
-      </c>
-      <c r="V101">
-        <v>0.2</v>
-      </c>
-      <c r="W101">
-        <v>0.05890478221340606</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Baa2/BBB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>4.094189409242717</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
